--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -463,17 +463,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm\-yy"/>
+    <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="#,##0.00_ ;[RED]\-#,##0.00\ "/>
     <numFmt numFmtId="168" formatCode="0%"/>
-    <numFmt numFmtId="169" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="170" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
-    <numFmt numFmtId="172" formatCode="General"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1125,7 +1124,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1257,11 +1256,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1297,15 +1296,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1313,11 +1312,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1325,15 +1324,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1345,19 +1344,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1369,7 +1368,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1565,37 +1564,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1668,8 +1667,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC111"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW111"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.99"/>
@@ -1699,7 +1698,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="28" style="1" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9"/>
       <c r="B1" s="10" t="s">
         <v>0</v>
@@ -1789,6 +1788,234 @@
         <f aca="false">AC57+AC110</f>
         <v>540</v>
       </c>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+      <c r="AP1" s="19"/>
+      <c r="AQ1" s="19"/>
+      <c r="AR1" s="19"/>
+      <c r="AS1" s="19"/>
+      <c r="AT1" s="19"/>
+      <c r="AU1" s="19"/>
+      <c r="AV1" s="19"/>
+      <c r="AW1" s="19"/>
+      <c r="AX1" s="19"/>
+      <c r="AY1" s="19"/>
+      <c r="AZ1" s="19"/>
+      <c r="BA1" s="19"/>
+      <c r="BB1" s="19"/>
+      <c r="BC1" s="19"/>
+      <c r="BD1" s="19"/>
+      <c r="BE1" s="19"/>
+      <c r="BF1" s="19"/>
+      <c r="BG1" s="19"/>
+      <c r="BH1" s="19"/>
+      <c r="BI1" s="19"/>
+      <c r="BJ1" s="19"/>
+      <c r="BK1" s="19"/>
+      <c r="BL1" s="19"/>
+      <c r="BM1" s="19"/>
+      <c r="BN1" s="19"/>
+      <c r="BO1" s="19"/>
+      <c r="BP1" s="19"/>
+      <c r="BQ1" s="19"/>
+      <c r="BR1" s="19"/>
+      <c r="BS1" s="19"/>
+      <c r="BT1" s="19"/>
+      <c r="BU1" s="19"/>
+      <c r="BV1" s="19"/>
+      <c r="BW1" s="19"/>
+      <c r="BX1" s="19"/>
+      <c r="BY1" s="19"/>
+      <c r="BZ1" s="19"/>
+      <c r="CA1" s="19"/>
+      <c r="CB1" s="19"/>
+      <c r="CC1" s="19"/>
+      <c r="CD1" s="19"/>
+      <c r="CE1" s="19"/>
+      <c r="CF1" s="19"/>
+      <c r="CG1" s="19"/>
+      <c r="CH1" s="19"/>
+      <c r="CI1" s="19"/>
+      <c r="CJ1" s="19"/>
+      <c r="CK1" s="19"/>
+      <c r="CL1" s="19"/>
+      <c r="CM1" s="19"/>
+      <c r="CN1" s="19"/>
+      <c r="CO1" s="19"/>
+      <c r="CP1" s="19"/>
+      <c r="CQ1" s="19"/>
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19"/>
+      <c r="CT1" s="19"/>
+      <c r="CU1" s="19"/>
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19"/>
+      <c r="CX1" s="19"/>
+      <c r="CY1" s="19"/>
+      <c r="CZ1" s="19"/>
+      <c r="DA1" s="19"/>
+      <c r="DB1" s="19"/>
+      <c r="DC1" s="19"/>
+      <c r="DD1" s="19"/>
+      <c r="DE1" s="19"/>
+      <c r="DF1" s="19"/>
+      <c r="DG1" s="19"/>
+      <c r="DH1" s="19"/>
+      <c r="DI1" s="19"/>
+      <c r="DJ1" s="19"/>
+      <c r="DK1" s="19"/>
+      <c r="DL1" s="19"/>
+      <c r="DM1" s="19"/>
+      <c r="DN1" s="19"/>
+      <c r="DO1" s="19"/>
+      <c r="DP1" s="19"/>
+      <c r="DQ1" s="19"/>
+      <c r="DR1" s="19"/>
+      <c r="DS1" s="19"/>
+      <c r="DT1" s="19"/>
+      <c r="DU1" s="19"/>
+      <c r="DV1" s="19"/>
+      <c r="DW1" s="19"/>
+      <c r="DX1" s="19"/>
+      <c r="DY1" s="19"/>
+      <c r="DZ1" s="19"/>
+      <c r="EA1" s="19"/>
+      <c r="EB1" s="19"/>
+      <c r="EC1" s="19"/>
+      <c r="ED1" s="19"/>
+      <c r="EE1" s="19"/>
+      <c r="EF1" s="19"/>
+      <c r="EG1" s="19"/>
+      <c r="EH1" s="19"/>
+      <c r="EI1" s="19"/>
+      <c r="EJ1" s="19"/>
+      <c r="EK1" s="19"/>
+      <c r="EL1" s="19"/>
+      <c r="EM1" s="19"/>
+      <c r="EN1" s="19"/>
+      <c r="EO1" s="19"/>
+      <c r="EP1" s="19"/>
+      <c r="EQ1" s="19"/>
+      <c r="ER1" s="19"/>
+      <c r="ES1" s="19"/>
+      <c r="ET1" s="19"/>
+      <c r="EU1" s="19"/>
+      <c r="EV1" s="19"/>
+      <c r="EW1" s="19"/>
+      <c r="EX1" s="19"/>
+      <c r="EY1" s="19"/>
+      <c r="EZ1" s="19"/>
+      <c r="FA1" s="19"/>
+      <c r="FB1" s="19"/>
+      <c r="FC1" s="19"/>
+      <c r="FD1" s="19"/>
+      <c r="FE1" s="19"/>
+      <c r="FF1" s="19"/>
+      <c r="FG1" s="19"/>
+      <c r="FH1" s="19"/>
+      <c r="FI1" s="19"/>
+      <c r="FJ1" s="19"/>
+      <c r="FK1" s="19"/>
+      <c r="FL1" s="19"/>
+      <c r="FM1" s="19"/>
+      <c r="FN1" s="19"/>
+      <c r="FO1" s="19"/>
+      <c r="FP1" s="19"/>
+      <c r="FQ1" s="19"/>
+      <c r="FR1" s="19"/>
+      <c r="FS1" s="19"/>
+      <c r="FT1" s="19"/>
+      <c r="FU1" s="19"/>
+      <c r="FV1" s="19"/>
+      <c r="FW1" s="19"/>
+      <c r="FX1" s="19"/>
+      <c r="FY1" s="19"/>
+      <c r="FZ1" s="19"/>
+      <c r="GA1" s="19"/>
+      <c r="GB1" s="19"/>
+      <c r="GC1" s="19"/>
+      <c r="GD1" s="19"/>
+      <c r="GE1" s="19"/>
+      <c r="GF1" s="19"/>
+      <c r="GG1" s="19"/>
+      <c r="GH1" s="19"/>
+      <c r="GI1" s="19"/>
+      <c r="GJ1" s="19"/>
+      <c r="GK1" s="19"/>
+      <c r="GL1" s="19"/>
+      <c r="GM1" s="19"/>
+      <c r="GN1" s="19"/>
+      <c r="GO1" s="19"/>
+      <c r="GP1" s="19"/>
+      <c r="GQ1" s="19"/>
+      <c r="GR1" s="19"/>
+      <c r="GS1" s="19"/>
+      <c r="GT1" s="19"/>
+      <c r="GU1" s="19"/>
+      <c r="GV1" s="19"/>
+      <c r="GW1" s="19"/>
+      <c r="GX1" s="19"/>
+      <c r="GY1" s="19"/>
+      <c r="GZ1" s="19"/>
+      <c r="HA1" s="19"/>
+      <c r="HB1" s="19"/>
+      <c r="HC1" s="19"/>
+      <c r="HD1" s="19"/>
+      <c r="HE1" s="19"/>
+      <c r="HF1" s="19"/>
+      <c r="HG1" s="19"/>
+      <c r="HH1" s="19"/>
+      <c r="HI1" s="19"/>
+      <c r="HJ1" s="19"/>
+      <c r="HK1" s="19"/>
+      <c r="HL1" s="19"/>
+      <c r="HM1" s="19"/>
+      <c r="HN1" s="19"/>
+      <c r="HO1" s="19"/>
+      <c r="HP1" s="19"/>
+      <c r="HQ1" s="19"/>
+      <c r="HR1" s="19"/>
+      <c r="HS1" s="19"/>
+      <c r="HT1" s="19"/>
+      <c r="HU1" s="19"/>
+      <c r="HV1" s="19"/>
+      <c r="HW1" s="19"/>
+      <c r="HX1" s="19"/>
+      <c r="HY1" s="19"/>
+      <c r="HZ1" s="19"/>
+      <c r="IA1" s="19"/>
+      <c r="IB1" s="19"/>
+      <c r="IC1" s="19"/>
+      <c r="ID1" s="19"/>
+      <c r="IE1" s="19"/>
+      <c r="IF1" s="19"/>
+      <c r="IG1" s="19"/>
+      <c r="IH1" s="19"/>
+      <c r="II1" s="19"/>
+      <c r="IJ1" s="19"/>
+      <c r="IK1" s="19"/>
+      <c r="IL1" s="19"/>
+      <c r="IM1" s="19"/>
+      <c r="IN1" s="19"/>
+      <c r="IO1" s="19"/>
+      <c r="IP1" s="19"/>
+      <c r="IQ1" s="19"/>
+      <c r="IR1" s="19"/>
+      <c r="IS1" s="19"/>
+      <c r="IT1" s="19"/>
+      <c r="IU1" s="19"/>
+      <c r="IV1" s="19"/>
+      <c r="IW1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9"/>
@@ -1888,7 +2115,7 @@
       <c r="Z3" s="24"/>
       <c r="AA3" s="25"/>
     </row>
-    <row r="4" s="31" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="20"/>
@@ -1945,8 +2172,236 @@
         <f aca="false">[1]Admin!$G$6</f>
         <v>0.06</v>
       </c>
-    </row>
-    <row r="5" s="31" customFormat="true" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="31"/>
+      <c r="AH4" s="31"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="31"/>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="31"/>
+      <c r="AN4" s="31"/>
+      <c r="AO4" s="31"/>
+      <c r="AP4" s="31"/>
+      <c r="AQ4" s="31"/>
+      <c r="AR4" s="31"/>
+      <c r="AS4" s="31"/>
+      <c r="AT4" s="31"/>
+      <c r="AU4" s="31"/>
+      <c r="AV4" s="31"/>
+      <c r="AW4" s="31"/>
+      <c r="AX4" s="31"/>
+      <c r="AY4" s="31"/>
+      <c r="AZ4" s="31"/>
+      <c r="BA4" s="31"/>
+      <c r="BB4" s="31"/>
+      <c r="BC4" s="31"/>
+      <c r="BD4" s="31"/>
+      <c r="BE4" s="31"/>
+      <c r="BF4" s="31"/>
+      <c r="BG4" s="31"/>
+      <c r="BH4" s="31"/>
+      <c r="BI4" s="31"/>
+      <c r="BJ4" s="31"/>
+      <c r="BK4" s="31"/>
+      <c r="BL4" s="31"/>
+      <c r="BM4" s="31"/>
+      <c r="BN4" s="31"/>
+      <c r="BO4" s="31"/>
+      <c r="BP4" s="31"/>
+      <c r="BQ4" s="31"/>
+      <c r="BR4" s="31"/>
+      <c r="BS4" s="31"/>
+      <c r="BT4" s="31"/>
+      <c r="BU4" s="31"/>
+      <c r="BV4" s="31"/>
+      <c r="BW4" s="31"/>
+      <c r="BX4" s="31"/>
+      <c r="BY4" s="31"/>
+      <c r="BZ4" s="31"/>
+      <c r="CA4" s="31"/>
+      <c r="CB4" s="31"/>
+      <c r="CC4" s="31"/>
+      <c r="CD4" s="31"/>
+      <c r="CE4" s="31"/>
+      <c r="CF4" s="31"/>
+      <c r="CG4" s="31"/>
+      <c r="CH4" s="31"/>
+      <c r="CI4" s="31"/>
+      <c r="CJ4" s="31"/>
+      <c r="CK4" s="31"/>
+      <c r="CL4" s="31"/>
+      <c r="CM4" s="31"/>
+      <c r="CN4" s="31"/>
+      <c r="CO4" s="31"/>
+      <c r="CP4" s="31"/>
+      <c r="CQ4" s="31"/>
+      <c r="CR4" s="31"/>
+      <c r="CS4" s="31"/>
+      <c r="CT4" s="31"/>
+      <c r="CU4" s="31"/>
+      <c r="CV4" s="31"/>
+      <c r="CW4" s="31"/>
+      <c r="CX4" s="31"/>
+      <c r="CY4" s="31"/>
+      <c r="CZ4" s="31"/>
+      <c r="DA4" s="31"/>
+      <c r="DB4" s="31"/>
+      <c r="DC4" s="31"/>
+      <c r="DD4" s="31"/>
+      <c r="DE4" s="31"/>
+      <c r="DF4" s="31"/>
+      <c r="DG4" s="31"/>
+      <c r="DH4" s="31"/>
+      <c r="DI4" s="31"/>
+      <c r="DJ4" s="31"/>
+      <c r="DK4" s="31"/>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="31"/>
+      <c r="DN4" s="31"/>
+      <c r="DO4" s="31"/>
+      <c r="DP4" s="31"/>
+      <c r="DQ4" s="31"/>
+      <c r="DR4" s="31"/>
+      <c r="DS4" s="31"/>
+      <c r="DT4" s="31"/>
+      <c r="DU4" s="31"/>
+      <c r="DV4" s="31"/>
+      <c r="DW4" s="31"/>
+      <c r="DX4" s="31"/>
+      <c r="DY4" s="31"/>
+      <c r="DZ4" s="31"/>
+      <c r="EA4" s="31"/>
+      <c r="EB4" s="31"/>
+      <c r="EC4" s="31"/>
+      <c r="ED4" s="31"/>
+      <c r="EE4" s="31"/>
+      <c r="EF4" s="31"/>
+      <c r="EG4" s="31"/>
+      <c r="EH4" s="31"/>
+      <c r="EI4" s="31"/>
+      <c r="EJ4" s="31"/>
+      <c r="EK4" s="31"/>
+      <c r="EL4" s="31"/>
+      <c r="EM4" s="31"/>
+      <c r="EN4" s="31"/>
+      <c r="EO4" s="31"/>
+      <c r="EP4" s="31"/>
+      <c r="EQ4" s="31"/>
+      <c r="ER4" s="31"/>
+      <c r="ES4" s="31"/>
+      <c r="ET4" s="31"/>
+      <c r="EU4" s="31"/>
+      <c r="EV4" s="31"/>
+      <c r="EW4" s="31"/>
+      <c r="EX4" s="31"/>
+      <c r="EY4" s="31"/>
+      <c r="EZ4" s="31"/>
+      <c r="FA4" s="31"/>
+      <c r="FB4" s="31"/>
+      <c r="FC4" s="31"/>
+      <c r="FD4" s="31"/>
+      <c r="FE4" s="31"/>
+      <c r="FF4" s="31"/>
+      <c r="FG4" s="31"/>
+      <c r="FH4" s="31"/>
+      <c r="FI4" s="31"/>
+      <c r="FJ4" s="31"/>
+      <c r="FK4" s="31"/>
+      <c r="FL4" s="31"/>
+      <c r="FM4" s="31"/>
+      <c r="FN4" s="31"/>
+      <c r="FO4" s="31"/>
+      <c r="FP4" s="31"/>
+      <c r="FQ4" s="31"/>
+      <c r="FR4" s="31"/>
+      <c r="FS4" s="31"/>
+      <c r="FT4" s="31"/>
+      <c r="FU4" s="31"/>
+      <c r="FV4" s="31"/>
+      <c r="FW4" s="31"/>
+      <c r="FX4" s="31"/>
+      <c r="FY4" s="31"/>
+      <c r="FZ4" s="31"/>
+      <c r="GA4" s="31"/>
+      <c r="GB4" s="31"/>
+      <c r="GC4" s="31"/>
+      <c r="GD4" s="31"/>
+      <c r="GE4" s="31"/>
+      <c r="GF4" s="31"/>
+      <c r="GG4" s="31"/>
+      <c r="GH4" s="31"/>
+      <c r="GI4" s="31"/>
+      <c r="GJ4" s="31"/>
+      <c r="GK4" s="31"/>
+      <c r="GL4" s="31"/>
+      <c r="GM4" s="31"/>
+      <c r="GN4" s="31"/>
+      <c r="GO4" s="31"/>
+      <c r="GP4" s="31"/>
+      <c r="GQ4" s="31"/>
+      <c r="GR4" s="31"/>
+      <c r="GS4" s="31"/>
+      <c r="GT4" s="31"/>
+      <c r="GU4" s="31"/>
+      <c r="GV4" s="31"/>
+      <c r="GW4" s="31"/>
+      <c r="GX4" s="31"/>
+      <c r="GY4" s="31"/>
+      <c r="GZ4" s="31"/>
+      <c r="HA4" s="31"/>
+      <c r="HB4" s="31"/>
+      <c r="HC4" s="31"/>
+      <c r="HD4" s="31"/>
+      <c r="HE4" s="31"/>
+      <c r="HF4" s="31"/>
+      <c r="HG4" s="31"/>
+      <c r="HH4" s="31"/>
+      <c r="HI4" s="31"/>
+      <c r="HJ4" s="31"/>
+      <c r="HK4" s="31"/>
+      <c r="HL4" s="31"/>
+      <c r="HM4" s="31"/>
+      <c r="HN4" s="31"/>
+      <c r="HO4" s="31"/>
+      <c r="HP4" s="31"/>
+      <c r="HQ4" s="31"/>
+      <c r="HR4" s="31"/>
+      <c r="HS4" s="31"/>
+      <c r="HT4" s="31"/>
+      <c r="HU4" s="31"/>
+      <c r="HV4" s="31"/>
+      <c r="HW4" s="31"/>
+      <c r="HX4" s="31"/>
+      <c r="HY4" s="31"/>
+      <c r="HZ4" s="31"/>
+      <c r="IA4" s="31"/>
+      <c r="IB4" s="31"/>
+      <c r="IC4" s="31"/>
+      <c r="ID4" s="31"/>
+      <c r="IE4" s="31"/>
+      <c r="IF4" s="31"/>
+      <c r="IG4" s="31"/>
+      <c r="IH4" s="31"/>
+      <c r="II4" s="31"/>
+      <c r="IJ4" s="31"/>
+      <c r="IK4" s="31"/>
+      <c r="IL4" s="31"/>
+      <c r="IM4" s="31"/>
+      <c r="IN4" s="31"/>
+      <c r="IO4" s="31"/>
+      <c r="IP4" s="31"/>
+      <c r="IQ4" s="31"/>
+      <c r="IR4" s="31"/>
+      <c r="IS4" s="31"/>
+      <c r="IT4" s="31"/>
+      <c r="IU4" s="31"/>
+      <c r="IV4" s="31"/>
+      <c r="IW4" s="31"/>
+    </row>
+    <row r="5" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="32"/>
       <c r="B5" s="33"/>
       <c r="C5" s="34"/>
@@ -1974,6 +2429,236 @@
       <c r="Y5" s="36"/>
       <c r="Z5" s="36"/>
       <c r="AA5" s="30"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="31"/>
+      <c r="BD5" s="31"/>
+      <c r="BE5" s="31"/>
+      <c r="BF5" s="31"/>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="31"/>
+      <c r="BI5" s="31"/>
+      <c r="BJ5" s="31"/>
+      <c r="BK5" s="31"/>
+      <c r="BL5" s="31"/>
+      <c r="BM5" s="31"/>
+      <c r="BN5" s="31"/>
+      <c r="BO5" s="31"/>
+      <c r="BP5" s="31"/>
+      <c r="BQ5" s="31"/>
+      <c r="BR5" s="31"/>
+      <c r="BS5" s="31"/>
+      <c r="BT5" s="31"/>
+      <c r="BU5" s="31"/>
+      <c r="BV5" s="31"/>
+      <c r="BW5" s="31"/>
+      <c r="BX5" s="31"/>
+      <c r="BY5" s="31"/>
+      <c r="BZ5" s="31"/>
+      <c r="CA5" s="31"/>
+      <c r="CB5" s="31"/>
+      <c r="CC5" s="31"/>
+      <c r="CD5" s="31"/>
+      <c r="CE5" s="31"/>
+      <c r="CF5" s="31"/>
+      <c r="CG5" s="31"/>
+      <c r="CH5" s="31"/>
+      <c r="CI5" s="31"/>
+      <c r="CJ5" s="31"/>
+      <c r="CK5" s="31"/>
+      <c r="CL5" s="31"/>
+      <c r="CM5" s="31"/>
+      <c r="CN5" s="31"/>
+      <c r="CO5" s="31"/>
+      <c r="CP5" s="31"/>
+      <c r="CQ5" s="31"/>
+      <c r="CR5" s="31"/>
+      <c r="CS5" s="31"/>
+      <c r="CT5" s="31"/>
+      <c r="CU5" s="31"/>
+      <c r="CV5" s="31"/>
+      <c r="CW5" s="31"/>
+      <c r="CX5" s="31"/>
+      <c r="CY5" s="31"/>
+      <c r="CZ5" s="31"/>
+      <c r="DA5" s="31"/>
+      <c r="DB5" s="31"/>
+      <c r="DC5" s="31"/>
+      <c r="DD5" s="31"/>
+      <c r="DE5" s="31"/>
+      <c r="DF5" s="31"/>
+      <c r="DG5" s="31"/>
+      <c r="DH5" s="31"/>
+      <c r="DI5" s="31"/>
+      <c r="DJ5" s="31"/>
+      <c r="DK5" s="31"/>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="31"/>
+      <c r="DN5" s="31"/>
+      <c r="DO5" s="31"/>
+      <c r="DP5" s="31"/>
+      <c r="DQ5" s="31"/>
+      <c r="DR5" s="31"/>
+      <c r="DS5" s="31"/>
+      <c r="DT5" s="31"/>
+      <c r="DU5" s="31"/>
+      <c r="DV5" s="31"/>
+      <c r="DW5" s="31"/>
+      <c r="DX5" s="31"/>
+      <c r="DY5" s="31"/>
+      <c r="DZ5" s="31"/>
+      <c r="EA5" s="31"/>
+      <c r="EB5" s="31"/>
+      <c r="EC5" s="31"/>
+      <c r="ED5" s="31"/>
+      <c r="EE5" s="31"/>
+      <c r="EF5" s="31"/>
+      <c r="EG5" s="31"/>
+      <c r="EH5" s="31"/>
+      <c r="EI5" s="31"/>
+      <c r="EJ5" s="31"/>
+      <c r="EK5" s="31"/>
+      <c r="EL5" s="31"/>
+      <c r="EM5" s="31"/>
+      <c r="EN5" s="31"/>
+      <c r="EO5" s="31"/>
+      <c r="EP5" s="31"/>
+      <c r="EQ5" s="31"/>
+      <c r="ER5" s="31"/>
+      <c r="ES5" s="31"/>
+      <c r="ET5" s="31"/>
+      <c r="EU5" s="31"/>
+      <c r="EV5" s="31"/>
+      <c r="EW5" s="31"/>
+      <c r="EX5" s="31"/>
+      <c r="EY5" s="31"/>
+      <c r="EZ5" s="31"/>
+      <c r="FA5" s="31"/>
+      <c r="FB5" s="31"/>
+      <c r="FC5" s="31"/>
+      <c r="FD5" s="31"/>
+      <c r="FE5" s="31"/>
+      <c r="FF5" s="31"/>
+      <c r="FG5" s="31"/>
+      <c r="FH5" s="31"/>
+      <c r="FI5" s="31"/>
+      <c r="FJ5" s="31"/>
+      <c r="FK5" s="31"/>
+      <c r="FL5" s="31"/>
+      <c r="FM5" s="31"/>
+      <c r="FN5" s="31"/>
+      <c r="FO5" s="31"/>
+      <c r="FP5" s="31"/>
+      <c r="FQ5" s="31"/>
+      <c r="FR5" s="31"/>
+      <c r="FS5" s="31"/>
+      <c r="FT5" s="31"/>
+      <c r="FU5" s="31"/>
+      <c r="FV5" s="31"/>
+      <c r="FW5" s="31"/>
+      <c r="FX5" s="31"/>
+      <c r="FY5" s="31"/>
+      <c r="FZ5" s="31"/>
+      <c r="GA5" s="31"/>
+      <c r="GB5" s="31"/>
+      <c r="GC5" s="31"/>
+      <c r="GD5" s="31"/>
+      <c r="GE5" s="31"/>
+      <c r="GF5" s="31"/>
+      <c r="GG5" s="31"/>
+      <c r="GH5" s="31"/>
+      <c r="GI5" s="31"/>
+      <c r="GJ5" s="31"/>
+      <c r="GK5" s="31"/>
+      <c r="GL5" s="31"/>
+      <c r="GM5" s="31"/>
+      <c r="GN5" s="31"/>
+      <c r="GO5" s="31"/>
+      <c r="GP5" s="31"/>
+      <c r="GQ5" s="31"/>
+      <c r="GR5" s="31"/>
+      <c r="GS5" s="31"/>
+      <c r="GT5" s="31"/>
+      <c r="GU5" s="31"/>
+      <c r="GV5" s="31"/>
+      <c r="GW5" s="31"/>
+      <c r="GX5" s="31"/>
+      <c r="GY5" s="31"/>
+      <c r="GZ5" s="31"/>
+      <c r="HA5" s="31"/>
+      <c r="HB5" s="31"/>
+      <c r="HC5" s="31"/>
+      <c r="HD5" s="31"/>
+      <c r="HE5" s="31"/>
+      <c r="HF5" s="31"/>
+      <c r="HG5" s="31"/>
+      <c r="HH5" s="31"/>
+      <c r="HI5" s="31"/>
+      <c r="HJ5" s="31"/>
+      <c r="HK5" s="31"/>
+      <c r="HL5" s="31"/>
+      <c r="HM5" s="31"/>
+      <c r="HN5" s="31"/>
+      <c r="HO5" s="31"/>
+      <c r="HP5" s="31"/>
+      <c r="HQ5" s="31"/>
+      <c r="HR5" s="31"/>
+      <c r="HS5" s="31"/>
+      <c r="HT5" s="31"/>
+      <c r="HU5" s="31"/>
+      <c r="HV5" s="31"/>
+      <c r="HW5" s="31"/>
+      <c r="HX5" s="31"/>
+      <c r="HY5" s="31"/>
+      <c r="HZ5" s="31"/>
+      <c r="IA5" s="31"/>
+      <c r="IB5" s="31"/>
+      <c r="IC5" s="31"/>
+      <c r="ID5" s="31"/>
+      <c r="IE5" s="31"/>
+      <c r="IF5" s="31"/>
+      <c r="IG5" s="31"/>
+      <c r="IH5" s="31"/>
+      <c r="II5" s="31"/>
+      <c r="IJ5" s="31"/>
+      <c r="IK5" s="31"/>
+      <c r="IL5" s="31"/>
+      <c r="IM5" s="31"/>
+      <c r="IN5" s="31"/>
+      <c r="IO5" s="31"/>
+      <c r="IP5" s="31"/>
+      <c r="IQ5" s="31"/>
+      <c r="IR5" s="31"/>
+      <c r="IS5" s="31"/>
+      <c r="IT5" s="31"/>
+      <c r="IU5" s="31"/>
+      <c r="IV5" s="31"/>
+      <c r="IW5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43"/>
@@ -8229,8 +8914,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW16"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="95" width="1.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="95" width="27.15"/>
@@ -8247,7 +8932,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="95" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="96"/>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -8272,8 +8957,241 @@
       <c r="V1" s="5"/>
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
-    </row>
-    <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
+      <c r="CY1" s="1"/>
+      <c r="CZ1" s="1"/>
+      <c r="DA1" s="1"/>
+      <c r="DB1" s="1"/>
+      <c r="DC1" s="1"/>
+      <c r="DD1" s="1"/>
+      <c r="DE1" s="1"/>
+      <c r="DF1" s="1"/>
+      <c r="DG1" s="1"/>
+      <c r="DH1" s="1"/>
+      <c r="DI1" s="1"/>
+      <c r="DJ1" s="1"/>
+      <c r="DK1" s="1"/>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
+      <c r="DP1" s="1"/>
+      <c r="DQ1" s="1"/>
+      <c r="DR1" s="1"/>
+      <c r="DS1" s="1"/>
+      <c r="DT1" s="1"/>
+      <c r="DU1" s="1"/>
+      <c r="DV1" s="1"/>
+      <c r="DW1" s="1"/>
+      <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
+      <c r="DZ1" s="1"/>
+      <c r="EA1" s="1"/>
+      <c r="EB1" s="1"/>
+      <c r="EC1" s="1"/>
+      <c r="ED1" s="1"/>
+      <c r="EE1" s="1"/>
+      <c r="EF1" s="1"/>
+      <c r="EG1" s="1"/>
+      <c r="EH1" s="1"/>
+      <c r="EI1" s="1"/>
+      <c r="EJ1" s="1"/>
+      <c r="EK1" s="1"/>
+      <c r="EL1" s="1"/>
+      <c r="EM1" s="1"/>
+      <c r="EN1" s="1"/>
+      <c r="EO1" s="1"/>
+      <c r="EP1" s="1"/>
+      <c r="EQ1" s="1"/>
+      <c r="ER1" s="1"/>
+      <c r="ES1" s="1"/>
+      <c r="ET1" s="1"/>
+      <c r="EU1" s="1"/>
+      <c r="EV1" s="1"/>
+      <c r="EW1" s="1"/>
+      <c r="EX1" s="1"/>
+      <c r="EY1" s="1"/>
+      <c r="EZ1" s="1"/>
+      <c r="FA1" s="1"/>
+      <c r="FB1" s="1"/>
+      <c r="FC1" s="1"/>
+      <c r="FD1" s="1"/>
+      <c r="FE1" s="1"/>
+      <c r="FF1" s="1"/>
+      <c r="FG1" s="1"/>
+      <c r="FH1" s="1"/>
+      <c r="FI1" s="1"/>
+      <c r="FJ1" s="1"/>
+      <c r="FK1" s="1"/>
+      <c r="FL1" s="1"/>
+      <c r="FM1" s="1"/>
+      <c r="FN1" s="1"/>
+      <c r="FO1" s="1"/>
+      <c r="FP1" s="1"/>
+      <c r="FQ1" s="1"/>
+      <c r="FR1" s="1"/>
+      <c r="FS1" s="1"/>
+      <c r="FT1" s="1"/>
+      <c r="FU1" s="1"/>
+      <c r="FV1" s="1"/>
+      <c r="FW1" s="1"/>
+      <c r="FX1" s="1"/>
+      <c r="FY1" s="1"/>
+      <c r="FZ1" s="1"/>
+      <c r="GA1" s="1"/>
+      <c r="GB1" s="1"/>
+      <c r="GC1" s="1"/>
+      <c r="GD1" s="1"/>
+      <c r="GE1" s="1"/>
+      <c r="GF1" s="1"/>
+      <c r="GG1" s="1"/>
+      <c r="GH1" s="1"/>
+      <c r="GI1" s="1"/>
+      <c r="GJ1" s="1"/>
+      <c r="GK1" s="1"/>
+      <c r="GL1" s="1"/>
+      <c r="GM1" s="1"/>
+      <c r="GN1" s="1"/>
+      <c r="GO1" s="1"/>
+      <c r="GP1" s="1"/>
+      <c r="GQ1" s="1"/>
+      <c r="GR1" s="1"/>
+      <c r="GS1" s="1"/>
+      <c r="GT1" s="1"/>
+      <c r="GU1" s="1"/>
+      <c r="GV1" s="1"/>
+      <c r="GW1" s="1"/>
+      <c r="GX1" s="1"/>
+      <c r="GY1" s="1"/>
+      <c r="GZ1" s="1"/>
+      <c r="HA1" s="1"/>
+      <c r="HB1" s="1"/>
+      <c r="HC1" s="1"/>
+      <c r="HD1" s="1"/>
+      <c r="HE1" s="1"/>
+      <c r="HF1" s="1"/>
+      <c r="HG1" s="1"/>
+      <c r="HH1" s="1"/>
+      <c r="HI1" s="1"/>
+      <c r="HJ1" s="1"/>
+      <c r="HK1" s="1"/>
+      <c r="HL1" s="1"/>
+      <c r="HM1" s="1"/>
+      <c r="HN1" s="1"/>
+      <c r="HO1" s="1"/>
+      <c r="HP1" s="1"/>
+      <c r="HQ1" s="1"/>
+      <c r="HR1" s="1"/>
+      <c r="HS1" s="1"/>
+      <c r="HT1" s="1"/>
+      <c r="HU1" s="1"/>
+      <c r="HV1" s="1"/>
+      <c r="HW1" s="1"/>
+      <c r="HX1" s="1"/>
+      <c r="HY1" s="1"/>
+      <c r="HZ1" s="1"/>
+      <c r="IA1" s="1"/>
+      <c r="IB1" s="1"/>
+      <c r="IC1" s="1"/>
+      <c r="ID1" s="1"/>
+      <c r="IE1" s="1"/>
+      <c r="IF1" s="1"/>
+      <c r="IG1" s="1"/>
+      <c r="IH1" s="1"/>
+      <c r="II1" s="1"/>
+      <c r="IJ1" s="1"/>
+      <c r="IK1" s="1"/>
+      <c r="IL1" s="1"/>
+      <c r="IM1" s="1"/>
+      <c r="IN1" s="1"/>
+      <c r="IO1" s="1"/>
+      <c r="IP1" s="1"/>
+      <c r="IQ1" s="1"/>
+      <c r="IR1" s="1"/>
+      <c r="IS1" s="1"/>
+      <c r="IT1" s="1"/>
+      <c r="IU1" s="1"/>
+      <c r="IV1" s="1"/>
+      <c r="IW1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="98"/>
       <c r="B2" s="99"/>
       <c r="C2" s="100"/>
@@ -8300,8 +9218,241 @@
       <c r="V2" s="5"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
-    </row>
-    <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
+      <c r="CN2" s="1"/>
+      <c r="CO2" s="1"/>
+      <c r="CP2" s="1"/>
+      <c r="CQ2" s="1"/>
+      <c r="CR2" s="1"/>
+      <c r="CS2" s="1"/>
+      <c r="CT2" s="1"/>
+      <c r="CU2" s="1"/>
+      <c r="CV2" s="1"/>
+      <c r="CW2" s="1"/>
+      <c r="CX2" s="1"/>
+      <c r="CY2" s="1"/>
+      <c r="CZ2" s="1"/>
+      <c r="DA2" s="1"/>
+      <c r="DB2" s="1"/>
+      <c r="DC2" s="1"/>
+      <c r="DD2" s="1"/>
+      <c r="DE2" s="1"/>
+      <c r="DF2" s="1"/>
+      <c r="DG2" s="1"/>
+      <c r="DH2" s="1"/>
+      <c r="DI2" s="1"/>
+      <c r="DJ2" s="1"/>
+      <c r="DK2" s="1"/>
+      <c r="DL2" s="1"/>
+      <c r="DM2" s="1"/>
+      <c r="DN2" s="1"/>
+      <c r="DO2" s="1"/>
+      <c r="DP2" s="1"/>
+      <c r="DQ2" s="1"/>
+      <c r="DR2" s="1"/>
+      <c r="DS2" s="1"/>
+      <c r="DT2" s="1"/>
+      <c r="DU2" s="1"/>
+      <c r="DV2" s="1"/>
+      <c r="DW2" s="1"/>
+      <c r="DX2" s="1"/>
+      <c r="DY2" s="1"/>
+      <c r="DZ2" s="1"/>
+      <c r="EA2" s="1"/>
+      <c r="EB2" s="1"/>
+      <c r="EC2" s="1"/>
+      <c r="ED2" s="1"/>
+      <c r="EE2" s="1"/>
+      <c r="EF2" s="1"/>
+      <c r="EG2" s="1"/>
+      <c r="EH2" s="1"/>
+      <c r="EI2" s="1"/>
+      <c r="EJ2" s="1"/>
+      <c r="EK2" s="1"/>
+      <c r="EL2" s="1"/>
+      <c r="EM2" s="1"/>
+      <c r="EN2" s="1"/>
+      <c r="EO2" s="1"/>
+      <c r="EP2" s="1"/>
+      <c r="EQ2" s="1"/>
+      <c r="ER2" s="1"/>
+      <c r="ES2" s="1"/>
+      <c r="ET2" s="1"/>
+      <c r="EU2" s="1"/>
+      <c r="EV2" s="1"/>
+      <c r="EW2" s="1"/>
+      <c r="EX2" s="1"/>
+      <c r="EY2" s="1"/>
+      <c r="EZ2" s="1"/>
+      <c r="FA2" s="1"/>
+      <c r="FB2" s="1"/>
+      <c r="FC2" s="1"/>
+      <c r="FD2" s="1"/>
+      <c r="FE2" s="1"/>
+      <c r="FF2" s="1"/>
+      <c r="FG2" s="1"/>
+      <c r="FH2" s="1"/>
+      <c r="FI2" s="1"/>
+      <c r="FJ2" s="1"/>
+      <c r="FK2" s="1"/>
+      <c r="FL2" s="1"/>
+      <c r="FM2" s="1"/>
+      <c r="FN2" s="1"/>
+      <c r="FO2" s="1"/>
+      <c r="FP2" s="1"/>
+      <c r="FQ2" s="1"/>
+      <c r="FR2" s="1"/>
+      <c r="FS2" s="1"/>
+      <c r="FT2" s="1"/>
+      <c r="FU2" s="1"/>
+      <c r="FV2" s="1"/>
+      <c r="FW2" s="1"/>
+      <c r="FX2" s="1"/>
+      <c r="FY2" s="1"/>
+      <c r="FZ2" s="1"/>
+      <c r="GA2" s="1"/>
+      <c r="GB2" s="1"/>
+      <c r="GC2" s="1"/>
+      <c r="GD2" s="1"/>
+      <c r="GE2" s="1"/>
+      <c r="GF2" s="1"/>
+      <c r="GG2" s="1"/>
+      <c r="GH2" s="1"/>
+      <c r="GI2" s="1"/>
+      <c r="GJ2" s="1"/>
+      <c r="GK2" s="1"/>
+      <c r="GL2" s="1"/>
+      <c r="GM2" s="1"/>
+      <c r="GN2" s="1"/>
+      <c r="GO2" s="1"/>
+      <c r="GP2" s="1"/>
+      <c r="GQ2" s="1"/>
+      <c r="GR2" s="1"/>
+      <c r="GS2" s="1"/>
+      <c r="GT2" s="1"/>
+      <c r="GU2" s="1"/>
+      <c r="GV2" s="1"/>
+      <c r="GW2" s="1"/>
+      <c r="GX2" s="1"/>
+      <c r="GY2" s="1"/>
+      <c r="GZ2" s="1"/>
+      <c r="HA2" s="1"/>
+      <c r="HB2" s="1"/>
+      <c r="HC2" s="1"/>
+      <c r="HD2" s="1"/>
+      <c r="HE2" s="1"/>
+      <c r="HF2" s="1"/>
+      <c r="HG2" s="1"/>
+      <c r="HH2" s="1"/>
+      <c r="HI2" s="1"/>
+      <c r="HJ2" s="1"/>
+      <c r="HK2" s="1"/>
+      <c r="HL2" s="1"/>
+      <c r="HM2" s="1"/>
+      <c r="HN2" s="1"/>
+      <c r="HO2" s="1"/>
+      <c r="HP2" s="1"/>
+      <c r="HQ2" s="1"/>
+      <c r="HR2" s="1"/>
+      <c r="HS2" s="1"/>
+      <c r="HT2" s="1"/>
+      <c r="HU2" s="1"/>
+      <c r="HV2" s="1"/>
+      <c r="HW2" s="1"/>
+      <c r="HX2" s="1"/>
+      <c r="HY2" s="1"/>
+      <c r="HZ2" s="1"/>
+      <c r="IA2" s="1"/>
+      <c r="IB2" s="1"/>
+      <c r="IC2" s="1"/>
+      <c r="ID2" s="1"/>
+      <c r="IE2" s="1"/>
+      <c r="IF2" s="1"/>
+      <c r="IG2" s="1"/>
+      <c r="IH2" s="1"/>
+      <c r="II2" s="1"/>
+      <c r="IJ2" s="1"/>
+      <c r="IK2" s="1"/>
+      <c r="IL2" s="1"/>
+      <c r="IM2" s="1"/>
+      <c r="IN2" s="1"/>
+      <c r="IO2" s="1"/>
+      <c r="IP2" s="1"/>
+      <c r="IQ2" s="1"/>
+      <c r="IR2" s="1"/>
+      <c r="IS2" s="1"/>
+      <c r="IT2" s="1"/>
+      <c r="IU2" s="1"/>
+      <c r="IV2" s="1"/>
+      <c r="IW2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="98"/>
       <c r="B3" s="99"/>
       <c r="C3" s="100"/>
@@ -8326,8 +9477,241 @@
       <c r="V3" s="5"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
-    </row>
-    <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1"/>
+      <c r="BT3" s="1"/>
+      <c r="BU3" s="1"/>
+      <c r="BV3" s="1"/>
+      <c r="BW3" s="1"/>
+      <c r="BX3" s="1"/>
+      <c r="BY3" s="1"/>
+      <c r="BZ3" s="1"/>
+      <c r="CA3" s="1"/>
+      <c r="CB3" s="1"/>
+      <c r="CC3" s="1"/>
+      <c r="CD3" s="1"/>
+      <c r="CE3" s="1"/>
+      <c r="CF3" s="1"/>
+      <c r="CG3" s="1"/>
+      <c r="CH3" s="1"/>
+      <c r="CI3" s="1"/>
+      <c r="CJ3" s="1"/>
+      <c r="CK3" s="1"/>
+      <c r="CL3" s="1"/>
+      <c r="CM3" s="1"/>
+      <c r="CN3" s="1"/>
+      <c r="CO3" s="1"/>
+      <c r="CP3" s="1"/>
+      <c r="CQ3" s="1"/>
+      <c r="CR3" s="1"/>
+      <c r="CS3" s="1"/>
+      <c r="CT3" s="1"/>
+      <c r="CU3" s="1"/>
+      <c r="CV3" s="1"/>
+      <c r="CW3" s="1"/>
+      <c r="CX3" s="1"/>
+      <c r="CY3" s="1"/>
+      <c r="CZ3" s="1"/>
+      <c r="DA3" s="1"/>
+      <c r="DB3" s="1"/>
+      <c r="DC3" s="1"/>
+      <c r="DD3" s="1"/>
+      <c r="DE3" s="1"/>
+      <c r="DF3" s="1"/>
+      <c r="DG3" s="1"/>
+      <c r="DH3" s="1"/>
+      <c r="DI3" s="1"/>
+      <c r="DJ3" s="1"/>
+      <c r="DK3" s="1"/>
+      <c r="DL3" s="1"/>
+      <c r="DM3" s="1"/>
+      <c r="DN3" s="1"/>
+      <c r="DO3" s="1"/>
+      <c r="DP3" s="1"/>
+      <c r="DQ3" s="1"/>
+      <c r="DR3" s="1"/>
+      <c r="DS3" s="1"/>
+      <c r="DT3" s="1"/>
+      <c r="DU3" s="1"/>
+      <c r="DV3" s="1"/>
+      <c r="DW3" s="1"/>
+      <c r="DX3" s="1"/>
+      <c r="DY3" s="1"/>
+      <c r="DZ3" s="1"/>
+      <c r="EA3" s="1"/>
+      <c r="EB3" s="1"/>
+      <c r="EC3" s="1"/>
+      <c r="ED3" s="1"/>
+      <c r="EE3" s="1"/>
+      <c r="EF3" s="1"/>
+      <c r="EG3" s="1"/>
+      <c r="EH3" s="1"/>
+      <c r="EI3" s="1"/>
+      <c r="EJ3" s="1"/>
+      <c r="EK3" s="1"/>
+      <c r="EL3" s="1"/>
+      <c r="EM3" s="1"/>
+      <c r="EN3" s="1"/>
+      <c r="EO3" s="1"/>
+      <c r="EP3" s="1"/>
+      <c r="EQ3" s="1"/>
+      <c r="ER3" s="1"/>
+      <c r="ES3" s="1"/>
+      <c r="ET3" s="1"/>
+      <c r="EU3" s="1"/>
+      <c r="EV3" s="1"/>
+      <c r="EW3" s="1"/>
+      <c r="EX3" s="1"/>
+      <c r="EY3" s="1"/>
+      <c r="EZ3" s="1"/>
+      <c r="FA3" s="1"/>
+      <c r="FB3" s="1"/>
+      <c r="FC3" s="1"/>
+      <c r="FD3" s="1"/>
+      <c r="FE3" s="1"/>
+      <c r="FF3" s="1"/>
+      <c r="FG3" s="1"/>
+      <c r="FH3" s="1"/>
+      <c r="FI3" s="1"/>
+      <c r="FJ3" s="1"/>
+      <c r="FK3" s="1"/>
+      <c r="FL3" s="1"/>
+      <c r="FM3" s="1"/>
+      <c r="FN3" s="1"/>
+      <c r="FO3" s="1"/>
+      <c r="FP3" s="1"/>
+      <c r="FQ3" s="1"/>
+      <c r="FR3" s="1"/>
+      <c r="FS3" s="1"/>
+      <c r="FT3" s="1"/>
+      <c r="FU3" s="1"/>
+      <c r="FV3" s="1"/>
+      <c r="FW3" s="1"/>
+      <c r="FX3" s="1"/>
+      <c r="FY3" s="1"/>
+      <c r="FZ3" s="1"/>
+      <c r="GA3" s="1"/>
+      <c r="GB3" s="1"/>
+      <c r="GC3" s="1"/>
+      <c r="GD3" s="1"/>
+      <c r="GE3" s="1"/>
+      <c r="GF3" s="1"/>
+      <c r="GG3" s="1"/>
+      <c r="GH3" s="1"/>
+      <c r="GI3" s="1"/>
+      <c r="GJ3" s="1"/>
+      <c r="GK3" s="1"/>
+      <c r="GL3" s="1"/>
+      <c r="GM3" s="1"/>
+      <c r="GN3" s="1"/>
+      <c r="GO3" s="1"/>
+      <c r="GP3" s="1"/>
+      <c r="GQ3" s="1"/>
+      <c r="GR3" s="1"/>
+      <c r="GS3" s="1"/>
+      <c r="GT3" s="1"/>
+      <c r="GU3" s="1"/>
+      <c r="GV3" s="1"/>
+      <c r="GW3" s="1"/>
+      <c r="GX3" s="1"/>
+      <c r="GY3" s="1"/>
+      <c r="GZ3" s="1"/>
+      <c r="HA3" s="1"/>
+      <c r="HB3" s="1"/>
+      <c r="HC3" s="1"/>
+      <c r="HD3" s="1"/>
+      <c r="HE3" s="1"/>
+      <c r="HF3" s="1"/>
+      <c r="HG3" s="1"/>
+      <c r="HH3" s="1"/>
+      <c r="HI3" s="1"/>
+      <c r="HJ3" s="1"/>
+      <c r="HK3" s="1"/>
+      <c r="HL3" s="1"/>
+      <c r="HM3" s="1"/>
+      <c r="HN3" s="1"/>
+      <c r="HO3" s="1"/>
+      <c r="HP3" s="1"/>
+      <c r="HQ3" s="1"/>
+      <c r="HR3" s="1"/>
+      <c r="HS3" s="1"/>
+      <c r="HT3" s="1"/>
+      <c r="HU3" s="1"/>
+      <c r="HV3" s="1"/>
+      <c r="HW3" s="1"/>
+      <c r="HX3" s="1"/>
+      <c r="HY3" s="1"/>
+      <c r="HZ3" s="1"/>
+      <c r="IA3" s="1"/>
+      <c r="IB3" s="1"/>
+      <c r="IC3" s="1"/>
+      <c r="ID3" s="1"/>
+      <c r="IE3" s="1"/>
+      <c r="IF3" s="1"/>
+      <c r="IG3" s="1"/>
+      <c r="IH3" s="1"/>
+      <c r="II3" s="1"/>
+      <c r="IJ3" s="1"/>
+      <c r="IK3" s="1"/>
+      <c r="IL3" s="1"/>
+      <c r="IM3" s="1"/>
+      <c r="IN3" s="1"/>
+      <c r="IO3" s="1"/>
+      <c r="IP3" s="1"/>
+      <c r="IQ3" s="1"/>
+      <c r="IR3" s="1"/>
+      <c r="IS3" s="1"/>
+      <c r="IT3" s="1"/>
+      <c r="IU3" s="1"/>
+      <c r="IV3" s="1"/>
+      <c r="IW3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="98"/>
       <c r="B4" s="108" t="s">
         <v>52</v>
@@ -8362,8 +9746,241 @@
       <c r="V4" s="5"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
-    </row>
-    <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1"/>
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="1"/>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1"/>
+      <c r="AW4" s="1"/>
+      <c r="AX4" s="1"/>
+      <c r="AY4" s="1"/>
+      <c r="AZ4" s="1"/>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1"/>
+      <c r="BC4" s="1"/>
+      <c r="BD4" s="1"/>
+      <c r="BE4" s="1"/>
+      <c r="BF4" s="1"/>
+      <c r="BG4" s="1"/>
+      <c r="BH4" s="1"/>
+      <c r="BI4" s="1"/>
+      <c r="BJ4" s="1"/>
+      <c r="BK4" s="1"/>
+      <c r="BL4" s="1"/>
+      <c r="BM4" s="1"/>
+      <c r="BN4" s="1"/>
+      <c r="BO4" s="1"/>
+      <c r="BP4" s="1"/>
+      <c r="BQ4" s="1"/>
+      <c r="BR4" s="1"/>
+      <c r="BS4" s="1"/>
+      <c r="BT4" s="1"/>
+      <c r="BU4" s="1"/>
+      <c r="BV4" s="1"/>
+      <c r="BW4" s="1"/>
+      <c r="BX4" s="1"/>
+      <c r="BY4" s="1"/>
+      <c r="BZ4" s="1"/>
+      <c r="CA4" s="1"/>
+      <c r="CB4" s="1"/>
+      <c r="CC4" s="1"/>
+      <c r="CD4" s="1"/>
+      <c r="CE4" s="1"/>
+      <c r="CF4" s="1"/>
+      <c r="CG4" s="1"/>
+      <c r="CH4" s="1"/>
+      <c r="CI4" s="1"/>
+      <c r="CJ4" s="1"/>
+      <c r="CK4" s="1"/>
+      <c r="CL4" s="1"/>
+      <c r="CM4" s="1"/>
+      <c r="CN4" s="1"/>
+      <c r="CO4" s="1"/>
+      <c r="CP4" s="1"/>
+      <c r="CQ4" s="1"/>
+      <c r="CR4" s="1"/>
+      <c r="CS4" s="1"/>
+      <c r="CT4" s="1"/>
+      <c r="CU4" s="1"/>
+      <c r="CV4" s="1"/>
+      <c r="CW4" s="1"/>
+      <c r="CX4" s="1"/>
+      <c r="CY4" s="1"/>
+      <c r="CZ4" s="1"/>
+      <c r="DA4" s="1"/>
+      <c r="DB4" s="1"/>
+      <c r="DC4" s="1"/>
+      <c r="DD4" s="1"/>
+      <c r="DE4" s="1"/>
+      <c r="DF4" s="1"/>
+      <c r="DG4" s="1"/>
+      <c r="DH4" s="1"/>
+      <c r="DI4" s="1"/>
+      <c r="DJ4" s="1"/>
+      <c r="DK4" s="1"/>
+      <c r="DL4" s="1"/>
+      <c r="DM4" s="1"/>
+      <c r="DN4" s="1"/>
+      <c r="DO4" s="1"/>
+      <c r="DP4" s="1"/>
+      <c r="DQ4" s="1"/>
+      <c r="DR4" s="1"/>
+      <c r="DS4" s="1"/>
+      <c r="DT4" s="1"/>
+      <c r="DU4" s="1"/>
+      <c r="DV4" s="1"/>
+      <c r="DW4" s="1"/>
+      <c r="DX4" s="1"/>
+      <c r="DY4" s="1"/>
+      <c r="DZ4" s="1"/>
+      <c r="EA4" s="1"/>
+      <c r="EB4" s="1"/>
+      <c r="EC4" s="1"/>
+      <c r="ED4" s="1"/>
+      <c r="EE4" s="1"/>
+      <c r="EF4" s="1"/>
+      <c r="EG4" s="1"/>
+      <c r="EH4" s="1"/>
+      <c r="EI4" s="1"/>
+      <c r="EJ4" s="1"/>
+      <c r="EK4" s="1"/>
+      <c r="EL4" s="1"/>
+      <c r="EM4" s="1"/>
+      <c r="EN4" s="1"/>
+      <c r="EO4" s="1"/>
+      <c r="EP4" s="1"/>
+      <c r="EQ4" s="1"/>
+      <c r="ER4" s="1"/>
+      <c r="ES4" s="1"/>
+      <c r="ET4" s="1"/>
+      <c r="EU4" s="1"/>
+      <c r="EV4" s="1"/>
+      <c r="EW4" s="1"/>
+      <c r="EX4" s="1"/>
+      <c r="EY4" s="1"/>
+      <c r="EZ4" s="1"/>
+      <c r="FA4" s="1"/>
+      <c r="FB4" s="1"/>
+      <c r="FC4" s="1"/>
+      <c r="FD4" s="1"/>
+      <c r="FE4" s="1"/>
+      <c r="FF4" s="1"/>
+      <c r="FG4" s="1"/>
+      <c r="FH4" s="1"/>
+      <c r="FI4" s="1"/>
+      <c r="FJ4" s="1"/>
+      <c r="FK4" s="1"/>
+      <c r="FL4" s="1"/>
+      <c r="FM4" s="1"/>
+      <c r="FN4" s="1"/>
+      <c r="FO4" s="1"/>
+      <c r="FP4" s="1"/>
+      <c r="FQ4" s="1"/>
+      <c r="FR4" s="1"/>
+      <c r="FS4" s="1"/>
+      <c r="FT4" s="1"/>
+      <c r="FU4" s="1"/>
+      <c r="FV4" s="1"/>
+      <c r="FW4" s="1"/>
+      <c r="FX4" s="1"/>
+      <c r="FY4" s="1"/>
+      <c r="FZ4" s="1"/>
+      <c r="GA4" s="1"/>
+      <c r="GB4" s="1"/>
+      <c r="GC4" s="1"/>
+      <c r="GD4" s="1"/>
+      <c r="GE4" s="1"/>
+      <c r="GF4" s="1"/>
+      <c r="GG4" s="1"/>
+      <c r="GH4" s="1"/>
+      <c r="GI4" s="1"/>
+      <c r="GJ4" s="1"/>
+      <c r="GK4" s="1"/>
+      <c r="GL4" s="1"/>
+      <c r="GM4" s="1"/>
+      <c r="GN4" s="1"/>
+      <c r="GO4" s="1"/>
+      <c r="GP4" s="1"/>
+      <c r="GQ4" s="1"/>
+      <c r="GR4" s="1"/>
+      <c r="GS4" s="1"/>
+      <c r="GT4" s="1"/>
+      <c r="GU4" s="1"/>
+      <c r="GV4" s="1"/>
+      <c r="GW4" s="1"/>
+      <c r="GX4" s="1"/>
+      <c r="GY4" s="1"/>
+      <c r="GZ4" s="1"/>
+      <c r="HA4" s="1"/>
+      <c r="HB4" s="1"/>
+      <c r="HC4" s="1"/>
+      <c r="HD4" s="1"/>
+      <c r="HE4" s="1"/>
+      <c r="HF4" s="1"/>
+      <c r="HG4" s="1"/>
+      <c r="HH4" s="1"/>
+      <c r="HI4" s="1"/>
+      <c r="HJ4" s="1"/>
+      <c r="HK4" s="1"/>
+      <c r="HL4" s="1"/>
+      <c r="HM4" s="1"/>
+      <c r="HN4" s="1"/>
+      <c r="HO4" s="1"/>
+      <c r="HP4" s="1"/>
+      <c r="HQ4" s="1"/>
+      <c r="HR4" s="1"/>
+      <c r="HS4" s="1"/>
+      <c r="HT4" s="1"/>
+      <c r="HU4" s="1"/>
+      <c r="HV4" s="1"/>
+      <c r="HW4" s="1"/>
+      <c r="HX4" s="1"/>
+      <c r="HY4" s="1"/>
+      <c r="HZ4" s="1"/>
+      <c r="IA4" s="1"/>
+      <c r="IB4" s="1"/>
+      <c r="IC4" s="1"/>
+      <c r="ID4" s="1"/>
+      <c r="IE4" s="1"/>
+      <c r="IF4" s="1"/>
+      <c r="IG4" s="1"/>
+      <c r="IH4" s="1"/>
+      <c r="II4" s="1"/>
+      <c r="IJ4" s="1"/>
+      <c r="IK4" s="1"/>
+      <c r="IL4" s="1"/>
+      <c r="IM4" s="1"/>
+      <c r="IN4" s="1"/>
+      <c r="IO4" s="1"/>
+      <c r="IP4" s="1"/>
+      <c r="IQ4" s="1"/>
+      <c r="IR4" s="1"/>
+      <c r="IS4" s="1"/>
+      <c r="IT4" s="1"/>
+      <c r="IU4" s="1"/>
+      <c r="IV4" s="1"/>
+      <c r="IW4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="98"/>
       <c r="B5" s="99" t="s">
         <v>56</v>
@@ -8392,8 +10009,241 @@
       <c r="V5" s="5"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
+      <c r="BE5" s="1"/>
+      <c r="BF5" s="1"/>
+      <c r="BG5" s="1"/>
+      <c r="BH5" s="1"/>
+      <c r="BI5" s="1"/>
+      <c r="BJ5" s="1"/>
+      <c r="BK5" s="1"/>
+      <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
+      <c r="BN5" s="1"/>
+      <c r="BO5" s="1"/>
+      <c r="BP5" s="1"/>
+      <c r="BQ5" s="1"/>
+      <c r="BR5" s="1"/>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1"/>
+      <c r="BU5" s="1"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+      <c r="BX5" s="1"/>
+      <c r="BY5" s="1"/>
+      <c r="BZ5" s="1"/>
+      <c r="CA5" s="1"/>
+      <c r="CB5" s="1"/>
+      <c r="CC5" s="1"/>
+      <c r="CD5" s="1"/>
+      <c r="CE5" s="1"/>
+      <c r="CF5" s="1"/>
+      <c r="CG5" s="1"/>
+      <c r="CH5" s="1"/>
+      <c r="CI5" s="1"/>
+      <c r="CJ5" s="1"/>
+      <c r="CK5" s="1"/>
+      <c r="CL5" s="1"/>
+      <c r="CM5" s="1"/>
+      <c r="CN5" s="1"/>
+      <c r="CO5" s="1"/>
+      <c r="CP5" s="1"/>
+      <c r="CQ5" s="1"/>
+      <c r="CR5" s="1"/>
+      <c r="CS5" s="1"/>
+      <c r="CT5" s="1"/>
+      <c r="CU5" s="1"/>
+      <c r="CV5" s="1"/>
+      <c r="CW5" s="1"/>
+      <c r="CX5" s="1"/>
+      <c r="CY5" s="1"/>
+      <c r="CZ5" s="1"/>
+      <c r="DA5" s="1"/>
+      <c r="DB5" s="1"/>
+      <c r="DC5" s="1"/>
+      <c r="DD5" s="1"/>
+      <c r="DE5" s="1"/>
+      <c r="DF5" s="1"/>
+      <c r="DG5" s="1"/>
+      <c r="DH5" s="1"/>
+      <c r="DI5" s="1"/>
+      <c r="DJ5" s="1"/>
+      <c r="DK5" s="1"/>
+      <c r="DL5" s="1"/>
+      <c r="DM5" s="1"/>
+      <c r="DN5" s="1"/>
+      <c r="DO5" s="1"/>
+      <c r="DP5" s="1"/>
+      <c r="DQ5" s="1"/>
+      <c r="DR5" s="1"/>
+      <c r="DS5" s="1"/>
+      <c r="DT5" s="1"/>
+      <c r="DU5" s="1"/>
+      <c r="DV5" s="1"/>
+      <c r="DW5" s="1"/>
+      <c r="DX5" s="1"/>
+      <c r="DY5" s="1"/>
+      <c r="DZ5" s="1"/>
+      <c r="EA5" s="1"/>
+      <c r="EB5" s="1"/>
+      <c r="EC5" s="1"/>
+      <c r="ED5" s="1"/>
+      <c r="EE5" s="1"/>
+      <c r="EF5" s="1"/>
+      <c r="EG5" s="1"/>
+      <c r="EH5" s="1"/>
+      <c r="EI5" s="1"/>
+      <c r="EJ5" s="1"/>
+      <c r="EK5" s="1"/>
+      <c r="EL5" s="1"/>
+      <c r="EM5" s="1"/>
+      <c r="EN5" s="1"/>
+      <c r="EO5" s="1"/>
+      <c r="EP5" s="1"/>
+      <c r="EQ5" s="1"/>
+      <c r="ER5" s="1"/>
+      <c r="ES5" s="1"/>
+      <c r="ET5" s="1"/>
+      <c r="EU5" s="1"/>
+      <c r="EV5" s="1"/>
+      <c r="EW5" s="1"/>
+      <c r="EX5" s="1"/>
+      <c r="EY5" s="1"/>
+      <c r="EZ5" s="1"/>
+      <c r="FA5" s="1"/>
+      <c r="FB5" s="1"/>
+      <c r="FC5" s="1"/>
+      <c r="FD5" s="1"/>
+      <c r="FE5" s="1"/>
+      <c r="FF5" s="1"/>
+      <c r="FG5" s="1"/>
+      <c r="FH5" s="1"/>
+      <c r="FI5" s="1"/>
+      <c r="FJ5" s="1"/>
+      <c r="FK5" s="1"/>
+      <c r="FL5" s="1"/>
+      <c r="FM5" s="1"/>
+      <c r="FN5" s="1"/>
+      <c r="FO5" s="1"/>
+      <c r="FP5" s="1"/>
+      <c r="FQ5" s="1"/>
+      <c r="FR5" s="1"/>
+      <c r="FS5" s="1"/>
+      <c r="FT5" s="1"/>
+      <c r="FU5" s="1"/>
+      <c r="FV5" s="1"/>
+      <c r="FW5" s="1"/>
+      <c r="FX5" s="1"/>
+      <c r="FY5" s="1"/>
+      <c r="FZ5" s="1"/>
+      <c r="GA5" s="1"/>
+      <c r="GB5" s="1"/>
+      <c r="GC5" s="1"/>
+      <c r="GD5" s="1"/>
+      <c r="GE5" s="1"/>
+      <c r="GF5" s="1"/>
+      <c r="GG5" s="1"/>
+      <c r="GH5" s="1"/>
+      <c r="GI5" s="1"/>
+      <c r="GJ5" s="1"/>
+      <c r="GK5" s="1"/>
+      <c r="GL5" s="1"/>
+      <c r="GM5" s="1"/>
+      <c r="GN5" s="1"/>
+      <c r="GO5" s="1"/>
+      <c r="GP5" s="1"/>
+      <c r="GQ5" s="1"/>
+      <c r="GR5" s="1"/>
+      <c r="GS5" s="1"/>
+      <c r="GT5" s="1"/>
+      <c r="GU5" s="1"/>
+      <c r="GV5" s="1"/>
+      <c r="GW5" s="1"/>
+      <c r="GX5" s="1"/>
+      <c r="GY5" s="1"/>
+      <c r="GZ5" s="1"/>
+      <c r="HA5" s="1"/>
+      <c r="HB5" s="1"/>
+      <c r="HC5" s="1"/>
+      <c r="HD5" s="1"/>
+      <c r="HE5" s="1"/>
+      <c r="HF5" s="1"/>
+      <c r="HG5" s="1"/>
+      <c r="HH5" s="1"/>
+      <c r="HI5" s="1"/>
+      <c r="HJ5" s="1"/>
+      <c r="HK5" s="1"/>
+      <c r="HL5" s="1"/>
+      <c r="HM5" s="1"/>
+      <c r="HN5" s="1"/>
+      <c r="HO5" s="1"/>
+      <c r="HP5" s="1"/>
+      <c r="HQ5" s="1"/>
+      <c r="HR5" s="1"/>
+      <c r="HS5" s="1"/>
+      <c r="HT5" s="1"/>
+      <c r="HU5" s="1"/>
+      <c r="HV5" s="1"/>
+      <c r="HW5" s="1"/>
+      <c r="HX5" s="1"/>
+      <c r="HY5" s="1"/>
+      <c r="HZ5" s="1"/>
+      <c r="IA5" s="1"/>
+      <c r="IB5" s="1"/>
+      <c r="IC5" s="1"/>
+      <c r="ID5" s="1"/>
+      <c r="IE5" s="1"/>
+      <c r="IF5" s="1"/>
+      <c r="IG5" s="1"/>
+      <c r="IH5" s="1"/>
+      <c r="II5" s="1"/>
+      <c r="IJ5" s="1"/>
+      <c r="IK5" s="1"/>
+      <c r="IL5" s="1"/>
+      <c r="IM5" s="1"/>
+      <c r="IN5" s="1"/>
+      <c r="IO5" s="1"/>
+      <c r="IP5" s="1"/>
+      <c r="IQ5" s="1"/>
+      <c r="IR5" s="1"/>
+      <c r="IS5" s="1"/>
+      <c r="IT5" s="1"/>
+      <c r="IU5" s="1"/>
+      <c r="IV5" s="1"/>
+      <c r="IW5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="98"/>
       <c r="B6" s="112" t="s">
         <v>42</v>
@@ -8428,8 +10278,241 @@
       <c r="V6" s="5"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-    </row>
-    <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
+      <c r="BF6" s="1"/>
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1"/>
+      <c r="BJ6" s="1"/>
+      <c r="BK6" s="1"/>
+      <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="1"/>
+      <c r="BQ6" s="1"/>
+      <c r="BR6" s="1"/>
+      <c r="BS6" s="1"/>
+      <c r="BT6" s="1"/>
+      <c r="BU6" s="1"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BX6" s="1"/>
+      <c r="BY6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CA6" s="1"/>
+      <c r="CB6" s="1"/>
+      <c r="CC6" s="1"/>
+      <c r="CD6" s="1"/>
+      <c r="CE6" s="1"/>
+      <c r="CF6" s="1"/>
+      <c r="CG6" s="1"/>
+      <c r="CH6" s="1"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="1"/>
+      <c r="CK6" s="1"/>
+      <c r="CL6" s="1"/>
+      <c r="CM6" s="1"/>
+      <c r="CN6" s="1"/>
+      <c r="CO6" s="1"/>
+      <c r="CP6" s="1"/>
+      <c r="CQ6" s="1"/>
+      <c r="CR6" s="1"/>
+      <c r="CS6" s="1"/>
+      <c r="CT6" s="1"/>
+      <c r="CU6" s="1"/>
+      <c r="CV6" s="1"/>
+      <c r="CW6" s="1"/>
+      <c r="CX6" s="1"/>
+      <c r="CY6" s="1"/>
+      <c r="CZ6" s="1"/>
+      <c r="DA6" s="1"/>
+      <c r="DB6" s="1"/>
+      <c r="DC6" s="1"/>
+      <c r="DD6" s="1"/>
+      <c r="DE6" s="1"/>
+      <c r="DF6" s="1"/>
+      <c r="DG6" s="1"/>
+      <c r="DH6" s="1"/>
+      <c r="DI6" s="1"/>
+      <c r="DJ6" s="1"/>
+      <c r="DK6" s="1"/>
+      <c r="DL6" s="1"/>
+      <c r="DM6" s="1"/>
+      <c r="DN6" s="1"/>
+      <c r="DO6" s="1"/>
+      <c r="DP6" s="1"/>
+      <c r="DQ6" s="1"/>
+      <c r="DR6" s="1"/>
+      <c r="DS6" s="1"/>
+      <c r="DT6" s="1"/>
+      <c r="DU6" s="1"/>
+      <c r="DV6" s="1"/>
+      <c r="DW6" s="1"/>
+      <c r="DX6" s="1"/>
+      <c r="DY6" s="1"/>
+      <c r="DZ6" s="1"/>
+      <c r="EA6" s="1"/>
+      <c r="EB6" s="1"/>
+      <c r="EC6" s="1"/>
+      <c r="ED6" s="1"/>
+      <c r="EE6" s="1"/>
+      <c r="EF6" s="1"/>
+      <c r="EG6" s="1"/>
+      <c r="EH6" s="1"/>
+      <c r="EI6" s="1"/>
+      <c r="EJ6" s="1"/>
+      <c r="EK6" s="1"/>
+      <c r="EL6" s="1"/>
+      <c r="EM6" s="1"/>
+      <c r="EN6" s="1"/>
+      <c r="EO6" s="1"/>
+      <c r="EP6" s="1"/>
+      <c r="EQ6" s="1"/>
+      <c r="ER6" s="1"/>
+      <c r="ES6" s="1"/>
+      <c r="ET6" s="1"/>
+      <c r="EU6" s="1"/>
+      <c r="EV6" s="1"/>
+      <c r="EW6" s="1"/>
+      <c r="EX6" s="1"/>
+      <c r="EY6" s="1"/>
+      <c r="EZ6" s="1"/>
+      <c r="FA6" s="1"/>
+      <c r="FB6" s="1"/>
+      <c r="FC6" s="1"/>
+      <c r="FD6" s="1"/>
+      <c r="FE6" s="1"/>
+      <c r="FF6" s="1"/>
+      <c r="FG6" s="1"/>
+      <c r="FH6" s="1"/>
+      <c r="FI6" s="1"/>
+      <c r="FJ6" s="1"/>
+      <c r="FK6" s="1"/>
+      <c r="FL6" s="1"/>
+      <c r="FM6" s="1"/>
+      <c r="FN6" s="1"/>
+      <c r="FO6" s="1"/>
+      <c r="FP6" s="1"/>
+      <c r="FQ6" s="1"/>
+      <c r="FR6" s="1"/>
+      <c r="FS6" s="1"/>
+      <c r="FT6" s="1"/>
+      <c r="FU6" s="1"/>
+      <c r="FV6" s="1"/>
+      <c r="FW6" s="1"/>
+      <c r="FX6" s="1"/>
+      <c r="FY6" s="1"/>
+      <c r="FZ6" s="1"/>
+      <c r="GA6" s="1"/>
+      <c r="GB6" s="1"/>
+      <c r="GC6" s="1"/>
+      <c r="GD6" s="1"/>
+      <c r="GE6" s="1"/>
+      <c r="GF6" s="1"/>
+      <c r="GG6" s="1"/>
+      <c r="GH6" s="1"/>
+      <c r="GI6" s="1"/>
+      <c r="GJ6" s="1"/>
+      <c r="GK6" s="1"/>
+      <c r="GL6" s="1"/>
+      <c r="GM6" s="1"/>
+      <c r="GN6" s="1"/>
+      <c r="GO6" s="1"/>
+      <c r="GP6" s="1"/>
+      <c r="GQ6" s="1"/>
+      <c r="GR6" s="1"/>
+      <c r="GS6" s="1"/>
+      <c r="GT6" s="1"/>
+      <c r="GU6" s="1"/>
+      <c r="GV6" s="1"/>
+      <c r="GW6" s="1"/>
+      <c r="GX6" s="1"/>
+      <c r="GY6" s="1"/>
+      <c r="GZ6" s="1"/>
+      <c r="HA6" s="1"/>
+      <c r="HB6" s="1"/>
+      <c r="HC6" s="1"/>
+      <c r="HD6" s="1"/>
+      <c r="HE6" s="1"/>
+      <c r="HF6" s="1"/>
+      <c r="HG6" s="1"/>
+      <c r="HH6" s="1"/>
+      <c r="HI6" s="1"/>
+      <c r="HJ6" s="1"/>
+      <c r="HK6" s="1"/>
+      <c r="HL6" s="1"/>
+      <c r="HM6" s="1"/>
+      <c r="HN6" s="1"/>
+      <c r="HO6" s="1"/>
+      <c r="HP6" s="1"/>
+      <c r="HQ6" s="1"/>
+      <c r="HR6" s="1"/>
+      <c r="HS6" s="1"/>
+      <c r="HT6" s="1"/>
+      <c r="HU6" s="1"/>
+      <c r="HV6" s="1"/>
+      <c r="HW6" s="1"/>
+      <c r="HX6" s="1"/>
+      <c r="HY6" s="1"/>
+      <c r="HZ6" s="1"/>
+      <c r="IA6" s="1"/>
+      <c r="IB6" s="1"/>
+      <c r="IC6" s="1"/>
+      <c r="ID6" s="1"/>
+      <c r="IE6" s="1"/>
+      <c r="IF6" s="1"/>
+      <c r="IG6" s="1"/>
+      <c r="IH6" s="1"/>
+      <c r="II6" s="1"/>
+      <c r="IJ6" s="1"/>
+      <c r="IK6" s="1"/>
+      <c r="IL6" s="1"/>
+      <c r="IM6" s="1"/>
+      <c r="IN6" s="1"/>
+      <c r="IO6" s="1"/>
+      <c r="IP6" s="1"/>
+      <c r="IQ6" s="1"/>
+      <c r="IR6" s="1"/>
+      <c r="IS6" s="1"/>
+      <c r="IT6" s="1"/>
+      <c r="IU6" s="1"/>
+      <c r="IV6" s="1"/>
+      <c r="IW6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98"/>
       <c r="B7" s="112" t="s">
         <v>47</v>
@@ -8464,8 +10547,241 @@
       <c r="V7" s="5"/>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
-    </row>
-    <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="1"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="1"/>
+      <c r="BJ7" s="1"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="1"/>
+      <c r="BR7" s="1"/>
+      <c r="BS7" s="1"/>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BX7" s="1"/>
+      <c r="BY7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CA7" s="1"/>
+      <c r="CB7" s="1"/>
+      <c r="CC7" s="1"/>
+      <c r="CD7" s="1"/>
+      <c r="CE7" s="1"/>
+      <c r="CF7" s="1"/>
+      <c r="CG7" s="1"/>
+      <c r="CH7" s="1"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="1"/>
+      <c r="CK7" s="1"/>
+      <c r="CL7" s="1"/>
+      <c r="CM7" s="1"/>
+      <c r="CN7" s="1"/>
+      <c r="CO7" s="1"/>
+      <c r="CP7" s="1"/>
+      <c r="CQ7" s="1"/>
+      <c r="CR7" s="1"/>
+      <c r="CS7" s="1"/>
+      <c r="CT7" s="1"/>
+      <c r="CU7" s="1"/>
+      <c r="CV7" s="1"/>
+      <c r="CW7" s="1"/>
+      <c r="CX7" s="1"/>
+      <c r="CY7" s="1"/>
+      <c r="CZ7" s="1"/>
+      <c r="DA7" s="1"/>
+      <c r="DB7" s="1"/>
+      <c r="DC7" s="1"/>
+      <c r="DD7" s="1"/>
+      <c r="DE7" s="1"/>
+      <c r="DF7" s="1"/>
+      <c r="DG7" s="1"/>
+      <c r="DH7" s="1"/>
+      <c r="DI7" s="1"/>
+      <c r="DJ7" s="1"/>
+      <c r="DK7" s="1"/>
+      <c r="DL7" s="1"/>
+      <c r="DM7" s="1"/>
+      <c r="DN7" s="1"/>
+      <c r="DO7" s="1"/>
+      <c r="DP7" s="1"/>
+      <c r="DQ7" s="1"/>
+      <c r="DR7" s="1"/>
+      <c r="DS7" s="1"/>
+      <c r="DT7" s="1"/>
+      <c r="DU7" s="1"/>
+      <c r="DV7" s="1"/>
+      <c r="DW7" s="1"/>
+      <c r="DX7" s="1"/>
+      <c r="DY7" s="1"/>
+      <c r="DZ7" s="1"/>
+      <c r="EA7" s="1"/>
+      <c r="EB7" s="1"/>
+      <c r="EC7" s="1"/>
+      <c r="ED7" s="1"/>
+      <c r="EE7" s="1"/>
+      <c r="EF7" s="1"/>
+      <c r="EG7" s="1"/>
+      <c r="EH7" s="1"/>
+      <c r="EI7" s="1"/>
+      <c r="EJ7" s="1"/>
+      <c r="EK7" s="1"/>
+      <c r="EL7" s="1"/>
+      <c r="EM7" s="1"/>
+      <c r="EN7" s="1"/>
+      <c r="EO7" s="1"/>
+      <c r="EP7" s="1"/>
+      <c r="EQ7" s="1"/>
+      <c r="ER7" s="1"/>
+      <c r="ES7" s="1"/>
+      <c r="ET7" s="1"/>
+      <c r="EU7" s="1"/>
+      <c r="EV7" s="1"/>
+      <c r="EW7" s="1"/>
+      <c r="EX7" s="1"/>
+      <c r="EY7" s="1"/>
+      <c r="EZ7" s="1"/>
+      <c r="FA7" s="1"/>
+      <c r="FB7" s="1"/>
+      <c r="FC7" s="1"/>
+      <c r="FD7" s="1"/>
+      <c r="FE7" s="1"/>
+      <c r="FF7" s="1"/>
+      <c r="FG7" s="1"/>
+      <c r="FH7" s="1"/>
+      <c r="FI7" s="1"/>
+      <c r="FJ7" s="1"/>
+      <c r="FK7" s="1"/>
+      <c r="FL7" s="1"/>
+      <c r="FM7" s="1"/>
+      <c r="FN7" s="1"/>
+      <c r="FO7" s="1"/>
+      <c r="FP7" s="1"/>
+      <c r="FQ7" s="1"/>
+      <c r="FR7" s="1"/>
+      <c r="FS7" s="1"/>
+      <c r="FT7" s="1"/>
+      <c r="FU7" s="1"/>
+      <c r="FV7" s="1"/>
+      <c r="FW7" s="1"/>
+      <c r="FX7" s="1"/>
+      <c r="FY7" s="1"/>
+      <c r="FZ7" s="1"/>
+      <c r="GA7" s="1"/>
+      <c r="GB7" s="1"/>
+      <c r="GC7" s="1"/>
+      <c r="GD7" s="1"/>
+      <c r="GE7" s="1"/>
+      <c r="GF7" s="1"/>
+      <c r="GG7" s="1"/>
+      <c r="GH7" s="1"/>
+      <c r="GI7" s="1"/>
+      <c r="GJ7" s="1"/>
+      <c r="GK7" s="1"/>
+      <c r="GL7" s="1"/>
+      <c r="GM7" s="1"/>
+      <c r="GN7" s="1"/>
+      <c r="GO7" s="1"/>
+      <c r="GP7" s="1"/>
+      <c r="GQ7" s="1"/>
+      <c r="GR7" s="1"/>
+      <c r="GS7" s="1"/>
+      <c r="GT7" s="1"/>
+      <c r="GU7" s="1"/>
+      <c r="GV7" s="1"/>
+      <c r="GW7" s="1"/>
+      <c r="GX7" s="1"/>
+      <c r="GY7" s="1"/>
+      <c r="GZ7" s="1"/>
+      <c r="HA7" s="1"/>
+      <c r="HB7" s="1"/>
+      <c r="HC7" s="1"/>
+      <c r="HD7" s="1"/>
+      <c r="HE7" s="1"/>
+      <c r="HF7" s="1"/>
+      <c r="HG7" s="1"/>
+      <c r="HH7" s="1"/>
+      <c r="HI7" s="1"/>
+      <c r="HJ7" s="1"/>
+      <c r="HK7" s="1"/>
+      <c r="HL7" s="1"/>
+      <c r="HM7" s="1"/>
+      <c r="HN7" s="1"/>
+      <c r="HO7" s="1"/>
+      <c r="HP7" s="1"/>
+      <c r="HQ7" s="1"/>
+      <c r="HR7" s="1"/>
+      <c r="HS7" s="1"/>
+      <c r="HT7" s="1"/>
+      <c r="HU7" s="1"/>
+      <c r="HV7" s="1"/>
+      <c r="HW7" s="1"/>
+      <c r="HX7" s="1"/>
+      <c r="HY7" s="1"/>
+      <c r="HZ7" s="1"/>
+      <c r="IA7" s="1"/>
+      <c r="IB7" s="1"/>
+      <c r="IC7" s="1"/>
+      <c r="ID7" s="1"/>
+      <c r="IE7" s="1"/>
+      <c r="IF7" s="1"/>
+      <c r="IG7" s="1"/>
+      <c r="IH7" s="1"/>
+      <c r="II7" s="1"/>
+      <c r="IJ7" s="1"/>
+      <c r="IK7" s="1"/>
+      <c r="IL7" s="1"/>
+      <c r="IM7" s="1"/>
+      <c r="IN7" s="1"/>
+      <c r="IO7" s="1"/>
+      <c r="IP7" s="1"/>
+      <c r="IQ7" s="1"/>
+      <c r="IR7" s="1"/>
+      <c r="IS7" s="1"/>
+      <c r="IT7" s="1"/>
+      <c r="IU7" s="1"/>
+      <c r="IV7" s="1"/>
+      <c r="IW7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="98"/>
       <c r="B8" s="112" t="s">
         <v>48</v>
@@ -8500,8 +10816,241 @@
       <c r="V8" s="5"/>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="1"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1"/>
+      <c r="AR8" s="1"/>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="1"/>
+      <c r="AU8" s="1"/>
+      <c r="AV8" s="1"/>
+      <c r="AW8" s="1"/>
+      <c r="AX8" s="1"/>
+      <c r="AY8" s="1"/>
+      <c r="AZ8" s="1"/>
+      <c r="BA8" s="1"/>
+      <c r="BB8" s="1"/>
+      <c r="BC8" s="1"/>
+      <c r="BD8" s="1"/>
+      <c r="BE8" s="1"/>
+      <c r="BF8" s="1"/>
+      <c r="BG8" s="1"/>
+      <c r="BH8" s="1"/>
+      <c r="BI8" s="1"/>
+      <c r="BJ8" s="1"/>
+      <c r="BK8" s="1"/>
+      <c r="BL8" s="1"/>
+      <c r="BM8" s="1"/>
+      <c r="BN8" s="1"/>
+      <c r="BO8" s="1"/>
+      <c r="BP8" s="1"/>
+      <c r="BQ8" s="1"/>
+      <c r="BR8" s="1"/>
+      <c r="BS8" s="1"/>
+      <c r="BT8" s="1"/>
+      <c r="BU8" s="1"/>
+      <c r="BV8" s="1"/>
+      <c r="BW8" s="1"/>
+      <c r="BX8" s="1"/>
+      <c r="BY8" s="1"/>
+      <c r="BZ8" s="1"/>
+      <c r="CA8" s="1"/>
+      <c r="CB8" s="1"/>
+      <c r="CC8" s="1"/>
+      <c r="CD8" s="1"/>
+      <c r="CE8" s="1"/>
+      <c r="CF8" s="1"/>
+      <c r="CG8" s="1"/>
+      <c r="CH8" s="1"/>
+      <c r="CI8" s="1"/>
+      <c r="CJ8" s="1"/>
+      <c r="CK8" s="1"/>
+      <c r="CL8" s="1"/>
+      <c r="CM8" s="1"/>
+      <c r="CN8" s="1"/>
+      <c r="CO8" s="1"/>
+      <c r="CP8" s="1"/>
+      <c r="CQ8" s="1"/>
+      <c r="CR8" s="1"/>
+      <c r="CS8" s="1"/>
+      <c r="CT8" s="1"/>
+      <c r="CU8" s="1"/>
+      <c r="CV8" s="1"/>
+      <c r="CW8" s="1"/>
+      <c r="CX8" s="1"/>
+      <c r="CY8" s="1"/>
+      <c r="CZ8" s="1"/>
+      <c r="DA8" s="1"/>
+      <c r="DB8" s="1"/>
+      <c r="DC8" s="1"/>
+      <c r="DD8" s="1"/>
+      <c r="DE8" s="1"/>
+      <c r="DF8" s="1"/>
+      <c r="DG8" s="1"/>
+      <c r="DH8" s="1"/>
+      <c r="DI8" s="1"/>
+      <c r="DJ8" s="1"/>
+      <c r="DK8" s="1"/>
+      <c r="DL8" s="1"/>
+      <c r="DM8" s="1"/>
+      <c r="DN8" s="1"/>
+      <c r="DO8" s="1"/>
+      <c r="DP8" s="1"/>
+      <c r="DQ8" s="1"/>
+      <c r="DR8" s="1"/>
+      <c r="DS8" s="1"/>
+      <c r="DT8" s="1"/>
+      <c r="DU8" s="1"/>
+      <c r="DV8" s="1"/>
+      <c r="DW8" s="1"/>
+      <c r="DX8" s="1"/>
+      <c r="DY8" s="1"/>
+      <c r="DZ8" s="1"/>
+      <c r="EA8" s="1"/>
+      <c r="EB8" s="1"/>
+      <c r="EC8" s="1"/>
+      <c r="ED8" s="1"/>
+      <c r="EE8" s="1"/>
+      <c r="EF8" s="1"/>
+      <c r="EG8" s="1"/>
+      <c r="EH8" s="1"/>
+      <c r="EI8" s="1"/>
+      <c r="EJ8" s="1"/>
+      <c r="EK8" s="1"/>
+      <c r="EL8" s="1"/>
+      <c r="EM8" s="1"/>
+      <c r="EN8" s="1"/>
+      <c r="EO8" s="1"/>
+      <c r="EP8" s="1"/>
+      <c r="EQ8" s="1"/>
+      <c r="ER8" s="1"/>
+      <c r="ES8" s="1"/>
+      <c r="ET8" s="1"/>
+      <c r="EU8" s="1"/>
+      <c r="EV8" s="1"/>
+      <c r="EW8" s="1"/>
+      <c r="EX8" s="1"/>
+      <c r="EY8" s="1"/>
+      <c r="EZ8" s="1"/>
+      <c r="FA8" s="1"/>
+      <c r="FB8" s="1"/>
+      <c r="FC8" s="1"/>
+      <c r="FD8" s="1"/>
+      <c r="FE8" s="1"/>
+      <c r="FF8" s="1"/>
+      <c r="FG8" s="1"/>
+      <c r="FH8" s="1"/>
+      <c r="FI8" s="1"/>
+      <c r="FJ8" s="1"/>
+      <c r="FK8" s="1"/>
+      <c r="FL8" s="1"/>
+      <c r="FM8" s="1"/>
+      <c r="FN8" s="1"/>
+      <c r="FO8" s="1"/>
+      <c r="FP8" s="1"/>
+      <c r="FQ8" s="1"/>
+      <c r="FR8" s="1"/>
+      <c r="FS8" s="1"/>
+      <c r="FT8" s="1"/>
+      <c r="FU8" s="1"/>
+      <c r="FV8" s="1"/>
+      <c r="FW8" s="1"/>
+      <c r="FX8" s="1"/>
+      <c r="FY8" s="1"/>
+      <c r="FZ8" s="1"/>
+      <c r="GA8" s="1"/>
+      <c r="GB8" s="1"/>
+      <c r="GC8" s="1"/>
+      <c r="GD8" s="1"/>
+      <c r="GE8" s="1"/>
+      <c r="GF8" s="1"/>
+      <c r="GG8" s="1"/>
+      <c r="GH8" s="1"/>
+      <c r="GI8" s="1"/>
+      <c r="GJ8" s="1"/>
+      <c r="GK8" s="1"/>
+      <c r="GL8" s="1"/>
+      <c r="GM8" s="1"/>
+      <c r="GN8" s="1"/>
+      <c r="GO8" s="1"/>
+      <c r="GP8" s="1"/>
+      <c r="GQ8" s="1"/>
+      <c r="GR8" s="1"/>
+      <c r="GS8" s="1"/>
+      <c r="GT8" s="1"/>
+      <c r="GU8" s="1"/>
+      <c r="GV8" s="1"/>
+      <c r="GW8" s="1"/>
+      <c r="GX8" s="1"/>
+      <c r="GY8" s="1"/>
+      <c r="GZ8" s="1"/>
+      <c r="HA8" s="1"/>
+      <c r="HB8" s="1"/>
+      <c r="HC8" s="1"/>
+      <c r="HD8" s="1"/>
+      <c r="HE8" s="1"/>
+      <c r="HF8" s="1"/>
+      <c r="HG8" s="1"/>
+      <c r="HH8" s="1"/>
+      <c r="HI8" s="1"/>
+      <c r="HJ8" s="1"/>
+      <c r="HK8" s="1"/>
+      <c r="HL8" s="1"/>
+      <c r="HM8" s="1"/>
+      <c r="HN8" s="1"/>
+      <c r="HO8" s="1"/>
+      <c r="HP8" s="1"/>
+      <c r="HQ8" s="1"/>
+      <c r="HR8" s="1"/>
+      <c r="HS8" s="1"/>
+      <c r="HT8" s="1"/>
+      <c r="HU8" s="1"/>
+      <c r="HV8" s="1"/>
+      <c r="HW8" s="1"/>
+      <c r="HX8" s="1"/>
+      <c r="HY8" s="1"/>
+      <c r="HZ8" s="1"/>
+      <c r="IA8" s="1"/>
+      <c r="IB8" s="1"/>
+      <c r="IC8" s="1"/>
+      <c r="ID8" s="1"/>
+      <c r="IE8" s="1"/>
+      <c r="IF8" s="1"/>
+      <c r="IG8" s="1"/>
+      <c r="IH8" s="1"/>
+      <c r="II8" s="1"/>
+      <c r="IJ8" s="1"/>
+      <c r="IK8" s="1"/>
+      <c r="IL8" s="1"/>
+      <c r="IM8" s="1"/>
+      <c r="IN8" s="1"/>
+      <c r="IO8" s="1"/>
+      <c r="IP8" s="1"/>
+      <c r="IQ8" s="1"/>
+      <c r="IR8" s="1"/>
+      <c r="IS8" s="1"/>
+      <c r="IT8" s="1"/>
+      <c r="IU8" s="1"/>
+      <c r="IV8" s="1"/>
+      <c r="IW8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="98"/>
       <c r="B9" s="112" t="s">
         <v>49</v>
@@ -8536,8 +11085,241 @@
       <c r="V9" s="5"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-    </row>
-    <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="1"/>
+      <c r="AR9" s="1"/>
+      <c r="AS9" s="1"/>
+      <c r="AT9" s="1"/>
+      <c r="AU9" s="1"/>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="1"/>
+      <c r="AX9" s="1"/>
+      <c r="AY9" s="1"/>
+      <c r="AZ9" s="1"/>
+      <c r="BA9" s="1"/>
+      <c r="BB9" s="1"/>
+      <c r="BC9" s="1"/>
+      <c r="BD9" s="1"/>
+      <c r="BE9" s="1"/>
+      <c r="BF9" s="1"/>
+      <c r="BG9" s="1"/>
+      <c r="BH9" s="1"/>
+      <c r="BI9" s="1"/>
+      <c r="BJ9" s="1"/>
+      <c r="BK9" s="1"/>
+      <c r="BL9" s="1"/>
+      <c r="BM9" s="1"/>
+      <c r="BN9" s="1"/>
+      <c r="BO9" s="1"/>
+      <c r="BP9" s="1"/>
+      <c r="BQ9" s="1"/>
+      <c r="BR9" s="1"/>
+      <c r="BS9" s="1"/>
+      <c r="BT9" s="1"/>
+      <c r="BU9" s="1"/>
+      <c r="BV9" s="1"/>
+      <c r="BW9" s="1"/>
+      <c r="BX9" s="1"/>
+      <c r="BY9" s="1"/>
+      <c r="BZ9" s="1"/>
+      <c r="CA9" s="1"/>
+      <c r="CB9" s="1"/>
+      <c r="CC9" s="1"/>
+      <c r="CD9" s="1"/>
+      <c r="CE9" s="1"/>
+      <c r="CF9" s="1"/>
+      <c r="CG9" s="1"/>
+      <c r="CH9" s="1"/>
+      <c r="CI9" s="1"/>
+      <c r="CJ9" s="1"/>
+      <c r="CK9" s="1"/>
+      <c r="CL9" s="1"/>
+      <c r="CM9" s="1"/>
+      <c r="CN9" s="1"/>
+      <c r="CO9" s="1"/>
+      <c r="CP9" s="1"/>
+      <c r="CQ9" s="1"/>
+      <c r="CR9" s="1"/>
+      <c r="CS9" s="1"/>
+      <c r="CT9" s="1"/>
+      <c r="CU9" s="1"/>
+      <c r="CV9" s="1"/>
+      <c r="CW9" s="1"/>
+      <c r="CX9" s="1"/>
+      <c r="CY9" s="1"/>
+      <c r="CZ9" s="1"/>
+      <c r="DA9" s="1"/>
+      <c r="DB9" s="1"/>
+      <c r="DC9" s="1"/>
+      <c r="DD9" s="1"/>
+      <c r="DE9" s="1"/>
+      <c r="DF9" s="1"/>
+      <c r="DG9" s="1"/>
+      <c r="DH9" s="1"/>
+      <c r="DI9" s="1"/>
+      <c r="DJ9" s="1"/>
+      <c r="DK9" s="1"/>
+      <c r="DL9" s="1"/>
+      <c r="DM9" s="1"/>
+      <c r="DN9" s="1"/>
+      <c r="DO9" s="1"/>
+      <c r="DP9" s="1"/>
+      <c r="DQ9" s="1"/>
+      <c r="DR9" s="1"/>
+      <c r="DS9" s="1"/>
+      <c r="DT9" s="1"/>
+      <c r="DU9" s="1"/>
+      <c r="DV9" s="1"/>
+      <c r="DW9" s="1"/>
+      <c r="DX9" s="1"/>
+      <c r="DY9" s="1"/>
+      <c r="DZ9" s="1"/>
+      <c r="EA9" s="1"/>
+      <c r="EB9" s="1"/>
+      <c r="EC9" s="1"/>
+      <c r="ED9" s="1"/>
+      <c r="EE9" s="1"/>
+      <c r="EF9" s="1"/>
+      <c r="EG9" s="1"/>
+      <c r="EH9" s="1"/>
+      <c r="EI9" s="1"/>
+      <c r="EJ9" s="1"/>
+      <c r="EK9" s="1"/>
+      <c r="EL9" s="1"/>
+      <c r="EM9" s="1"/>
+      <c r="EN9" s="1"/>
+      <c r="EO9" s="1"/>
+      <c r="EP9" s="1"/>
+      <c r="EQ9" s="1"/>
+      <c r="ER9" s="1"/>
+      <c r="ES9" s="1"/>
+      <c r="ET9" s="1"/>
+      <c r="EU9" s="1"/>
+      <c r="EV9" s="1"/>
+      <c r="EW9" s="1"/>
+      <c r="EX9" s="1"/>
+      <c r="EY9" s="1"/>
+      <c r="EZ9" s="1"/>
+      <c r="FA9" s="1"/>
+      <c r="FB9" s="1"/>
+      <c r="FC9" s="1"/>
+      <c r="FD9" s="1"/>
+      <c r="FE9" s="1"/>
+      <c r="FF9" s="1"/>
+      <c r="FG9" s="1"/>
+      <c r="FH9" s="1"/>
+      <c r="FI9" s="1"/>
+      <c r="FJ9" s="1"/>
+      <c r="FK9" s="1"/>
+      <c r="FL9" s="1"/>
+      <c r="FM9" s="1"/>
+      <c r="FN9" s="1"/>
+      <c r="FO9" s="1"/>
+      <c r="FP9" s="1"/>
+      <c r="FQ9" s="1"/>
+      <c r="FR9" s="1"/>
+      <c r="FS9" s="1"/>
+      <c r="FT9" s="1"/>
+      <c r="FU9" s="1"/>
+      <c r="FV9" s="1"/>
+      <c r="FW9" s="1"/>
+      <c r="FX9" s="1"/>
+      <c r="FY9" s="1"/>
+      <c r="FZ9" s="1"/>
+      <c r="GA9" s="1"/>
+      <c r="GB9" s="1"/>
+      <c r="GC9" s="1"/>
+      <c r="GD9" s="1"/>
+      <c r="GE9" s="1"/>
+      <c r="GF9" s="1"/>
+      <c r="GG9" s="1"/>
+      <c r="GH9" s="1"/>
+      <c r="GI9" s="1"/>
+      <c r="GJ9" s="1"/>
+      <c r="GK9" s="1"/>
+      <c r="GL9" s="1"/>
+      <c r="GM9" s="1"/>
+      <c r="GN9" s="1"/>
+      <c r="GO9" s="1"/>
+      <c r="GP9" s="1"/>
+      <c r="GQ9" s="1"/>
+      <c r="GR9" s="1"/>
+      <c r="GS9" s="1"/>
+      <c r="GT9" s="1"/>
+      <c r="GU9" s="1"/>
+      <c r="GV9" s="1"/>
+      <c r="GW9" s="1"/>
+      <c r="GX9" s="1"/>
+      <c r="GY9" s="1"/>
+      <c r="GZ9" s="1"/>
+      <c r="HA9" s="1"/>
+      <c r="HB9" s="1"/>
+      <c r="HC9" s="1"/>
+      <c r="HD9" s="1"/>
+      <c r="HE9" s="1"/>
+      <c r="HF9" s="1"/>
+      <c r="HG9" s="1"/>
+      <c r="HH9" s="1"/>
+      <c r="HI9" s="1"/>
+      <c r="HJ9" s="1"/>
+      <c r="HK9" s="1"/>
+      <c r="HL9" s="1"/>
+      <c r="HM9" s="1"/>
+      <c r="HN9" s="1"/>
+      <c r="HO9" s="1"/>
+      <c r="HP9" s="1"/>
+      <c r="HQ9" s="1"/>
+      <c r="HR9" s="1"/>
+      <c r="HS9" s="1"/>
+      <c r="HT9" s="1"/>
+      <c r="HU9" s="1"/>
+      <c r="HV9" s="1"/>
+      <c r="HW9" s="1"/>
+      <c r="HX9" s="1"/>
+      <c r="HY9" s="1"/>
+      <c r="HZ9" s="1"/>
+      <c r="IA9" s="1"/>
+      <c r="IB9" s="1"/>
+      <c r="IC9" s="1"/>
+      <c r="ID9" s="1"/>
+      <c r="IE9" s="1"/>
+      <c r="IF9" s="1"/>
+      <c r="IG9" s="1"/>
+      <c r="IH9" s="1"/>
+      <c r="II9" s="1"/>
+      <c r="IJ9" s="1"/>
+      <c r="IK9" s="1"/>
+      <c r="IL9" s="1"/>
+      <c r="IM9" s="1"/>
+      <c r="IN9" s="1"/>
+      <c r="IO9" s="1"/>
+      <c r="IP9" s="1"/>
+      <c r="IQ9" s="1"/>
+      <c r="IR9" s="1"/>
+      <c r="IS9" s="1"/>
+      <c r="IT9" s="1"/>
+      <c r="IU9" s="1"/>
+      <c r="IV9" s="1"/>
+      <c r="IW9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="98"/>
       <c r="B10" s="112" t="s">
         <v>50</v>
@@ -8572,8 +11354,241 @@
       <c r="V10" s="5"/>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
-    </row>
-    <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="1"/>
+      <c r="AP10" s="1"/>
+      <c r="AQ10" s="1"/>
+      <c r="AR10" s="1"/>
+      <c r="AS10" s="1"/>
+      <c r="AT10" s="1"/>
+      <c r="AU10" s="1"/>
+      <c r="AV10" s="1"/>
+      <c r="AW10" s="1"/>
+      <c r="AX10" s="1"/>
+      <c r="AY10" s="1"/>
+      <c r="AZ10" s="1"/>
+      <c r="BA10" s="1"/>
+      <c r="BB10" s="1"/>
+      <c r="BC10" s="1"/>
+      <c r="BD10" s="1"/>
+      <c r="BE10" s="1"/>
+      <c r="BF10" s="1"/>
+      <c r="BG10" s="1"/>
+      <c r="BH10" s="1"/>
+      <c r="BI10" s="1"/>
+      <c r="BJ10" s="1"/>
+      <c r="BK10" s="1"/>
+      <c r="BL10" s="1"/>
+      <c r="BM10" s="1"/>
+      <c r="BN10" s="1"/>
+      <c r="BO10" s="1"/>
+      <c r="BP10" s="1"/>
+      <c r="BQ10" s="1"/>
+      <c r="BR10" s="1"/>
+      <c r="BS10" s="1"/>
+      <c r="BT10" s="1"/>
+      <c r="BU10" s="1"/>
+      <c r="BV10" s="1"/>
+      <c r="BW10" s="1"/>
+      <c r="BX10" s="1"/>
+      <c r="BY10" s="1"/>
+      <c r="BZ10" s="1"/>
+      <c r="CA10" s="1"/>
+      <c r="CB10" s="1"/>
+      <c r="CC10" s="1"/>
+      <c r="CD10" s="1"/>
+      <c r="CE10" s="1"/>
+      <c r="CF10" s="1"/>
+      <c r="CG10" s="1"/>
+      <c r="CH10" s="1"/>
+      <c r="CI10" s="1"/>
+      <c r="CJ10" s="1"/>
+      <c r="CK10" s="1"/>
+      <c r="CL10" s="1"/>
+      <c r="CM10" s="1"/>
+      <c r="CN10" s="1"/>
+      <c r="CO10" s="1"/>
+      <c r="CP10" s="1"/>
+      <c r="CQ10" s="1"/>
+      <c r="CR10" s="1"/>
+      <c r="CS10" s="1"/>
+      <c r="CT10" s="1"/>
+      <c r="CU10" s="1"/>
+      <c r="CV10" s="1"/>
+      <c r="CW10" s="1"/>
+      <c r="CX10" s="1"/>
+      <c r="CY10" s="1"/>
+      <c r="CZ10" s="1"/>
+      <c r="DA10" s="1"/>
+      <c r="DB10" s="1"/>
+      <c r="DC10" s="1"/>
+      <c r="DD10" s="1"/>
+      <c r="DE10" s="1"/>
+      <c r="DF10" s="1"/>
+      <c r="DG10" s="1"/>
+      <c r="DH10" s="1"/>
+      <c r="DI10" s="1"/>
+      <c r="DJ10" s="1"/>
+      <c r="DK10" s="1"/>
+      <c r="DL10" s="1"/>
+      <c r="DM10" s="1"/>
+      <c r="DN10" s="1"/>
+      <c r="DO10" s="1"/>
+      <c r="DP10" s="1"/>
+      <c r="DQ10" s="1"/>
+      <c r="DR10" s="1"/>
+      <c r="DS10" s="1"/>
+      <c r="DT10" s="1"/>
+      <c r="DU10" s="1"/>
+      <c r="DV10" s="1"/>
+      <c r="DW10" s="1"/>
+      <c r="DX10" s="1"/>
+      <c r="DY10" s="1"/>
+      <c r="DZ10" s="1"/>
+      <c r="EA10" s="1"/>
+      <c r="EB10" s="1"/>
+      <c r="EC10" s="1"/>
+      <c r="ED10" s="1"/>
+      <c r="EE10" s="1"/>
+      <c r="EF10" s="1"/>
+      <c r="EG10" s="1"/>
+      <c r="EH10" s="1"/>
+      <c r="EI10" s="1"/>
+      <c r="EJ10" s="1"/>
+      <c r="EK10" s="1"/>
+      <c r="EL10" s="1"/>
+      <c r="EM10" s="1"/>
+      <c r="EN10" s="1"/>
+      <c r="EO10" s="1"/>
+      <c r="EP10" s="1"/>
+      <c r="EQ10" s="1"/>
+      <c r="ER10" s="1"/>
+      <c r="ES10" s="1"/>
+      <c r="ET10" s="1"/>
+      <c r="EU10" s="1"/>
+      <c r="EV10" s="1"/>
+      <c r="EW10" s="1"/>
+      <c r="EX10" s="1"/>
+      <c r="EY10" s="1"/>
+      <c r="EZ10" s="1"/>
+      <c r="FA10" s="1"/>
+      <c r="FB10" s="1"/>
+      <c r="FC10" s="1"/>
+      <c r="FD10" s="1"/>
+      <c r="FE10" s="1"/>
+      <c r="FF10" s="1"/>
+      <c r="FG10" s="1"/>
+      <c r="FH10" s="1"/>
+      <c r="FI10" s="1"/>
+      <c r="FJ10" s="1"/>
+      <c r="FK10" s="1"/>
+      <c r="FL10" s="1"/>
+      <c r="FM10" s="1"/>
+      <c r="FN10" s="1"/>
+      <c r="FO10" s="1"/>
+      <c r="FP10" s="1"/>
+      <c r="FQ10" s="1"/>
+      <c r="FR10" s="1"/>
+      <c r="FS10" s="1"/>
+      <c r="FT10" s="1"/>
+      <c r="FU10" s="1"/>
+      <c r="FV10" s="1"/>
+      <c r="FW10" s="1"/>
+      <c r="FX10" s="1"/>
+      <c r="FY10" s="1"/>
+      <c r="FZ10" s="1"/>
+      <c r="GA10" s="1"/>
+      <c r="GB10" s="1"/>
+      <c r="GC10" s="1"/>
+      <c r="GD10" s="1"/>
+      <c r="GE10" s="1"/>
+      <c r="GF10" s="1"/>
+      <c r="GG10" s="1"/>
+      <c r="GH10" s="1"/>
+      <c r="GI10" s="1"/>
+      <c r="GJ10" s="1"/>
+      <c r="GK10" s="1"/>
+      <c r="GL10" s="1"/>
+      <c r="GM10" s="1"/>
+      <c r="GN10" s="1"/>
+      <c r="GO10" s="1"/>
+      <c r="GP10" s="1"/>
+      <c r="GQ10" s="1"/>
+      <c r="GR10" s="1"/>
+      <c r="GS10" s="1"/>
+      <c r="GT10" s="1"/>
+      <c r="GU10" s="1"/>
+      <c r="GV10" s="1"/>
+      <c r="GW10" s="1"/>
+      <c r="GX10" s="1"/>
+      <c r="GY10" s="1"/>
+      <c r="GZ10" s="1"/>
+      <c r="HA10" s="1"/>
+      <c r="HB10" s="1"/>
+      <c r="HC10" s="1"/>
+      <c r="HD10" s="1"/>
+      <c r="HE10" s="1"/>
+      <c r="HF10" s="1"/>
+      <c r="HG10" s="1"/>
+      <c r="HH10" s="1"/>
+      <c r="HI10" s="1"/>
+      <c r="HJ10" s="1"/>
+      <c r="HK10" s="1"/>
+      <c r="HL10" s="1"/>
+      <c r="HM10" s="1"/>
+      <c r="HN10" s="1"/>
+      <c r="HO10" s="1"/>
+      <c r="HP10" s="1"/>
+      <c r="HQ10" s="1"/>
+      <c r="HR10" s="1"/>
+      <c r="HS10" s="1"/>
+      <c r="HT10" s="1"/>
+      <c r="HU10" s="1"/>
+      <c r="HV10" s="1"/>
+      <c r="HW10" s="1"/>
+      <c r="HX10" s="1"/>
+      <c r="HY10" s="1"/>
+      <c r="HZ10" s="1"/>
+      <c r="IA10" s="1"/>
+      <c r="IB10" s="1"/>
+      <c r="IC10" s="1"/>
+      <c r="ID10" s="1"/>
+      <c r="IE10" s="1"/>
+      <c r="IF10" s="1"/>
+      <c r="IG10" s="1"/>
+      <c r="IH10" s="1"/>
+      <c r="II10" s="1"/>
+      <c r="IJ10" s="1"/>
+      <c r="IK10" s="1"/>
+      <c r="IL10" s="1"/>
+      <c r="IM10" s="1"/>
+      <c r="IN10" s="1"/>
+      <c r="IO10" s="1"/>
+      <c r="IP10" s="1"/>
+      <c r="IQ10" s="1"/>
+      <c r="IR10" s="1"/>
+      <c r="IS10" s="1"/>
+      <c r="IT10" s="1"/>
+      <c r="IU10" s="1"/>
+      <c r="IV10" s="1"/>
+      <c r="IW10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="98"/>
       <c r="B11" s="114" t="s">
         <v>63</v>
@@ -8608,8 +11623,241 @@
       <c r="V11" s="5"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-    </row>
-    <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="1"/>
+      <c r="AP11" s="1"/>
+      <c r="AQ11" s="1"/>
+      <c r="AR11" s="1"/>
+      <c r="AS11" s="1"/>
+      <c r="AT11" s="1"/>
+      <c r="AU11" s="1"/>
+      <c r="AV11" s="1"/>
+      <c r="AW11" s="1"/>
+      <c r="AX11" s="1"/>
+      <c r="AY11" s="1"/>
+      <c r="AZ11" s="1"/>
+      <c r="BA11" s="1"/>
+      <c r="BB11" s="1"/>
+      <c r="BC11" s="1"/>
+      <c r="BD11" s="1"/>
+      <c r="BE11" s="1"/>
+      <c r="BF11" s="1"/>
+      <c r="BG11" s="1"/>
+      <c r="BH11" s="1"/>
+      <c r="BI11" s="1"/>
+      <c r="BJ11" s="1"/>
+      <c r="BK11" s="1"/>
+      <c r="BL11" s="1"/>
+      <c r="BM11" s="1"/>
+      <c r="BN11" s="1"/>
+      <c r="BO11" s="1"/>
+      <c r="BP11" s="1"/>
+      <c r="BQ11" s="1"/>
+      <c r="BR11" s="1"/>
+      <c r="BS11" s="1"/>
+      <c r="BT11" s="1"/>
+      <c r="BU11" s="1"/>
+      <c r="BV11" s="1"/>
+      <c r="BW11" s="1"/>
+      <c r="BX11" s="1"/>
+      <c r="BY11" s="1"/>
+      <c r="BZ11" s="1"/>
+      <c r="CA11" s="1"/>
+      <c r="CB11" s="1"/>
+      <c r="CC11" s="1"/>
+      <c r="CD11" s="1"/>
+      <c r="CE11" s="1"/>
+      <c r="CF11" s="1"/>
+      <c r="CG11" s="1"/>
+      <c r="CH11" s="1"/>
+      <c r="CI11" s="1"/>
+      <c r="CJ11" s="1"/>
+      <c r="CK11" s="1"/>
+      <c r="CL11" s="1"/>
+      <c r="CM11" s="1"/>
+      <c r="CN11" s="1"/>
+      <c r="CO11" s="1"/>
+      <c r="CP11" s="1"/>
+      <c r="CQ11" s="1"/>
+      <c r="CR11" s="1"/>
+      <c r="CS11" s="1"/>
+      <c r="CT11" s="1"/>
+      <c r="CU11" s="1"/>
+      <c r="CV11" s="1"/>
+      <c r="CW11" s="1"/>
+      <c r="CX11" s="1"/>
+      <c r="CY11" s="1"/>
+      <c r="CZ11" s="1"/>
+      <c r="DA11" s="1"/>
+      <c r="DB11" s="1"/>
+      <c r="DC11" s="1"/>
+      <c r="DD11" s="1"/>
+      <c r="DE11" s="1"/>
+      <c r="DF11" s="1"/>
+      <c r="DG11" s="1"/>
+      <c r="DH11" s="1"/>
+      <c r="DI11" s="1"/>
+      <c r="DJ11" s="1"/>
+      <c r="DK11" s="1"/>
+      <c r="DL11" s="1"/>
+      <c r="DM11" s="1"/>
+      <c r="DN11" s="1"/>
+      <c r="DO11" s="1"/>
+      <c r="DP11" s="1"/>
+      <c r="DQ11" s="1"/>
+      <c r="DR11" s="1"/>
+      <c r="DS11" s="1"/>
+      <c r="DT11" s="1"/>
+      <c r="DU11" s="1"/>
+      <c r="DV11" s="1"/>
+      <c r="DW11" s="1"/>
+      <c r="DX11" s="1"/>
+      <c r="DY11" s="1"/>
+      <c r="DZ11" s="1"/>
+      <c r="EA11" s="1"/>
+      <c r="EB11" s="1"/>
+      <c r="EC11" s="1"/>
+      <c r="ED11" s="1"/>
+      <c r="EE11" s="1"/>
+      <c r="EF11" s="1"/>
+      <c r="EG11" s="1"/>
+      <c r="EH11" s="1"/>
+      <c r="EI11" s="1"/>
+      <c r="EJ11" s="1"/>
+      <c r="EK11" s="1"/>
+      <c r="EL11" s="1"/>
+      <c r="EM11" s="1"/>
+      <c r="EN11" s="1"/>
+      <c r="EO11" s="1"/>
+      <c r="EP11" s="1"/>
+      <c r="EQ11" s="1"/>
+      <c r="ER11" s="1"/>
+      <c r="ES11" s="1"/>
+      <c r="ET11" s="1"/>
+      <c r="EU11" s="1"/>
+      <c r="EV11" s="1"/>
+      <c r="EW11" s="1"/>
+      <c r="EX11" s="1"/>
+      <c r="EY11" s="1"/>
+      <c r="EZ11" s="1"/>
+      <c r="FA11" s="1"/>
+      <c r="FB11" s="1"/>
+      <c r="FC11" s="1"/>
+      <c r="FD11" s="1"/>
+      <c r="FE11" s="1"/>
+      <c r="FF11" s="1"/>
+      <c r="FG11" s="1"/>
+      <c r="FH11" s="1"/>
+      <c r="FI11" s="1"/>
+      <c r="FJ11" s="1"/>
+      <c r="FK11" s="1"/>
+      <c r="FL11" s="1"/>
+      <c r="FM11" s="1"/>
+      <c r="FN11" s="1"/>
+      <c r="FO11" s="1"/>
+      <c r="FP11" s="1"/>
+      <c r="FQ11" s="1"/>
+      <c r="FR11" s="1"/>
+      <c r="FS11" s="1"/>
+      <c r="FT11" s="1"/>
+      <c r="FU11" s="1"/>
+      <c r="FV11" s="1"/>
+      <c r="FW11" s="1"/>
+      <c r="FX11" s="1"/>
+      <c r="FY11" s="1"/>
+      <c r="FZ11" s="1"/>
+      <c r="GA11" s="1"/>
+      <c r="GB11" s="1"/>
+      <c r="GC11" s="1"/>
+      <c r="GD11" s="1"/>
+      <c r="GE11" s="1"/>
+      <c r="GF11" s="1"/>
+      <c r="GG11" s="1"/>
+      <c r="GH11" s="1"/>
+      <c r="GI11" s="1"/>
+      <c r="GJ11" s="1"/>
+      <c r="GK11" s="1"/>
+      <c r="GL11" s="1"/>
+      <c r="GM11" s="1"/>
+      <c r="GN11" s="1"/>
+      <c r="GO11" s="1"/>
+      <c r="GP11" s="1"/>
+      <c r="GQ11" s="1"/>
+      <c r="GR11" s="1"/>
+      <c r="GS11" s="1"/>
+      <c r="GT11" s="1"/>
+      <c r="GU11" s="1"/>
+      <c r="GV11" s="1"/>
+      <c r="GW11" s="1"/>
+      <c r="GX11" s="1"/>
+      <c r="GY11" s="1"/>
+      <c r="GZ11" s="1"/>
+      <c r="HA11" s="1"/>
+      <c r="HB11" s="1"/>
+      <c r="HC11" s="1"/>
+      <c r="HD11" s="1"/>
+      <c r="HE11" s="1"/>
+      <c r="HF11" s="1"/>
+      <c r="HG11" s="1"/>
+      <c r="HH11" s="1"/>
+      <c r="HI11" s="1"/>
+      <c r="HJ11" s="1"/>
+      <c r="HK11" s="1"/>
+      <c r="HL11" s="1"/>
+      <c r="HM11" s="1"/>
+      <c r="HN11" s="1"/>
+      <c r="HO11" s="1"/>
+      <c r="HP11" s="1"/>
+      <c r="HQ11" s="1"/>
+      <c r="HR11" s="1"/>
+      <c r="HS11" s="1"/>
+      <c r="HT11" s="1"/>
+      <c r="HU11" s="1"/>
+      <c r="HV11" s="1"/>
+      <c r="HW11" s="1"/>
+      <c r="HX11" s="1"/>
+      <c r="HY11" s="1"/>
+      <c r="HZ11" s="1"/>
+      <c r="IA11" s="1"/>
+      <c r="IB11" s="1"/>
+      <c r="IC11" s="1"/>
+      <c r="ID11" s="1"/>
+      <c r="IE11" s="1"/>
+      <c r="IF11" s="1"/>
+      <c r="IG11" s="1"/>
+      <c r="IH11" s="1"/>
+      <c r="II11" s="1"/>
+      <c r="IJ11" s="1"/>
+      <c r="IK11" s="1"/>
+      <c r="IL11" s="1"/>
+      <c r="IM11" s="1"/>
+      <c r="IN11" s="1"/>
+      <c r="IO11" s="1"/>
+      <c r="IP11" s="1"/>
+      <c r="IQ11" s="1"/>
+      <c r="IR11" s="1"/>
+      <c r="IS11" s="1"/>
+      <c r="IT11" s="1"/>
+      <c r="IU11" s="1"/>
+      <c r="IV11" s="1"/>
+      <c r="IW11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="98"/>
       <c r="B12" s="99"/>
       <c r="C12" s="100"/>
@@ -8634,8 +11882,241 @@
       <c r="V12" s="5"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-    </row>
-    <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="1"/>
+      <c r="AP12" s="1"/>
+      <c r="AQ12" s="1"/>
+      <c r="AR12" s="1"/>
+      <c r="AS12" s="1"/>
+      <c r="AT12" s="1"/>
+      <c r="AU12" s="1"/>
+      <c r="AV12" s="1"/>
+      <c r="AW12" s="1"/>
+      <c r="AX12" s="1"/>
+      <c r="AY12" s="1"/>
+      <c r="AZ12" s="1"/>
+      <c r="BA12" s="1"/>
+      <c r="BB12" s="1"/>
+      <c r="BC12" s="1"/>
+      <c r="BD12" s="1"/>
+      <c r="BE12" s="1"/>
+      <c r="BF12" s="1"/>
+      <c r="BG12" s="1"/>
+      <c r="BH12" s="1"/>
+      <c r="BI12" s="1"/>
+      <c r="BJ12" s="1"/>
+      <c r="BK12" s="1"/>
+      <c r="BL12" s="1"/>
+      <c r="BM12" s="1"/>
+      <c r="BN12" s="1"/>
+      <c r="BO12" s="1"/>
+      <c r="BP12" s="1"/>
+      <c r="BQ12" s="1"/>
+      <c r="BR12" s="1"/>
+      <c r="BS12" s="1"/>
+      <c r="BT12" s="1"/>
+      <c r="BU12" s="1"/>
+      <c r="BV12" s="1"/>
+      <c r="BW12" s="1"/>
+      <c r="BX12" s="1"/>
+      <c r="BY12" s="1"/>
+      <c r="BZ12" s="1"/>
+      <c r="CA12" s="1"/>
+      <c r="CB12" s="1"/>
+      <c r="CC12" s="1"/>
+      <c r="CD12" s="1"/>
+      <c r="CE12" s="1"/>
+      <c r="CF12" s="1"/>
+      <c r="CG12" s="1"/>
+      <c r="CH12" s="1"/>
+      <c r="CI12" s="1"/>
+      <c r="CJ12" s="1"/>
+      <c r="CK12" s="1"/>
+      <c r="CL12" s="1"/>
+      <c r="CM12" s="1"/>
+      <c r="CN12" s="1"/>
+      <c r="CO12" s="1"/>
+      <c r="CP12" s="1"/>
+      <c r="CQ12" s="1"/>
+      <c r="CR12" s="1"/>
+      <c r="CS12" s="1"/>
+      <c r="CT12" s="1"/>
+      <c r="CU12" s="1"/>
+      <c r="CV12" s="1"/>
+      <c r="CW12" s="1"/>
+      <c r="CX12" s="1"/>
+      <c r="CY12" s="1"/>
+      <c r="CZ12" s="1"/>
+      <c r="DA12" s="1"/>
+      <c r="DB12" s="1"/>
+      <c r="DC12" s="1"/>
+      <c r="DD12" s="1"/>
+      <c r="DE12" s="1"/>
+      <c r="DF12" s="1"/>
+      <c r="DG12" s="1"/>
+      <c r="DH12" s="1"/>
+      <c r="DI12" s="1"/>
+      <c r="DJ12" s="1"/>
+      <c r="DK12" s="1"/>
+      <c r="DL12" s="1"/>
+      <c r="DM12" s="1"/>
+      <c r="DN12" s="1"/>
+      <c r="DO12" s="1"/>
+      <c r="DP12" s="1"/>
+      <c r="DQ12" s="1"/>
+      <c r="DR12" s="1"/>
+      <c r="DS12" s="1"/>
+      <c r="DT12" s="1"/>
+      <c r="DU12" s="1"/>
+      <c r="DV12" s="1"/>
+      <c r="DW12" s="1"/>
+      <c r="DX12" s="1"/>
+      <c r="DY12" s="1"/>
+      <c r="DZ12" s="1"/>
+      <c r="EA12" s="1"/>
+      <c r="EB12" s="1"/>
+      <c r="EC12" s="1"/>
+      <c r="ED12" s="1"/>
+      <c r="EE12" s="1"/>
+      <c r="EF12" s="1"/>
+      <c r="EG12" s="1"/>
+      <c r="EH12" s="1"/>
+      <c r="EI12" s="1"/>
+      <c r="EJ12" s="1"/>
+      <c r="EK12" s="1"/>
+      <c r="EL12" s="1"/>
+      <c r="EM12" s="1"/>
+      <c r="EN12" s="1"/>
+      <c r="EO12" s="1"/>
+      <c r="EP12" s="1"/>
+      <c r="EQ12" s="1"/>
+      <c r="ER12" s="1"/>
+      <c r="ES12" s="1"/>
+      <c r="ET12" s="1"/>
+      <c r="EU12" s="1"/>
+      <c r="EV12" s="1"/>
+      <c r="EW12" s="1"/>
+      <c r="EX12" s="1"/>
+      <c r="EY12" s="1"/>
+      <c r="EZ12" s="1"/>
+      <c r="FA12" s="1"/>
+      <c r="FB12" s="1"/>
+      <c r="FC12" s="1"/>
+      <c r="FD12" s="1"/>
+      <c r="FE12" s="1"/>
+      <c r="FF12" s="1"/>
+      <c r="FG12" s="1"/>
+      <c r="FH12" s="1"/>
+      <c r="FI12" s="1"/>
+      <c r="FJ12" s="1"/>
+      <c r="FK12" s="1"/>
+      <c r="FL12" s="1"/>
+      <c r="FM12" s="1"/>
+      <c r="FN12" s="1"/>
+      <c r="FO12" s="1"/>
+      <c r="FP12" s="1"/>
+      <c r="FQ12" s="1"/>
+      <c r="FR12" s="1"/>
+      <c r="FS12" s="1"/>
+      <c r="FT12" s="1"/>
+      <c r="FU12" s="1"/>
+      <c r="FV12" s="1"/>
+      <c r="FW12" s="1"/>
+      <c r="FX12" s="1"/>
+      <c r="FY12" s="1"/>
+      <c r="FZ12" s="1"/>
+      <c r="GA12" s="1"/>
+      <c r="GB12" s="1"/>
+      <c r="GC12" s="1"/>
+      <c r="GD12" s="1"/>
+      <c r="GE12" s="1"/>
+      <c r="GF12" s="1"/>
+      <c r="GG12" s="1"/>
+      <c r="GH12" s="1"/>
+      <c r="GI12" s="1"/>
+      <c r="GJ12" s="1"/>
+      <c r="GK12" s="1"/>
+      <c r="GL12" s="1"/>
+      <c r="GM12" s="1"/>
+      <c r="GN12" s="1"/>
+      <c r="GO12" s="1"/>
+      <c r="GP12" s="1"/>
+      <c r="GQ12" s="1"/>
+      <c r="GR12" s="1"/>
+      <c r="GS12" s="1"/>
+      <c r="GT12" s="1"/>
+      <c r="GU12" s="1"/>
+      <c r="GV12" s="1"/>
+      <c r="GW12" s="1"/>
+      <c r="GX12" s="1"/>
+      <c r="GY12" s="1"/>
+      <c r="GZ12" s="1"/>
+      <c r="HA12" s="1"/>
+      <c r="HB12" s="1"/>
+      <c r="HC12" s="1"/>
+      <c r="HD12" s="1"/>
+      <c r="HE12" s="1"/>
+      <c r="HF12" s="1"/>
+      <c r="HG12" s="1"/>
+      <c r="HH12" s="1"/>
+      <c r="HI12" s="1"/>
+      <c r="HJ12" s="1"/>
+      <c r="HK12" s="1"/>
+      <c r="HL12" s="1"/>
+      <c r="HM12" s="1"/>
+      <c r="HN12" s="1"/>
+      <c r="HO12" s="1"/>
+      <c r="HP12" s="1"/>
+      <c r="HQ12" s="1"/>
+      <c r="HR12" s="1"/>
+      <c r="HS12" s="1"/>
+      <c r="HT12" s="1"/>
+      <c r="HU12" s="1"/>
+      <c r="HV12" s="1"/>
+      <c r="HW12" s="1"/>
+      <c r="HX12" s="1"/>
+      <c r="HY12" s="1"/>
+      <c r="HZ12" s="1"/>
+      <c r="IA12" s="1"/>
+      <c r="IB12" s="1"/>
+      <c r="IC12" s="1"/>
+      <c r="ID12" s="1"/>
+      <c r="IE12" s="1"/>
+      <c r="IF12" s="1"/>
+      <c r="IG12" s="1"/>
+      <c r="IH12" s="1"/>
+      <c r="II12" s="1"/>
+      <c r="IJ12" s="1"/>
+      <c r="IK12" s="1"/>
+      <c r="IL12" s="1"/>
+      <c r="IM12" s="1"/>
+      <c r="IN12" s="1"/>
+      <c r="IO12" s="1"/>
+      <c r="IP12" s="1"/>
+      <c r="IQ12" s="1"/>
+      <c r="IR12" s="1"/>
+      <c r="IS12" s="1"/>
+      <c r="IT12" s="1"/>
+      <c r="IU12" s="1"/>
+      <c r="IV12" s="1"/>
+      <c r="IW12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98"/>
       <c r="B13" s="114" t="s">
         <v>64</v>
@@ -8670,8 +12151,241 @@
       <c r="V13" s="5"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-    </row>
-    <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+      <c r="AO13" s="1"/>
+      <c r="AP13" s="1"/>
+      <c r="AQ13" s="1"/>
+      <c r="AR13" s="1"/>
+      <c r="AS13" s="1"/>
+      <c r="AT13" s="1"/>
+      <c r="AU13" s="1"/>
+      <c r="AV13" s="1"/>
+      <c r="AW13" s="1"/>
+      <c r="AX13" s="1"/>
+      <c r="AY13" s="1"/>
+      <c r="AZ13" s="1"/>
+      <c r="BA13" s="1"/>
+      <c r="BB13" s="1"/>
+      <c r="BC13" s="1"/>
+      <c r="BD13" s="1"/>
+      <c r="BE13" s="1"/>
+      <c r="BF13" s="1"/>
+      <c r="BG13" s="1"/>
+      <c r="BH13" s="1"/>
+      <c r="BI13" s="1"/>
+      <c r="BJ13" s="1"/>
+      <c r="BK13" s="1"/>
+      <c r="BL13" s="1"/>
+      <c r="BM13" s="1"/>
+      <c r="BN13" s="1"/>
+      <c r="BO13" s="1"/>
+      <c r="BP13" s="1"/>
+      <c r="BQ13" s="1"/>
+      <c r="BR13" s="1"/>
+      <c r="BS13" s="1"/>
+      <c r="BT13" s="1"/>
+      <c r="BU13" s="1"/>
+      <c r="BV13" s="1"/>
+      <c r="BW13" s="1"/>
+      <c r="BX13" s="1"/>
+      <c r="BY13" s="1"/>
+      <c r="BZ13" s="1"/>
+      <c r="CA13" s="1"/>
+      <c r="CB13" s="1"/>
+      <c r="CC13" s="1"/>
+      <c r="CD13" s="1"/>
+      <c r="CE13" s="1"/>
+      <c r="CF13" s="1"/>
+      <c r="CG13" s="1"/>
+      <c r="CH13" s="1"/>
+      <c r="CI13" s="1"/>
+      <c r="CJ13" s="1"/>
+      <c r="CK13" s="1"/>
+      <c r="CL13" s="1"/>
+      <c r="CM13" s="1"/>
+      <c r="CN13" s="1"/>
+      <c r="CO13" s="1"/>
+      <c r="CP13" s="1"/>
+      <c r="CQ13" s="1"/>
+      <c r="CR13" s="1"/>
+      <c r="CS13" s="1"/>
+      <c r="CT13" s="1"/>
+      <c r="CU13" s="1"/>
+      <c r="CV13" s="1"/>
+      <c r="CW13" s="1"/>
+      <c r="CX13" s="1"/>
+      <c r="CY13" s="1"/>
+      <c r="CZ13" s="1"/>
+      <c r="DA13" s="1"/>
+      <c r="DB13" s="1"/>
+      <c r="DC13" s="1"/>
+      <c r="DD13" s="1"/>
+      <c r="DE13" s="1"/>
+      <c r="DF13" s="1"/>
+      <c r="DG13" s="1"/>
+      <c r="DH13" s="1"/>
+      <c r="DI13" s="1"/>
+      <c r="DJ13" s="1"/>
+      <c r="DK13" s="1"/>
+      <c r="DL13" s="1"/>
+      <c r="DM13" s="1"/>
+      <c r="DN13" s="1"/>
+      <c r="DO13" s="1"/>
+      <c r="DP13" s="1"/>
+      <c r="DQ13" s="1"/>
+      <c r="DR13" s="1"/>
+      <c r="DS13" s="1"/>
+      <c r="DT13" s="1"/>
+      <c r="DU13" s="1"/>
+      <c r="DV13" s="1"/>
+      <c r="DW13" s="1"/>
+      <c r="DX13" s="1"/>
+      <c r="DY13" s="1"/>
+      <c r="DZ13" s="1"/>
+      <c r="EA13" s="1"/>
+      <c r="EB13" s="1"/>
+      <c r="EC13" s="1"/>
+      <c r="ED13" s="1"/>
+      <c r="EE13" s="1"/>
+      <c r="EF13" s="1"/>
+      <c r="EG13" s="1"/>
+      <c r="EH13" s="1"/>
+      <c r="EI13" s="1"/>
+      <c r="EJ13" s="1"/>
+      <c r="EK13" s="1"/>
+      <c r="EL13" s="1"/>
+      <c r="EM13" s="1"/>
+      <c r="EN13" s="1"/>
+      <c r="EO13" s="1"/>
+      <c r="EP13" s="1"/>
+      <c r="EQ13" s="1"/>
+      <c r="ER13" s="1"/>
+      <c r="ES13" s="1"/>
+      <c r="ET13" s="1"/>
+      <c r="EU13" s="1"/>
+      <c r="EV13" s="1"/>
+      <c r="EW13" s="1"/>
+      <c r="EX13" s="1"/>
+      <c r="EY13" s="1"/>
+      <c r="EZ13" s="1"/>
+      <c r="FA13" s="1"/>
+      <c r="FB13" s="1"/>
+      <c r="FC13" s="1"/>
+      <c r="FD13" s="1"/>
+      <c r="FE13" s="1"/>
+      <c r="FF13" s="1"/>
+      <c r="FG13" s="1"/>
+      <c r="FH13" s="1"/>
+      <c r="FI13" s="1"/>
+      <c r="FJ13" s="1"/>
+      <c r="FK13" s="1"/>
+      <c r="FL13" s="1"/>
+      <c r="FM13" s="1"/>
+      <c r="FN13" s="1"/>
+      <c r="FO13" s="1"/>
+      <c r="FP13" s="1"/>
+      <c r="FQ13" s="1"/>
+      <c r="FR13" s="1"/>
+      <c r="FS13" s="1"/>
+      <c r="FT13" s="1"/>
+      <c r="FU13" s="1"/>
+      <c r="FV13" s="1"/>
+      <c r="FW13" s="1"/>
+      <c r="FX13" s="1"/>
+      <c r="FY13" s="1"/>
+      <c r="FZ13" s="1"/>
+      <c r="GA13" s="1"/>
+      <c r="GB13" s="1"/>
+      <c r="GC13" s="1"/>
+      <c r="GD13" s="1"/>
+      <c r="GE13" s="1"/>
+      <c r="GF13" s="1"/>
+      <c r="GG13" s="1"/>
+      <c r="GH13" s="1"/>
+      <c r="GI13" s="1"/>
+      <c r="GJ13" s="1"/>
+      <c r="GK13" s="1"/>
+      <c r="GL13" s="1"/>
+      <c r="GM13" s="1"/>
+      <c r="GN13" s="1"/>
+      <c r="GO13" s="1"/>
+      <c r="GP13" s="1"/>
+      <c r="GQ13" s="1"/>
+      <c r="GR13" s="1"/>
+      <c r="GS13" s="1"/>
+      <c r="GT13" s="1"/>
+      <c r="GU13" s="1"/>
+      <c r="GV13" s="1"/>
+      <c r="GW13" s="1"/>
+      <c r="GX13" s="1"/>
+      <c r="GY13" s="1"/>
+      <c r="GZ13" s="1"/>
+      <c r="HA13" s="1"/>
+      <c r="HB13" s="1"/>
+      <c r="HC13" s="1"/>
+      <c r="HD13" s="1"/>
+      <c r="HE13" s="1"/>
+      <c r="HF13" s="1"/>
+      <c r="HG13" s="1"/>
+      <c r="HH13" s="1"/>
+      <c r="HI13" s="1"/>
+      <c r="HJ13" s="1"/>
+      <c r="HK13" s="1"/>
+      <c r="HL13" s="1"/>
+      <c r="HM13" s="1"/>
+      <c r="HN13" s="1"/>
+      <c r="HO13" s="1"/>
+      <c r="HP13" s="1"/>
+      <c r="HQ13" s="1"/>
+      <c r="HR13" s="1"/>
+      <c r="HS13" s="1"/>
+      <c r="HT13" s="1"/>
+      <c r="HU13" s="1"/>
+      <c r="HV13" s="1"/>
+      <c r="HW13" s="1"/>
+      <c r="HX13" s="1"/>
+      <c r="HY13" s="1"/>
+      <c r="HZ13" s="1"/>
+      <c r="IA13" s="1"/>
+      <c r="IB13" s="1"/>
+      <c r="IC13" s="1"/>
+      <c r="ID13" s="1"/>
+      <c r="IE13" s="1"/>
+      <c r="IF13" s="1"/>
+      <c r="IG13" s="1"/>
+      <c r="IH13" s="1"/>
+      <c r="II13" s="1"/>
+      <c r="IJ13" s="1"/>
+      <c r="IK13" s="1"/>
+      <c r="IL13" s="1"/>
+      <c r="IM13" s="1"/>
+      <c r="IN13" s="1"/>
+      <c r="IO13" s="1"/>
+      <c r="IP13" s="1"/>
+      <c r="IQ13" s="1"/>
+      <c r="IR13" s="1"/>
+      <c r="IS13" s="1"/>
+      <c r="IT13" s="1"/>
+      <c r="IU13" s="1"/>
+      <c r="IV13" s="1"/>
+      <c r="IW13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="98"/>
       <c r="B14" s="99"/>
       <c r="C14" s="100"/>
@@ -8696,8 +12410,241 @@
       <c r="V14" s="5"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-    </row>
-    <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="1"/>
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="1"/>
+      <c r="AR14" s="1"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="1"/>
+      <c r="AU14" s="1"/>
+      <c r="AV14" s="1"/>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="1"/>
+      <c r="AZ14" s="1"/>
+      <c r="BA14" s="1"/>
+      <c r="BB14" s="1"/>
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1"/>
+      <c r="BE14" s="1"/>
+      <c r="BF14" s="1"/>
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="1"/>
+      <c r="BI14" s="1"/>
+      <c r="BJ14" s="1"/>
+      <c r="BK14" s="1"/>
+      <c r="BL14" s="1"/>
+      <c r="BM14" s="1"/>
+      <c r="BN14" s="1"/>
+      <c r="BO14" s="1"/>
+      <c r="BP14" s="1"/>
+      <c r="BQ14" s="1"/>
+      <c r="BR14" s="1"/>
+      <c r="BS14" s="1"/>
+      <c r="BT14" s="1"/>
+      <c r="BU14" s="1"/>
+      <c r="BV14" s="1"/>
+      <c r="BW14" s="1"/>
+      <c r="BX14" s="1"/>
+      <c r="BY14" s="1"/>
+      <c r="BZ14" s="1"/>
+      <c r="CA14" s="1"/>
+      <c r="CB14" s="1"/>
+      <c r="CC14" s="1"/>
+      <c r="CD14" s="1"/>
+      <c r="CE14" s="1"/>
+      <c r="CF14" s="1"/>
+      <c r="CG14" s="1"/>
+      <c r="CH14" s="1"/>
+      <c r="CI14" s="1"/>
+      <c r="CJ14" s="1"/>
+      <c r="CK14" s="1"/>
+      <c r="CL14" s="1"/>
+      <c r="CM14" s="1"/>
+      <c r="CN14" s="1"/>
+      <c r="CO14" s="1"/>
+      <c r="CP14" s="1"/>
+      <c r="CQ14" s="1"/>
+      <c r="CR14" s="1"/>
+      <c r="CS14" s="1"/>
+      <c r="CT14" s="1"/>
+      <c r="CU14" s="1"/>
+      <c r="CV14" s="1"/>
+      <c r="CW14" s="1"/>
+      <c r="CX14" s="1"/>
+      <c r="CY14" s="1"/>
+      <c r="CZ14" s="1"/>
+      <c r="DA14" s="1"/>
+      <c r="DB14" s="1"/>
+      <c r="DC14" s="1"/>
+      <c r="DD14" s="1"/>
+      <c r="DE14" s="1"/>
+      <c r="DF14" s="1"/>
+      <c r="DG14" s="1"/>
+      <c r="DH14" s="1"/>
+      <c r="DI14" s="1"/>
+      <c r="DJ14" s="1"/>
+      <c r="DK14" s="1"/>
+      <c r="DL14" s="1"/>
+      <c r="DM14" s="1"/>
+      <c r="DN14" s="1"/>
+      <c r="DO14" s="1"/>
+      <c r="DP14" s="1"/>
+      <c r="DQ14" s="1"/>
+      <c r="DR14" s="1"/>
+      <c r="DS14" s="1"/>
+      <c r="DT14" s="1"/>
+      <c r="DU14" s="1"/>
+      <c r="DV14" s="1"/>
+      <c r="DW14" s="1"/>
+      <c r="DX14" s="1"/>
+      <c r="DY14" s="1"/>
+      <c r="DZ14" s="1"/>
+      <c r="EA14" s="1"/>
+      <c r="EB14" s="1"/>
+      <c r="EC14" s="1"/>
+      <c r="ED14" s="1"/>
+      <c r="EE14" s="1"/>
+      <c r="EF14" s="1"/>
+      <c r="EG14" s="1"/>
+      <c r="EH14" s="1"/>
+      <c r="EI14" s="1"/>
+      <c r="EJ14" s="1"/>
+      <c r="EK14" s="1"/>
+      <c r="EL14" s="1"/>
+      <c r="EM14" s="1"/>
+      <c r="EN14" s="1"/>
+      <c r="EO14" s="1"/>
+      <c r="EP14" s="1"/>
+      <c r="EQ14" s="1"/>
+      <c r="ER14" s="1"/>
+      <c r="ES14" s="1"/>
+      <c r="ET14" s="1"/>
+      <c r="EU14" s="1"/>
+      <c r="EV14" s="1"/>
+      <c r="EW14" s="1"/>
+      <c r="EX14" s="1"/>
+      <c r="EY14" s="1"/>
+      <c r="EZ14" s="1"/>
+      <c r="FA14" s="1"/>
+      <c r="FB14" s="1"/>
+      <c r="FC14" s="1"/>
+      <c r="FD14" s="1"/>
+      <c r="FE14" s="1"/>
+      <c r="FF14" s="1"/>
+      <c r="FG14" s="1"/>
+      <c r="FH14" s="1"/>
+      <c r="FI14" s="1"/>
+      <c r="FJ14" s="1"/>
+      <c r="FK14" s="1"/>
+      <c r="FL14" s="1"/>
+      <c r="FM14" s="1"/>
+      <c r="FN14" s="1"/>
+      <c r="FO14" s="1"/>
+      <c r="FP14" s="1"/>
+      <c r="FQ14" s="1"/>
+      <c r="FR14" s="1"/>
+      <c r="FS14" s="1"/>
+      <c r="FT14" s="1"/>
+      <c r="FU14" s="1"/>
+      <c r="FV14" s="1"/>
+      <c r="FW14" s="1"/>
+      <c r="FX14" s="1"/>
+      <c r="FY14" s="1"/>
+      <c r="FZ14" s="1"/>
+      <c r="GA14" s="1"/>
+      <c r="GB14" s="1"/>
+      <c r="GC14" s="1"/>
+      <c r="GD14" s="1"/>
+      <c r="GE14" s="1"/>
+      <c r="GF14" s="1"/>
+      <c r="GG14" s="1"/>
+      <c r="GH14" s="1"/>
+      <c r="GI14" s="1"/>
+      <c r="GJ14" s="1"/>
+      <c r="GK14" s="1"/>
+      <c r="GL14" s="1"/>
+      <c r="GM14" s="1"/>
+      <c r="GN14" s="1"/>
+      <c r="GO14" s="1"/>
+      <c r="GP14" s="1"/>
+      <c r="GQ14" s="1"/>
+      <c r="GR14" s="1"/>
+      <c r="GS14" s="1"/>
+      <c r="GT14" s="1"/>
+      <c r="GU14" s="1"/>
+      <c r="GV14" s="1"/>
+      <c r="GW14" s="1"/>
+      <c r="GX14" s="1"/>
+      <c r="GY14" s="1"/>
+      <c r="GZ14" s="1"/>
+      <c r="HA14" s="1"/>
+      <c r="HB14" s="1"/>
+      <c r="HC14" s="1"/>
+      <c r="HD14" s="1"/>
+      <c r="HE14" s="1"/>
+      <c r="HF14" s="1"/>
+      <c r="HG14" s="1"/>
+      <c r="HH14" s="1"/>
+      <c r="HI14" s="1"/>
+      <c r="HJ14" s="1"/>
+      <c r="HK14" s="1"/>
+      <c r="HL14" s="1"/>
+      <c r="HM14" s="1"/>
+      <c r="HN14" s="1"/>
+      <c r="HO14" s="1"/>
+      <c r="HP14" s="1"/>
+      <c r="HQ14" s="1"/>
+      <c r="HR14" s="1"/>
+      <c r="HS14" s="1"/>
+      <c r="HT14" s="1"/>
+      <c r="HU14" s="1"/>
+      <c r="HV14" s="1"/>
+      <c r="HW14" s="1"/>
+      <c r="HX14" s="1"/>
+      <c r="HY14" s="1"/>
+      <c r="HZ14" s="1"/>
+      <c r="IA14" s="1"/>
+      <c r="IB14" s="1"/>
+      <c r="IC14" s="1"/>
+      <c r="ID14" s="1"/>
+      <c r="IE14" s="1"/>
+      <c r="IF14" s="1"/>
+      <c r="IG14" s="1"/>
+      <c r="IH14" s="1"/>
+      <c r="II14" s="1"/>
+      <c r="IJ14" s="1"/>
+      <c r="IK14" s="1"/>
+      <c r="IL14" s="1"/>
+      <c r="IM14" s="1"/>
+      <c r="IN14" s="1"/>
+      <c r="IO14" s="1"/>
+      <c r="IP14" s="1"/>
+      <c r="IQ14" s="1"/>
+      <c r="IR14" s="1"/>
+      <c r="IS14" s="1"/>
+      <c r="IT14" s="1"/>
+      <c r="IU14" s="1"/>
+      <c r="IV14" s="1"/>
+      <c r="IW14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="98"/>
       <c r="B15" s="118" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
@@ -8734,8 +12681,241 @@
       <c r="V15" s="5"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-    </row>
-    <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+      <c r="AP15" s="1"/>
+      <c r="AQ15" s="1"/>
+      <c r="AR15" s="1"/>
+      <c r="AS15" s="1"/>
+      <c r="AT15" s="1"/>
+      <c r="AU15" s="1"/>
+      <c r="AV15" s="1"/>
+      <c r="AW15" s="1"/>
+      <c r="AX15" s="1"/>
+      <c r="AY15" s="1"/>
+      <c r="AZ15" s="1"/>
+      <c r="BA15" s="1"/>
+      <c r="BB15" s="1"/>
+      <c r="BC15" s="1"/>
+      <c r="BD15" s="1"/>
+      <c r="BE15" s="1"/>
+      <c r="BF15" s="1"/>
+      <c r="BG15" s="1"/>
+      <c r="BH15" s="1"/>
+      <c r="BI15" s="1"/>
+      <c r="BJ15" s="1"/>
+      <c r="BK15" s="1"/>
+      <c r="BL15" s="1"/>
+      <c r="BM15" s="1"/>
+      <c r="BN15" s="1"/>
+      <c r="BO15" s="1"/>
+      <c r="BP15" s="1"/>
+      <c r="BQ15" s="1"/>
+      <c r="BR15" s="1"/>
+      <c r="BS15" s="1"/>
+      <c r="BT15" s="1"/>
+      <c r="BU15" s="1"/>
+      <c r="BV15" s="1"/>
+      <c r="BW15" s="1"/>
+      <c r="BX15" s="1"/>
+      <c r="BY15" s="1"/>
+      <c r="BZ15" s="1"/>
+      <c r="CA15" s="1"/>
+      <c r="CB15" s="1"/>
+      <c r="CC15" s="1"/>
+      <c r="CD15" s="1"/>
+      <c r="CE15" s="1"/>
+      <c r="CF15" s="1"/>
+      <c r="CG15" s="1"/>
+      <c r="CH15" s="1"/>
+      <c r="CI15" s="1"/>
+      <c r="CJ15" s="1"/>
+      <c r="CK15" s="1"/>
+      <c r="CL15" s="1"/>
+      <c r="CM15" s="1"/>
+      <c r="CN15" s="1"/>
+      <c r="CO15" s="1"/>
+      <c r="CP15" s="1"/>
+      <c r="CQ15" s="1"/>
+      <c r="CR15" s="1"/>
+      <c r="CS15" s="1"/>
+      <c r="CT15" s="1"/>
+      <c r="CU15" s="1"/>
+      <c r="CV15" s="1"/>
+      <c r="CW15" s="1"/>
+      <c r="CX15" s="1"/>
+      <c r="CY15" s="1"/>
+      <c r="CZ15" s="1"/>
+      <c r="DA15" s="1"/>
+      <c r="DB15" s="1"/>
+      <c r="DC15" s="1"/>
+      <c r="DD15" s="1"/>
+      <c r="DE15" s="1"/>
+      <c r="DF15" s="1"/>
+      <c r="DG15" s="1"/>
+      <c r="DH15" s="1"/>
+      <c r="DI15" s="1"/>
+      <c r="DJ15" s="1"/>
+      <c r="DK15" s="1"/>
+      <c r="DL15" s="1"/>
+      <c r="DM15" s="1"/>
+      <c r="DN15" s="1"/>
+      <c r="DO15" s="1"/>
+      <c r="DP15" s="1"/>
+      <c r="DQ15" s="1"/>
+      <c r="DR15" s="1"/>
+      <c r="DS15" s="1"/>
+      <c r="DT15" s="1"/>
+      <c r="DU15" s="1"/>
+      <c r="DV15" s="1"/>
+      <c r="DW15" s="1"/>
+      <c r="DX15" s="1"/>
+      <c r="DY15" s="1"/>
+      <c r="DZ15" s="1"/>
+      <c r="EA15" s="1"/>
+      <c r="EB15" s="1"/>
+      <c r="EC15" s="1"/>
+      <c r="ED15" s="1"/>
+      <c r="EE15" s="1"/>
+      <c r="EF15" s="1"/>
+      <c r="EG15" s="1"/>
+      <c r="EH15" s="1"/>
+      <c r="EI15" s="1"/>
+      <c r="EJ15" s="1"/>
+      <c r="EK15" s="1"/>
+      <c r="EL15" s="1"/>
+      <c r="EM15" s="1"/>
+      <c r="EN15" s="1"/>
+      <c r="EO15" s="1"/>
+      <c r="EP15" s="1"/>
+      <c r="EQ15" s="1"/>
+      <c r="ER15" s="1"/>
+      <c r="ES15" s="1"/>
+      <c r="ET15" s="1"/>
+      <c r="EU15" s="1"/>
+      <c r="EV15" s="1"/>
+      <c r="EW15" s="1"/>
+      <c r="EX15" s="1"/>
+      <c r="EY15" s="1"/>
+      <c r="EZ15" s="1"/>
+      <c r="FA15" s="1"/>
+      <c r="FB15" s="1"/>
+      <c r="FC15" s="1"/>
+      <c r="FD15" s="1"/>
+      <c r="FE15" s="1"/>
+      <c r="FF15" s="1"/>
+      <c r="FG15" s="1"/>
+      <c r="FH15" s="1"/>
+      <c r="FI15" s="1"/>
+      <c r="FJ15" s="1"/>
+      <c r="FK15" s="1"/>
+      <c r="FL15" s="1"/>
+      <c r="FM15" s="1"/>
+      <c r="FN15" s="1"/>
+      <c r="FO15" s="1"/>
+      <c r="FP15" s="1"/>
+      <c r="FQ15" s="1"/>
+      <c r="FR15" s="1"/>
+      <c r="FS15" s="1"/>
+      <c r="FT15" s="1"/>
+      <c r="FU15" s="1"/>
+      <c r="FV15" s="1"/>
+      <c r="FW15" s="1"/>
+      <c r="FX15" s="1"/>
+      <c r="FY15" s="1"/>
+      <c r="FZ15" s="1"/>
+      <c r="GA15" s="1"/>
+      <c r="GB15" s="1"/>
+      <c r="GC15" s="1"/>
+      <c r="GD15" s="1"/>
+      <c r="GE15" s="1"/>
+      <c r="GF15" s="1"/>
+      <c r="GG15" s="1"/>
+      <c r="GH15" s="1"/>
+      <c r="GI15" s="1"/>
+      <c r="GJ15" s="1"/>
+      <c r="GK15" s="1"/>
+      <c r="GL15" s="1"/>
+      <c r="GM15" s="1"/>
+      <c r="GN15" s="1"/>
+      <c r="GO15" s="1"/>
+      <c r="GP15" s="1"/>
+      <c r="GQ15" s="1"/>
+      <c r="GR15" s="1"/>
+      <c r="GS15" s="1"/>
+      <c r="GT15" s="1"/>
+      <c r="GU15" s="1"/>
+      <c r="GV15" s="1"/>
+      <c r="GW15" s="1"/>
+      <c r="GX15" s="1"/>
+      <c r="GY15" s="1"/>
+      <c r="GZ15" s="1"/>
+      <c r="HA15" s="1"/>
+      <c r="HB15" s="1"/>
+      <c r="HC15" s="1"/>
+      <c r="HD15" s="1"/>
+      <c r="HE15" s="1"/>
+      <c r="HF15" s="1"/>
+      <c r="HG15" s="1"/>
+      <c r="HH15" s="1"/>
+      <c r="HI15" s="1"/>
+      <c r="HJ15" s="1"/>
+      <c r="HK15" s="1"/>
+      <c r="HL15" s="1"/>
+      <c r="HM15" s="1"/>
+      <c r="HN15" s="1"/>
+      <c r="HO15" s="1"/>
+      <c r="HP15" s="1"/>
+      <c r="HQ15" s="1"/>
+      <c r="HR15" s="1"/>
+      <c r="HS15" s="1"/>
+      <c r="HT15" s="1"/>
+      <c r="HU15" s="1"/>
+      <c r="HV15" s="1"/>
+      <c r="HW15" s="1"/>
+      <c r="HX15" s="1"/>
+      <c r="HY15" s="1"/>
+      <c r="HZ15" s="1"/>
+      <c r="IA15" s="1"/>
+      <c r="IB15" s="1"/>
+      <c r="IC15" s="1"/>
+      <c r="ID15" s="1"/>
+      <c r="IE15" s="1"/>
+      <c r="IF15" s="1"/>
+      <c r="IG15" s="1"/>
+      <c r="IH15" s="1"/>
+      <c r="II15" s="1"/>
+      <c r="IJ15" s="1"/>
+      <c r="IK15" s="1"/>
+      <c r="IL15" s="1"/>
+      <c r="IM15" s="1"/>
+      <c r="IN15" s="1"/>
+      <c r="IO15" s="1"/>
+      <c r="IP15" s="1"/>
+      <c r="IQ15" s="1"/>
+      <c r="IR15" s="1"/>
+      <c r="IS15" s="1"/>
+      <c r="IT15" s="1"/>
+      <c r="IU15" s="1"/>
+      <c r="IV15" s="1"/>
+      <c r="IW15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="120"/>
       <c r="B16" s="121"/>
       <c r="C16" s="122"/>
@@ -8760,6 +12940,239 @@
       <c r="V16" s="5"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="1"/>
+      <c r="AP16" s="1"/>
+      <c r="AQ16" s="1"/>
+      <c r="AR16" s="1"/>
+      <c r="AS16" s="1"/>
+      <c r="AT16" s="1"/>
+      <c r="AU16" s="1"/>
+      <c r="AV16" s="1"/>
+      <c r="AW16" s="1"/>
+      <c r="AX16" s="1"/>
+      <c r="AY16" s="1"/>
+      <c r="AZ16" s="1"/>
+      <c r="BA16" s="1"/>
+      <c r="BB16" s="1"/>
+      <c r="BC16" s="1"/>
+      <c r="BD16" s="1"/>
+      <c r="BE16" s="1"/>
+      <c r="BF16" s="1"/>
+      <c r="BG16" s="1"/>
+      <c r="BH16" s="1"/>
+      <c r="BI16" s="1"/>
+      <c r="BJ16" s="1"/>
+      <c r="BK16" s="1"/>
+      <c r="BL16" s="1"/>
+      <c r="BM16" s="1"/>
+      <c r="BN16" s="1"/>
+      <c r="BO16" s="1"/>
+      <c r="BP16" s="1"/>
+      <c r="BQ16" s="1"/>
+      <c r="BR16" s="1"/>
+      <c r="BS16" s="1"/>
+      <c r="BT16" s="1"/>
+      <c r="BU16" s="1"/>
+      <c r="BV16" s="1"/>
+      <c r="BW16" s="1"/>
+      <c r="BX16" s="1"/>
+      <c r="BY16" s="1"/>
+      <c r="BZ16" s="1"/>
+      <c r="CA16" s="1"/>
+      <c r="CB16" s="1"/>
+      <c r="CC16" s="1"/>
+      <c r="CD16" s="1"/>
+      <c r="CE16" s="1"/>
+      <c r="CF16" s="1"/>
+      <c r="CG16" s="1"/>
+      <c r="CH16" s="1"/>
+      <c r="CI16" s="1"/>
+      <c r="CJ16" s="1"/>
+      <c r="CK16" s="1"/>
+      <c r="CL16" s="1"/>
+      <c r="CM16" s="1"/>
+      <c r="CN16" s="1"/>
+      <c r="CO16" s="1"/>
+      <c r="CP16" s="1"/>
+      <c r="CQ16" s="1"/>
+      <c r="CR16" s="1"/>
+      <c r="CS16" s="1"/>
+      <c r="CT16" s="1"/>
+      <c r="CU16" s="1"/>
+      <c r="CV16" s="1"/>
+      <c r="CW16" s="1"/>
+      <c r="CX16" s="1"/>
+      <c r="CY16" s="1"/>
+      <c r="CZ16" s="1"/>
+      <c r="DA16" s="1"/>
+      <c r="DB16" s="1"/>
+      <c r="DC16" s="1"/>
+      <c r="DD16" s="1"/>
+      <c r="DE16" s="1"/>
+      <c r="DF16" s="1"/>
+      <c r="DG16" s="1"/>
+      <c r="DH16" s="1"/>
+      <c r="DI16" s="1"/>
+      <c r="DJ16" s="1"/>
+      <c r="DK16" s="1"/>
+      <c r="DL16" s="1"/>
+      <c r="DM16" s="1"/>
+      <c r="DN16" s="1"/>
+      <c r="DO16" s="1"/>
+      <c r="DP16" s="1"/>
+      <c r="DQ16" s="1"/>
+      <c r="DR16" s="1"/>
+      <c r="DS16" s="1"/>
+      <c r="DT16" s="1"/>
+      <c r="DU16" s="1"/>
+      <c r="DV16" s="1"/>
+      <c r="DW16" s="1"/>
+      <c r="DX16" s="1"/>
+      <c r="DY16" s="1"/>
+      <c r="DZ16" s="1"/>
+      <c r="EA16" s="1"/>
+      <c r="EB16" s="1"/>
+      <c r="EC16" s="1"/>
+      <c r="ED16" s="1"/>
+      <c r="EE16" s="1"/>
+      <c r="EF16" s="1"/>
+      <c r="EG16" s="1"/>
+      <c r="EH16" s="1"/>
+      <c r="EI16" s="1"/>
+      <c r="EJ16" s="1"/>
+      <c r="EK16" s="1"/>
+      <c r="EL16" s="1"/>
+      <c r="EM16" s="1"/>
+      <c r="EN16" s="1"/>
+      <c r="EO16" s="1"/>
+      <c r="EP16" s="1"/>
+      <c r="EQ16" s="1"/>
+      <c r="ER16" s="1"/>
+      <c r="ES16" s="1"/>
+      <c r="ET16" s="1"/>
+      <c r="EU16" s="1"/>
+      <c r="EV16" s="1"/>
+      <c r="EW16" s="1"/>
+      <c r="EX16" s="1"/>
+      <c r="EY16" s="1"/>
+      <c r="EZ16" s="1"/>
+      <c r="FA16" s="1"/>
+      <c r="FB16" s="1"/>
+      <c r="FC16" s="1"/>
+      <c r="FD16" s="1"/>
+      <c r="FE16" s="1"/>
+      <c r="FF16" s="1"/>
+      <c r="FG16" s="1"/>
+      <c r="FH16" s="1"/>
+      <c r="FI16" s="1"/>
+      <c r="FJ16" s="1"/>
+      <c r="FK16" s="1"/>
+      <c r="FL16" s="1"/>
+      <c r="FM16" s="1"/>
+      <c r="FN16" s="1"/>
+      <c r="FO16" s="1"/>
+      <c r="FP16" s="1"/>
+      <c r="FQ16" s="1"/>
+      <c r="FR16" s="1"/>
+      <c r="FS16" s="1"/>
+      <c r="FT16" s="1"/>
+      <c r="FU16" s="1"/>
+      <c r="FV16" s="1"/>
+      <c r="FW16" s="1"/>
+      <c r="FX16" s="1"/>
+      <c r="FY16" s="1"/>
+      <c r="FZ16" s="1"/>
+      <c r="GA16" s="1"/>
+      <c r="GB16" s="1"/>
+      <c r="GC16" s="1"/>
+      <c r="GD16" s="1"/>
+      <c r="GE16" s="1"/>
+      <c r="GF16" s="1"/>
+      <c r="GG16" s="1"/>
+      <c r="GH16" s="1"/>
+      <c r="GI16" s="1"/>
+      <c r="GJ16" s="1"/>
+      <c r="GK16" s="1"/>
+      <c r="GL16" s="1"/>
+      <c r="GM16" s="1"/>
+      <c r="GN16" s="1"/>
+      <c r="GO16" s="1"/>
+      <c r="GP16" s="1"/>
+      <c r="GQ16" s="1"/>
+      <c r="GR16" s="1"/>
+      <c r="GS16" s="1"/>
+      <c r="GT16" s="1"/>
+      <c r="GU16" s="1"/>
+      <c r="GV16" s="1"/>
+      <c r="GW16" s="1"/>
+      <c r="GX16" s="1"/>
+      <c r="GY16" s="1"/>
+      <c r="GZ16" s="1"/>
+      <c r="HA16" s="1"/>
+      <c r="HB16" s="1"/>
+      <c r="HC16" s="1"/>
+      <c r="HD16" s="1"/>
+      <c r="HE16" s="1"/>
+      <c r="HF16" s="1"/>
+      <c r="HG16" s="1"/>
+      <c r="HH16" s="1"/>
+      <c r="HI16" s="1"/>
+      <c r="HJ16" s="1"/>
+      <c r="HK16" s="1"/>
+      <c r="HL16" s="1"/>
+      <c r="HM16" s="1"/>
+      <c r="HN16" s="1"/>
+      <c r="HO16" s="1"/>
+      <c r="HP16" s="1"/>
+      <c r="HQ16" s="1"/>
+      <c r="HR16" s="1"/>
+      <c r="HS16" s="1"/>
+      <c r="HT16" s="1"/>
+      <c r="HU16" s="1"/>
+      <c r="HV16" s="1"/>
+      <c r="HW16" s="1"/>
+      <c r="HX16" s="1"/>
+      <c r="HY16" s="1"/>
+      <c r="HZ16" s="1"/>
+      <c r="IA16" s="1"/>
+      <c r="IB16" s="1"/>
+      <c r="IC16" s="1"/>
+      <c r="ID16" s="1"/>
+      <c r="IE16" s="1"/>
+      <c r="IF16" s="1"/>
+      <c r="IG16" s="1"/>
+      <c r="IH16" s="1"/>
+      <c r="II16" s="1"/>
+      <c r="IJ16" s="1"/>
+      <c r="IK16" s="1"/>
+      <c r="IL16" s="1"/>
+      <c r="IM16" s="1"/>
+      <c r="IN16" s="1"/>
+      <c r="IO16" s="1"/>
+      <c r="IP16" s="1"/>
+      <c r="IQ16" s="1"/>
+      <c r="IR16" s="1"/>
+      <c r="IS16" s="1"/>
+      <c r="IT16" s="1"/>
+      <c r="IU16" s="1"/>
+      <c r="IV16" s="1"/>
+      <c r="IW16" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -8799,8 +13212,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW30"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
@@ -8883,7 +13296,7 @@
       <c r="L4" s="139"/>
       <c r="M4" s="129"/>
     </row>
-    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
         <v>69</v>
@@ -8915,8 +13328,252 @@
         <v>77</v>
       </c>
       <c r="M5" s="140"/>
-    </row>
-    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N5" s="142"/>
+      <c r="O5" s="142"/>
+      <c r="P5" s="142"/>
+      <c r="Q5" s="142"/>
+      <c r="R5" s="142"/>
+      <c r="S5" s="142"/>
+      <c r="T5" s="142"/>
+      <c r="U5" s="142"/>
+      <c r="V5" s="142"/>
+      <c r="W5" s="142"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="142"/>
+      <c r="Z5" s="142"/>
+      <c r="AA5" s="142"/>
+      <c r="AB5" s="142"/>
+      <c r="AC5" s="142"/>
+      <c r="AD5" s="142"/>
+      <c r="AE5" s="142"/>
+      <c r="AF5" s="142"/>
+      <c r="AG5" s="142"/>
+      <c r="AH5" s="142"/>
+      <c r="AI5" s="142"/>
+      <c r="AJ5" s="142"/>
+      <c r="AK5" s="142"/>
+      <c r="AL5" s="142"/>
+      <c r="AM5" s="142"/>
+      <c r="AN5" s="142"/>
+      <c r="AO5" s="142"/>
+      <c r="AP5" s="142"/>
+      <c r="AQ5" s="142"/>
+      <c r="AR5" s="142"/>
+      <c r="AS5" s="142"/>
+      <c r="AT5" s="142"/>
+      <c r="AU5" s="142"/>
+      <c r="AV5" s="142"/>
+      <c r="AW5" s="142"/>
+      <c r="AX5" s="142"/>
+      <c r="AY5" s="142"/>
+      <c r="AZ5" s="142"/>
+      <c r="BA5" s="142"/>
+      <c r="BB5" s="142"/>
+      <c r="BC5" s="142"/>
+      <c r="BD5" s="142"/>
+      <c r="BE5" s="142"/>
+      <c r="BF5" s="142"/>
+      <c r="BG5" s="142"/>
+      <c r="BH5" s="142"/>
+      <c r="BI5" s="142"/>
+      <c r="BJ5" s="142"/>
+      <c r="BK5" s="142"/>
+      <c r="BL5" s="142"/>
+      <c r="BM5" s="142"/>
+      <c r="BN5" s="142"/>
+      <c r="BO5" s="142"/>
+      <c r="BP5" s="142"/>
+      <c r="BQ5" s="142"/>
+      <c r="BR5" s="142"/>
+      <c r="BS5" s="142"/>
+      <c r="BT5" s="142"/>
+      <c r="BU5" s="142"/>
+      <c r="BV5" s="142"/>
+      <c r="BW5" s="142"/>
+      <c r="BX5" s="142"/>
+      <c r="BY5" s="142"/>
+      <c r="BZ5" s="142"/>
+      <c r="CA5" s="142"/>
+      <c r="CB5" s="142"/>
+      <c r="CC5" s="142"/>
+      <c r="CD5" s="142"/>
+      <c r="CE5" s="142"/>
+      <c r="CF5" s="142"/>
+      <c r="CG5" s="142"/>
+      <c r="CH5" s="142"/>
+      <c r="CI5" s="142"/>
+      <c r="CJ5" s="142"/>
+      <c r="CK5" s="142"/>
+      <c r="CL5" s="142"/>
+      <c r="CM5" s="142"/>
+      <c r="CN5" s="142"/>
+      <c r="CO5" s="142"/>
+      <c r="CP5" s="142"/>
+      <c r="CQ5" s="142"/>
+      <c r="CR5" s="142"/>
+      <c r="CS5" s="142"/>
+      <c r="CT5" s="142"/>
+      <c r="CU5" s="142"/>
+      <c r="CV5" s="142"/>
+      <c r="CW5" s="142"/>
+      <c r="CX5" s="142"/>
+      <c r="CY5" s="142"/>
+      <c r="CZ5" s="142"/>
+      <c r="DA5" s="142"/>
+      <c r="DB5" s="142"/>
+      <c r="DC5" s="142"/>
+      <c r="DD5" s="142"/>
+      <c r="DE5" s="142"/>
+      <c r="DF5" s="142"/>
+      <c r="DG5" s="142"/>
+      <c r="DH5" s="142"/>
+      <c r="DI5" s="142"/>
+      <c r="DJ5" s="142"/>
+      <c r="DK5" s="142"/>
+      <c r="DL5" s="142"/>
+      <c r="DM5" s="142"/>
+      <c r="DN5" s="142"/>
+      <c r="DO5" s="142"/>
+      <c r="DP5" s="142"/>
+      <c r="DQ5" s="142"/>
+      <c r="DR5" s="142"/>
+      <c r="DS5" s="142"/>
+      <c r="DT5" s="142"/>
+      <c r="DU5" s="142"/>
+      <c r="DV5" s="142"/>
+      <c r="DW5" s="142"/>
+      <c r="DX5" s="142"/>
+      <c r="DY5" s="142"/>
+      <c r="DZ5" s="142"/>
+      <c r="EA5" s="142"/>
+      <c r="EB5" s="142"/>
+      <c r="EC5" s="142"/>
+      <c r="ED5" s="142"/>
+      <c r="EE5" s="142"/>
+      <c r="EF5" s="142"/>
+      <c r="EG5" s="142"/>
+      <c r="EH5" s="142"/>
+      <c r="EI5" s="142"/>
+      <c r="EJ5" s="142"/>
+      <c r="EK5" s="142"/>
+      <c r="EL5" s="142"/>
+      <c r="EM5" s="142"/>
+      <c r="EN5" s="142"/>
+      <c r="EO5" s="142"/>
+      <c r="EP5" s="142"/>
+      <c r="EQ5" s="142"/>
+      <c r="ER5" s="142"/>
+      <c r="ES5" s="142"/>
+      <c r="ET5" s="142"/>
+      <c r="EU5" s="142"/>
+      <c r="EV5" s="142"/>
+      <c r="EW5" s="142"/>
+      <c r="EX5" s="142"/>
+      <c r="EY5" s="142"/>
+      <c r="EZ5" s="142"/>
+      <c r="FA5" s="142"/>
+      <c r="FB5" s="142"/>
+      <c r="FC5" s="142"/>
+      <c r="FD5" s="142"/>
+      <c r="FE5" s="142"/>
+      <c r="FF5" s="142"/>
+      <c r="FG5" s="142"/>
+      <c r="FH5" s="142"/>
+      <c r="FI5" s="142"/>
+      <c r="FJ5" s="142"/>
+      <c r="FK5" s="142"/>
+      <c r="FL5" s="142"/>
+      <c r="FM5" s="142"/>
+      <c r="FN5" s="142"/>
+      <c r="FO5" s="142"/>
+      <c r="FP5" s="142"/>
+      <c r="FQ5" s="142"/>
+      <c r="FR5" s="142"/>
+      <c r="FS5" s="142"/>
+      <c r="FT5" s="142"/>
+      <c r="FU5" s="142"/>
+      <c r="FV5" s="142"/>
+      <c r="FW5" s="142"/>
+      <c r="FX5" s="142"/>
+      <c r="FY5" s="142"/>
+      <c r="FZ5" s="142"/>
+      <c r="GA5" s="142"/>
+      <c r="GB5" s="142"/>
+      <c r="GC5" s="142"/>
+      <c r="GD5" s="142"/>
+      <c r="GE5" s="142"/>
+      <c r="GF5" s="142"/>
+      <c r="GG5" s="142"/>
+      <c r="GH5" s="142"/>
+      <c r="GI5" s="142"/>
+      <c r="GJ5" s="142"/>
+      <c r="GK5" s="142"/>
+      <c r="GL5" s="142"/>
+      <c r="GM5" s="142"/>
+      <c r="GN5" s="142"/>
+      <c r="GO5" s="142"/>
+      <c r="GP5" s="142"/>
+      <c r="GQ5" s="142"/>
+      <c r="GR5" s="142"/>
+      <c r="GS5" s="142"/>
+      <c r="GT5" s="142"/>
+      <c r="GU5" s="142"/>
+      <c r="GV5" s="142"/>
+      <c r="GW5" s="142"/>
+      <c r="GX5" s="142"/>
+      <c r="GY5" s="142"/>
+      <c r="GZ5" s="142"/>
+      <c r="HA5" s="142"/>
+      <c r="HB5" s="142"/>
+      <c r="HC5" s="142"/>
+      <c r="HD5" s="142"/>
+      <c r="HE5" s="142"/>
+      <c r="HF5" s="142"/>
+      <c r="HG5" s="142"/>
+      <c r="HH5" s="142"/>
+      <c r="HI5" s="142"/>
+      <c r="HJ5" s="142"/>
+      <c r="HK5" s="142"/>
+      <c r="HL5" s="142"/>
+      <c r="HM5" s="142"/>
+      <c r="HN5" s="142"/>
+      <c r="HO5" s="142"/>
+      <c r="HP5" s="142"/>
+      <c r="HQ5" s="142"/>
+      <c r="HR5" s="142"/>
+      <c r="HS5" s="142"/>
+      <c r="HT5" s="142"/>
+      <c r="HU5" s="142"/>
+      <c r="HV5" s="142"/>
+      <c r="HW5" s="142"/>
+      <c r="HX5" s="142"/>
+      <c r="HY5" s="142"/>
+      <c r="HZ5" s="142"/>
+      <c r="IA5" s="142"/>
+      <c r="IB5" s="142"/>
+      <c r="IC5" s="142"/>
+      <c r="ID5" s="142"/>
+      <c r="IE5" s="142"/>
+      <c r="IF5" s="142"/>
+      <c r="IG5" s="142"/>
+      <c r="IH5" s="142"/>
+      <c r="II5" s="142"/>
+      <c r="IJ5" s="142"/>
+      <c r="IK5" s="142"/>
+      <c r="IL5" s="142"/>
+      <c r="IM5" s="142"/>
+      <c r="IN5" s="142"/>
+      <c r="IO5" s="142"/>
+      <c r="IP5" s="142"/>
+      <c r="IQ5" s="142"/>
+      <c r="IR5" s="142"/>
+      <c r="IS5" s="142"/>
+      <c r="IT5" s="142"/>
+      <c r="IU5" s="142"/>
+      <c r="IV5" s="142"/>
+      <c r="IW5" s="142"/>
+    </row>
+    <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="140"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -8936,6 +13593,250 @@
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="142"/>
+      <c r="T6" s="142"/>
+      <c r="U6" s="142"/>
+      <c r="V6" s="142"/>
+      <c r="W6" s="142"/>
+      <c r="X6" s="142"/>
+      <c r="Y6" s="142"/>
+      <c r="Z6" s="142"/>
+      <c r="AA6" s="142"/>
+      <c r="AB6" s="142"/>
+      <c r="AC6" s="142"/>
+      <c r="AD6" s="142"/>
+      <c r="AE6" s="142"/>
+      <c r="AF6" s="142"/>
+      <c r="AG6" s="142"/>
+      <c r="AH6" s="142"/>
+      <c r="AI6" s="142"/>
+      <c r="AJ6" s="142"/>
+      <c r="AK6" s="142"/>
+      <c r="AL6" s="142"/>
+      <c r="AM6" s="142"/>
+      <c r="AN6" s="142"/>
+      <c r="AO6" s="142"/>
+      <c r="AP6" s="142"/>
+      <c r="AQ6" s="142"/>
+      <c r="AR6" s="142"/>
+      <c r="AS6" s="142"/>
+      <c r="AT6" s="142"/>
+      <c r="AU6" s="142"/>
+      <c r="AV6" s="142"/>
+      <c r="AW6" s="142"/>
+      <c r="AX6" s="142"/>
+      <c r="AY6" s="142"/>
+      <c r="AZ6" s="142"/>
+      <c r="BA6" s="142"/>
+      <c r="BB6" s="142"/>
+      <c r="BC6" s="142"/>
+      <c r="BD6" s="142"/>
+      <c r="BE6" s="142"/>
+      <c r="BF6" s="142"/>
+      <c r="BG6" s="142"/>
+      <c r="BH6" s="142"/>
+      <c r="BI6" s="142"/>
+      <c r="BJ6" s="142"/>
+      <c r="BK6" s="142"/>
+      <c r="BL6" s="142"/>
+      <c r="BM6" s="142"/>
+      <c r="BN6" s="142"/>
+      <c r="BO6" s="142"/>
+      <c r="BP6" s="142"/>
+      <c r="BQ6" s="142"/>
+      <c r="BR6" s="142"/>
+      <c r="BS6" s="142"/>
+      <c r="BT6" s="142"/>
+      <c r="BU6" s="142"/>
+      <c r="BV6" s="142"/>
+      <c r="BW6" s="142"/>
+      <c r="BX6" s="142"/>
+      <c r="BY6" s="142"/>
+      <c r="BZ6" s="142"/>
+      <c r="CA6" s="142"/>
+      <c r="CB6" s="142"/>
+      <c r="CC6" s="142"/>
+      <c r="CD6" s="142"/>
+      <c r="CE6" s="142"/>
+      <c r="CF6" s="142"/>
+      <c r="CG6" s="142"/>
+      <c r="CH6" s="142"/>
+      <c r="CI6" s="142"/>
+      <c r="CJ6" s="142"/>
+      <c r="CK6" s="142"/>
+      <c r="CL6" s="142"/>
+      <c r="CM6" s="142"/>
+      <c r="CN6" s="142"/>
+      <c r="CO6" s="142"/>
+      <c r="CP6" s="142"/>
+      <c r="CQ6" s="142"/>
+      <c r="CR6" s="142"/>
+      <c r="CS6" s="142"/>
+      <c r="CT6" s="142"/>
+      <c r="CU6" s="142"/>
+      <c r="CV6" s="142"/>
+      <c r="CW6" s="142"/>
+      <c r="CX6" s="142"/>
+      <c r="CY6" s="142"/>
+      <c r="CZ6" s="142"/>
+      <c r="DA6" s="142"/>
+      <c r="DB6" s="142"/>
+      <c r="DC6" s="142"/>
+      <c r="DD6" s="142"/>
+      <c r="DE6" s="142"/>
+      <c r="DF6" s="142"/>
+      <c r="DG6" s="142"/>
+      <c r="DH6" s="142"/>
+      <c r="DI6" s="142"/>
+      <c r="DJ6" s="142"/>
+      <c r="DK6" s="142"/>
+      <c r="DL6" s="142"/>
+      <c r="DM6" s="142"/>
+      <c r="DN6" s="142"/>
+      <c r="DO6" s="142"/>
+      <c r="DP6" s="142"/>
+      <c r="DQ6" s="142"/>
+      <c r="DR6" s="142"/>
+      <c r="DS6" s="142"/>
+      <c r="DT6" s="142"/>
+      <c r="DU6" s="142"/>
+      <c r="DV6" s="142"/>
+      <c r="DW6" s="142"/>
+      <c r="DX6" s="142"/>
+      <c r="DY6" s="142"/>
+      <c r="DZ6" s="142"/>
+      <c r="EA6" s="142"/>
+      <c r="EB6" s="142"/>
+      <c r="EC6" s="142"/>
+      <c r="ED6" s="142"/>
+      <c r="EE6" s="142"/>
+      <c r="EF6" s="142"/>
+      <c r="EG6" s="142"/>
+      <c r="EH6" s="142"/>
+      <c r="EI6" s="142"/>
+      <c r="EJ6" s="142"/>
+      <c r="EK6" s="142"/>
+      <c r="EL6" s="142"/>
+      <c r="EM6" s="142"/>
+      <c r="EN6" s="142"/>
+      <c r="EO6" s="142"/>
+      <c r="EP6" s="142"/>
+      <c r="EQ6" s="142"/>
+      <c r="ER6" s="142"/>
+      <c r="ES6" s="142"/>
+      <c r="ET6" s="142"/>
+      <c r="EU6" s="142"/>
+      <c r="EV6" s="142"/>
+      <c r="EW6" s="142"/>
+      <c r="EX6" s="142"/>
+      <c r="EY6" s="142"/>
+      <c r="EZ6" s="142"/>
+      <c r="FA6" s="142"/>
+      <c r="FB6" s="142"/>
+      <c r="FC6" s="142"/>
+      <c r="FD6" s="142"/>
+      <c r="FE6" s="142"/>
+      <c r="FF6" s="142"/>
+      <c r="FG6" s="142"/>
+      <c r="FH6" s="142"/>
+      <c r="FI6" s="142"/>
+      <c r="FJ6" s="142"/>
+      <c r="FK6" s="142"/>
+      <c r="FL6" s="142"/>
+      <c r="FM6" s="142"/>
+      <c r="FN6" s="142"/>
+      <c r="FO6" s="142"/>
+      <c r="FP6" s="142"/>
+      <c r="FQ6" s="142"/>
+      <c r="FR6" s="142"/>
+      <c r="FS6" s="142"/>
+      <c r="FT6" s="142"/>
+      <c r="FU6" s="142"/>
+      <c r="FV6" s="142"/>
+      <c r="FW6" s="142"/>
+      <c r="FX6" s="142"/>
+      <c r="FY6" s="142"/>
+      <c r="FZ6" s="142"/>
+      <c r="GA6" s="142"/>
+      <c r="GB6" s="142"/>
+      <c r="GC6" s="142"/>
+      <c r="GD6" s="142"/>
+      <c r="GE6" s="142"/>
+      <c r="GF6" s="142"/>
+      <c r="GG6" s="142"/>
+      <c r="GH6" s="142"/>
+      <c r="GI6" s="142"/>
+      <c r="GJ6" s="142"/>
+      <c r="GK6" s="142"/>
+      <c r="GL6" s="142"/>
+      <c r="GM6" s="142"/>
+      <c r="GN6" s="142"/>
+      <c r="GO6" s="142"/>
+      <c r="GP6" s="142"/>
+      <c r="GQ6" s="142"/>
+      <c r="GR6" s="142"/>
+      <c r="GS6" s="142"/>
+      <c r="GT6" s="142"/>
+      <c r="GU6" s="142"/>
+      <c r="GV6" s="142"/>
+      <c r="GW6" s="142"/>
+      <c r="GX6" s="142"/>
+      <c r="GY6" s="142"/>
+      <c r="GZ6" s="142"/>
+      <c r="HA6" s="142"/>
+      <c r="HB6" s="142"/>
+      <c r="HC6" s="142"/>
+      <c r="HD6" s="142"/>
+      <c r="HE6" s="142"/>
+      <c r="HF6" s="142"/>
+      <c r="HG6" s="142"/>
+      <c r="HH6" s="142"/>
+      <c r="HI6" s="142"/>
+      <c r="HJ6" s="142"/>
+      <c r="HK6" s="142"/>
+      <c r="HL6" s="142"/>
+      <c r="HM6" s="142"/>
+      <c r="HN6" s="142"/>
+      <c r="HO6" s="142"/>
+      <c r="HP6" s="142"/>
+      <c r="HQ6" s="142"/>
+      <c r="HR6" s="142"/>
+      <c r="HS6" s="142"/>
+      <c r="HT6" s="142"/>
+      <c r="HU6" s="142"/>
+      <c r="HV6" s="142"/>
+      <c r="HW6" s="142"/>
+      <c r="HX6" s="142"/>
+      <c r="HY6" s="142"/>
+      <c r="HZ6" s="142"/>
+      <c r="IA6" s="142"/>
+      <c r="IB6" s="142"/>
+      <c r="IC6" s="142"/>
+      <c r="ID6" s="142"/>
+      <c r="IE6" s="142"/>
+      <c r="IF6" s="142"/>
+      <c r="IG6" s="142"/>
+      <c r="IH6" s="142"/>
+      <c r="II6" s="142"/>
+      <c r="IJ6" s="142"/>
+      <c r="IK6" s="142"/>
+      <c r="IL6" s="142"/>
+      <c r="IM6" s="142"/>
+      <c r="IN6" s="142"/>
+      <c r="IO6" s="142"/>
+      <c r="IP6" s="142"/>
+      <c r="IQ6" s="142"/>
+      <c r="IR6" s="142"/>
+      <c r="IS6" s="142"/>
+      <c r="IT6" s="142"/>
+      <c r="IU6" s="142"/>
+      <c r="IV6" s="142"/>
+      <c r="IW6" s="142"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="129"/>
@@ -9189,7 +14090,7 @@
       <c r="L18" s="63"/>
       <c r="M18" s="129"/>
     </row>
-    <row r="19" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
         <v>69</v>
@@ -9221,8 +14122,252 @@
         <v>77</v>
       </c>
       <c r="M19" s="140"/>
-    </row>
-    <row r="20" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N19" s="142"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="142"/>
+      <c r="Q19" s="142"/>
+      <c r="R19" s="142"/>
+      <c r="S19" s="142"/>
+      <c r="T19" s="142"/>
+      <c r="U19" s="142"/>
+      <c r="V19" s="142"/>
+      <c r="W19" s="142"/>
+      <c r="X19" s="142"/>
+      <c r="Y19" s="142"/>
+      <c r="Z19" s="142"/>
+      <c r="AA19" s="142"/>
+      <c r="AB19" s="142"/>
+      <c r="AC19" s="142"/>
+      <c r="AD19" s="142"/>
+      <c r="AE19" s="142"/>
+      <c r="AF19" s="142"/>
+      <c r="AG19" s="142"/>
+      <c r="AH19" s="142"/>
+      <c r="AI19" s="142"/>
+      <c r="AJ19" s="142"/>
+      <c r="AK19" s="142"/>
+      <c r="AL19" s="142"/>
+      <c r="AM19" s="142"/>
+      <c r="AN19" s="142"/>
+      <c r="AO19" s="142"/>
+      <c r="AP19" s="142"/>
+      <c r="AQ19" s="142"/>
+      <c r="AR19" s="142"/>
+      <c r="AS19" s="142"/>
+      <c r="AT19" s="142"/>
+      <c r="AU19" s="142"/>
+      <c r="AV19" s="142"/>
+      <c r="AW19" s="142"/>
+      <c r="AX19" s="142"/>
+      <c r="AY19" s="142"/>
+      <c r="AZ19" s="142"/>
+      <c r="BA19" s="142"/>
+      <c r="BB19" s="142"/>
+      <c r="BC19" s="142"/>
+      <c r="BD19" s="142"/>
+      <c r="BE19" s="142"/>
+      <c r="BF19" s="142"/>
+      <c r="BG19" s="142"/>
+      <c r="BH19" s="142"/>
+      <c r="BI19" s="142"/>
+      <c r="BJ19" s="142"/>
+      <c r="BK19" s="142"/>
+      <c r="BL19" s="142"/>
+      <c r="BM19" s="142"/>
+      <c r="BN19" s="142"/>
+      <c r="BO19" s="142"/>
+      <c r="BP19" s="142"/>
+      <c r="BQ19" s="142"/>
+      <c r="BR19" s="142"/>
+      <c r="BS19" s="142"/>
+      <c r="BT19" s="142"/>
+      <c r="BU19" s="142"/>
+      <c r="BV19" s="142"/>
+      <c r="BW19" s="142"/>
+      <c r="BX19" s="142"/>
+      <c r="BY19" s="142"/>
+      <c r="BZ19" s="142"/>
+      <c r="CA19" s="142"/>
+      <c r="CB19" s="142"/>
+      <c r="CC19" s="142"/>
+      <c r="CD19" s="142"/>
+      <c r="CE19" s="142"/>
+      <c r="CF19" s="142"/>
+      <c r="CG19" s="142"/>
+      <c r="CH19" s="142"/>
+      <c r="CI19" s="142"/>
+      <c r="CJ19" s="142"/>
+      <c r="CK19" s="142"/>
+      <c r="CL19" s="142"/>
+      <c r="CM19" s="142"/>
+      <c r="CN19" s="142"/>
+      <c r="CO19" s="142"/>
+      <c r="CP19" s="142"/>
+      <c r="CQ19" s="142"/>
+      <c r="CR19" s="142"/>
+      <c r="CS19" s="142"/>
+      <c r="CT19" s="142"/>
+      <c r="CU19" s="142"/>
+      <c r="CV19" s="142"/>
+      <c r="CW19" s="142"/>
+      <c r="CX19" s="142"/>
+      <c r="CY19" s="142"/>
+      <c r="CZ19" s="142"/>
+      <c r="DA19" s="142"/>
+      <c r="DB19" s="142"/>
+      <c r="DC19" s="142"/>
+      <c r="DD19" s="142"/>
+      <c r="DE19" s="142"/>
+      <c r="DF19" s="142"/>
+      <c r="DG19" s="142"/>
+      <c r="DH19" s="142"/>
+      <c r="DI19" s="142"/>
+      <c r="DJ19" s="142"/>
+      <c r="DK19" s="142"/>
+      <c r="DL19" s="142"/>
+      <c r="DM19" s="142"/>
+      <c r="DN19" s="142"/>
+      <c r="DO19" s="142"/>
+      <c r="DP19" s="142"/>
+      <c r="DQ19" s="142"/>
+      <c r="DR19" s="142"/>
+      <c r="DS19" s="142"/>
+      <c r="DT19" s="142"/>
+      <c r="DU19" s="142"/>
+      <c r="DV19" s="142"/>
+      <c r="DW19" s="142"/>
+      <c r="DX19" s="142"/>
+      <c r="DY19" s="142"/>
+      <c r="DZ19" s="142"/>
+      <c r="EA19" s="142"/>
+      <c r="EB19" s="142"/>
+      <c r="EC19" s="142"/>
+      <c r="ED19" s="142"/>
+      <c r="EE19" s="142"/>
+      <c r="EF19" s="142"/>
+      <c r="EG19" s="142"/>
+      <c r="EH19" s="142"/>
+      <c r="EI19" s="142"/>
+      <c r="EJ19" s="142"/>
+      <c r="EK19" s="142"/>
+      <c r="EL19" s="142"/>
+      <c r="EM19" s="142"/>
+      <c r="EN19" s="142"/>
+      <c r="EO19" s="142"/>
+      <c r="EP19" s="142"/>
+      <c r="EQ19" s="142"/>
+      <c r="ER19" s="142"/>
+      <c r="ES19" s="142"/>
+      <c r="ET19" s="142"/>
+      <c r="EU19" s="142"/>
+      <c r="EV19" s="142"/>
+      <c r="EW19" s="142"/>
+      <c r="EX19" s="142"/>
+      <c r="EY19" s="142"/>
+      <c r="EZ19" s="142"/>
+      <c r="FA19" s="142"/>
+      <c r="FB19" s="142"/>
+      <c r="FC19" s="142"/>
+      <c r="FD19" s="142"/>
+      <c r="FE19" s="142"/>
+      <c r="FF19" s="142"/>
+      <c r="FG19" s="142"/>
+      <c r="FH19" s="142"/>
+      <c r="FI19" s="142"/>
+      <c r="FJ19" s="142"/>
+      <c r="FK19" s="142"/>
+      <c r="FL19" s="142"/>
+      <c r="FM19" s="142"/>
+      <c r="FN19" s="142"/>
+      <c r="FO19" s="142"/>
+      <c r="FP19" s="142"/>
+      <c r="FQ19" s="142"/>
+      <c r="FR19" s="142"/>
+      <c r="FS19" s="142"/>
+      <c r="FT19" s="142"/>
+      <c r="FU19" s="142"/>
+      <c r="FV19" s="142"/>
+      <c r="FW19" s="142"/>
+      <c r="FX19" s="142"/>
+      <c r="FY19" s="142"/>
+      <c r="FZ19" s="142"/>
+      <c r="GA19" s="142"/>
+      <c r="GB19" s="142"/>
+      <c r="GC19" s="142"/>
+      <c r="GD19" s="142"/>
+      <c r="GE19" s="142"/>
+      <c r="GF19" s="142"/>
+      <c r="GG19" s="142"/>
+      <c r="GH19" s="142"/>
+      <c r="GI19" s="142"/>
+      <c r="GJ19" s="142"/>
+      <c r="GK19" s="142"/>
+      <c r="GL19" s="142"/>
+      <c r="GM19" s="142"/>
+      <c r="GN19" s="142"/>
+      <c r="GO19" s="142"/>
+      <c r="GP19" s="142"/>
+      <c r="GQ19" s="142"/>
+      <c r="GR19" s="142"/>
+      <c r="GS19" s="142"/>
+      <c r="GT19" s="142"/>
+      <c r="GU19" s="142"/>
+      <c r="GV19" s="142"/>
+      <c r="GW19" s="142"/>
+      <c r="GX19" s="142"/>
+      <c r="GY19" s="142"/>
+      <c r="GZ19" s="142"/>
+      <c r="HA19" s="142"/>
+      <c r="HB19" s="142"/>
+      <c r="HC19" s="142"/>
+      <c r="HD19" s="142"/>
+      <c r="HE19" s="142"/>
+      <c r="HF19" s="142"/>
+      <c r="HG19" s="142"/>
+      <c r="HH19" s="142"/>
+      <c r="HI19" s="142"/>
+      <c r="HJ19" s="142"/>
+      <c r="HK19" s="142"/>
+      <c r="HL19" s="142"/>
+      <c r="HM19" s="142"/>
+      <c r="HN19" s="142"/>
+      <c r="HO19" s="142"/>
+      <c r="HP19" s="142"/>
+      <c r="HQ19" s="142"/>
+      <c r="HR19" s="142"/>
+      <c r="HS19" s="142"/>
+      <c r="HT19" s="142"/>
+      <c r="HU19" s="142"/>
+      <c r="HV19" s="142"/>
+      <c r="HW19" s="142"/>
+      <c r="HX19" s="142"/>
+      <c r="HY19" s="142"/>
+      <c r="HZ19" s="142"/>
+      <c r="IA19" s="142"/>
+      <c r="IB19" s="142"/>
+      <c r="IC19" s="142"/>
+      <c r="ID19" s="142"/>
+      <c r="IE19" s="142"/>
+      <c r="IF19" s="142"/>
+      <c r="IG19" s="142"/>
+      <c r="IH19" s="142"/>
+      <c r="II19" s="142"/>
+      <c r="IJ19" s="142"/>
+      <c r="IK19" s="142"/>
+      <c r="IL19" s="142"/>
+      <c r="IM19" s="142"/>
+      <c r="IN19" s="142"/>
+      <c r="IO19" s="142"/>
+      <c r="IP19" s="142"/>
+      <c r="IQ19" s="142"/>
+      <c r="IR19" s="142"/>
+      <c r="IS19" s="142"/>
+      <c r="IT19" s="142"/>
+      <c r="IU19" s="142"/>
+      <c r="IV19" s="142"/>
+      <c r="IW19" s="142"/>
+    </row>
+    <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="140"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -9242,8 +14387,252 @@
       </c>
       <c r="L20" s="21"/>
       <c r="M20" s="140"/>
-    </row>
-    <row r="21" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N20" s="142"/>
+      <c r="O20" s="142"/>
+      <c r="P20" s="142"/>
+      <c r="Q20" s="142"/>
+      <c r="R20" s="142"/>
+      <c r="S20" s="142"/>
+      <c r="T20" s="142"/>
+      <c r="U20" s="142"/>
+      <c r="V20" s="142"/>
+      <c r="W20" s="142"/>
+      <c r="X20" s="142"/>
+      <c r="Y20" s="142"/>
+      <c r="Z20" s="142"/>
+      <c r="AA20" s="142"/>
+      <c r="AB20" s="142"/>
+      <c r="AC20" s="142"/>
+      <c r="AD20" s="142"/>
+      <c r="AE20" s="142"/>
+      <c r="AF20" s="142"/>
+      <c r="AG20" s="142"/>
+      <c r="AH20" s="142"/>
+      <c r="AI20" s="142"/>
+      <c r="AJ20" s="142"/>
+      <c r="AK20" s="142"/>
+      <c r="AL20" s="142"/>
+      <c r="AM20" s="142"/>
+      <c r="AN20" s="142"/>
+      <c r="AO20" s="142"/>
+      <c r="AP20" s="142"/>
+      <c r="AQ20" s="142"/>
+      <c r="AR20" s="142"/>
+      <c r="AS20" s="142"/>
+      <c r="AT20" s="142"/>
+      <c r="AU20" s="142"/>
+      <c r="AV20" s="142"/>
+      <c r="AW20" s="142"/>
+      <c r="AX20" s="142"/>
+      <c r="AY20" s="142"/>
+      <c r="AZ20" s="142"/>
+      <c r="BA20" s="142"/>
+      <c r="BB20" s="142"/>
+      <c r="BC20" s="142"/>
+      <c r="BD20" s="142"/>
+      <c r="BE20" s="142"/>
+      <c r="BF20" s="142"/>
+      <c r="BG20" s="142"/>
+      <c r="BH20" s="142"/>
+      <c r="BI20" s="142"/>
+      <c r="BJ20" s="142"/>
+      <c r="BK20" s="142"/>
+      <c r="BL20" s="142"/>
+      <c r="BM20" s="142"/>
+      <c r="BN20" s="142"/>
+      <c r="BO20" s="142"/>
+      <c r="BP20" s="142"/>
+      <c r="BQ20" s="142"/>
+      <c r="BR20" s="142"/>
+      <c r="BS20" s="142"/>
+      <c r="BT20" s="142"/>
+      <c r="BU20" s="142"/>
+      <c r="BV20" s="142"/>
+      <c r="BW20" s="142"/>
+      <c r="BX20" s="142"/>
+      <c r="BY20" s="142"/>
+      <c r="BZ20" s="142"/>
+      <c r="CA20" s="142"/>
+      <c r="CB20" s="142"/>
+      <c r="CC20" s="142"/>
+      <c r="CD20" s="142"/>
+      <c r="CE20" s="142"/>
+      <c r="CF20" s="142"/>
+      <c r="CG20" s="142"/>
+      <c r="CH20" s="142"/>
+      <c r="CI20" s="142"/>
+      <c r="CJ20" s="142"/>
+      <c r="CK20" s="142"/>
+      <c r="CL20" s="142"/>
+      <c r="CM20" s="142"/>
+      <c r="CN20" s="142"/>
+      <c r="CO20" s="142"/>
+      <c r="CP20" s="142"/>
+      <c r="CQ20" s="142"/>
+      <c r="CR20" s="142"/>
+      <c r="CS20" s="142"/>
+      <c r="CT20" s="142"/>
+      <c r="CU20" s="142"/>
+      <c r="CV20" s="142"/>
+      <c r="CW20" s="142"/>
+      <c r="CX20" s="142"/>
+      <c r="CY20" s="142"/>
+      <c r="CZ20" s="142"/>
+      <c r="DA20" s="142"/>
+      <c r="DB20" s="142"/>
+      <c r="DC20" s="142"/>
+      <c r="DD20" s="142"/>
+      <c r="DE20" s="142"/>
+      <c r="DF20" s="142"/>
+      <c r="DG20" s="142"/>
+      <c r="DH20" s="142"/>
+      <c r="DI20" s="142"/>
+      <c r="DJ20" s="142"/>
+      <c r="DK20" s="142"/>
+      <c r="DL20" s="142"/>
+      <c r="DM20" s="142"/>
+      <c r="DN20" s="142"/>
+      <c r="DO20" s="142"/>
+      <c r="DP20" s="142"/>
+      <c r="DQ20" s="142"/>
+      <c r="DR20" s="142"/>
+      <c r="DS20" s="142"/>
+      <c r="DT20" s="142"/>
+      <c r="DU20" s="142"/>
+      <c r="DV20" s="142"/>
+      <c r="DW20" s="142"/>
+      <c r="DX20" s="142"/>
+      <c r="DY20" s="142"/>
+      <c r="DZ20" s="142"/>
+      <c r="EA20" s="142"/>
+      <c r="EB20" s="142"/>
+      <c r="EC20" s="142"/>
+      <c r="ED20" s="142"/>
+      <c r="EE20" s="142"/>
+      <c r="EF20" s="142"/>
+      <c r="EG20" s="142"/>
+      <c r="EH20" s="142"/>
+      <c r="EI20" s="142"/>
+      <c r="EJ20" s="142"/>
+      <c r="EK20" s="142"/>
+      <c r="EL20" s="142"/>
+      <c r="EM20" s="142"/>
+      <c r="EN20" s="142"/>
+      <c r="EO20" s="142"/>
+      <c r="EP20" s="142"/>
+      <c r="EQ20" s="142"/>
+      <c r="ER20" s="142"/>
+      <c r="ES20" s="142"/>
+      <c r="ET20" s="142"/>
+      <c r="EU20" s="142"/>
+      <c r="EV20" s="142"/>
+      <c r="EW20" s="142"/>
+      <c r="EX20" s="142"/>
+      <c r="EY20" s="142"/>
+      <c r="EZ20" s="142"/>
+      <c r="FA20" s="142"/>
+      <c r="FB20" s="142"/>
+      <c r="FC20" s="142"/>
+      <c r="FD20" s="142"/>
+      <c r="FE20" s="142"/>
+      <c r="FF20" s="142"/>
+      <c r="FG20" s="142"/>
+      <c r="FH20" s="142"/>
+      <c r="FI20" s="142"/>
+      <c r="FJ20" s="142"/>
+      <c r="FK20" s="142"/>
+      <c r="FL20" s="142"/>
+      <c r="FM20" s="142"/>
+      <c r="FN20" s="142"/>
+      <c r="FO20" s="142"/>
+      <c r="FP20" s="142"/>
+      <c r="FQ20" s="142"/>
+      <c r="FR20" s="142"/>
+      <c r="FS20" s="142"/>
+      <c r="FT20" s="142"/>
+      <c r="FU20" s="142"/>
+      <c r="FV20" s="142"/>
+      <c r="FW20" s="142"/>
+      <c r="FX20" s="142"/>
+      <c r="FY20" s="142"/>
+      <c r="FZ20" s="142"/>
+      <c r="GA20" s="142"/>
+      <c r="GB20" s="142"/>
+      <c r="GC20" s="142"/>
+      <c r="GD20" s="142"/>
+      <c r="GE20" s="142"/>
+      <c r="GF20" s="142"/>
+      <c r="GG20" s="142"/>
+      <c r="GH20" s="142"/>
+      <c r="GI20" s="142"/>
+      <c r="GJ20" s="142"/>
+      <c r="GK20" s="142"/>
+      <c r="GL20" s="142"/>
+      <c r="GM20" s="142"/>
+      <c r="GN20" s="142"/>
+      <c r="GO20" s="142"/>
+      <c r="GP20" s="142"/>
+      <c r="GQ20" s="142"/>
+      <c r="GR20" s="142"/>
+      <c r="GS20" s="142"/>
+      <c r="GT20" s="142"/>
+      <c r="GU20" s="142"/>
+      <c r="GV20" s="142"/>
+      <c r="GW20" s="142"/>
+      <c r="GX20" s="142"/>
+      <c r="GY20" s="142"/>
+      <c r="GZ20" s="142"/>
+      <c r="HA20" s="142"/>
+      <c r="HB20" s="142"/>
+      <c r="HC20" s="142"/>
+      <c r="HD20" s="142"/>
+      <c r="HE20" s="142"/>
+      <c r="HF20" s="142"/>
+      <c r="HG20" s="142"/>
+      <c r="HH20" s="142"/>
+      <c r="HI20" s="142"/>
+      <c r="HJ20" s="142"/>
+      <c r="HK20" s="142"/>
+      <c r="HL20" s="142"/>
+      <c r="HM20" s="142"/>
+      <c r="HN20" s="142"/>
+      <c r="HO20" s="142"/>
+      <c r="HP20" s="142"/>
+      <c r="HQ20" s="142"/>
+      <c r="HR20" s="142"/>
+      <c r="HS20" s="142"/>
+      <c r="HT20" s="142"/>
+      <c r="HU20" s="142"/>
+      <c r="HV20" s="142"/>
+      <c r="HW20" s="142"/>
+      <c r="HX20" s="142"/>
+      <c r="HY20" s="142"/>
+      <c r="HZ20" s="142"/>
+      <c r="IA20" s="142"/>
+      <c r="IB20" s="142"/>
+      <c r="IC20" s="142"/>
+      <c r="ID20" s="142"/>
+      <c r="IE20" s="142"/>
+      <c r="IF20" s="142"/>
+      <c r="IG20" s="142"/>
+      <c r="IH20" s="142"/>
+      <c r="II20" s="142"/>
+      <c r="IJ20" s="142"/>
+      <c r="IK20" s="142"/>
+      <c r="IL20" s="142"/>
+      <c r="IM20" s="142"/>
+      <c r="IN20" s="142"/>
+      <c r="IO20" s="142"/>
+      <c r="IP20" s="142"/>
+      <c r="IQ20" s="142"/>
+      <c r="IR20" s="142"/>
+      <c r="IS20" s="142"/>
+      <c r="IT20" s="142"/>
+      <c r="IU20" s="142"/>
+      <c r="IV20" s="142"/>
+      <c r="IW20" s="142"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="140"/>
       <c r="B21" s="144"/>
       <c r="C21" s="144"/>
@@ -9257,6 +14646,250 @@
       <c r="K21" s="145"/>
       <c r="L21" s="144"/>
       <c r="M21" s="140"/>
+      <c r="N21" s="142"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="142"/>
+      <c r="Q21" s="142"/>
+      <c r="R21" s="142"/>
+      <c r="S21" s="142"/>
+      <c r="T21" s="142"/>
+      <c r="U21" s="142"/>
+      <c r="V21" s="142"/>
+      <c r="W21" s="142"/>
+      <c r="X21" s="142"/>
+      <c r="Y21" s="142"/>
+      <c r="Z21" s="142"/>
+      <c r="AA21" s="142"/>
+      <c r="AB21" s="142"/>
+      <c r="AC21" s="142"/>
+      <c r="AD21" s="142"/>
+      <c r="AE21" s="142"/>
+      <c r="AF21" s="142"/>
+      <c r="AG21" s="142"/>
+      <c r="AH21" s="142"/>
+      <c r="AI21" s="142"/>
+      <c r="AJ21" s="142"/>
+      <c r="AK21" s="142"/>
+      <c r="AL21" s="142"/>
+      <c r="AM21" s="142"/>
+      <c r="AN21" s="142"/>
+      <c r="AO21" s="142"/>
+      <c r="AP21" s="142"/>
+      <c r="AQ21" s="142"/>
+      <c r="AR21" s="142"/>
+      <c r="AS21" s="142"/>
+      <c r="AT21" s="142"/>
+      <c r="AU21" s="142"/>
+      <c r="AV21" s="142"/>
+      <c r="AW21" s="142"/>
+      <c r="AX21" s="142"/>
+      <c r="AY21" s="142"/>
+      <c r="AZ21" s="142"/>
+      <c r="BA21" s="142"/>
+      <c r="BB21" s="142"/>
+      <c r="BC21" s="142"/>
+      <c r="BD21" s="142"/>
+      <c r="BE21" s="142"/>
+      <c r="BF21" s="142"/>
+      <c r="BG21" s="142"/>
+      <c r="BH21" s="142"/>
+      <c r="BI21" s="142"/>
+      <c r="BJ21" s="142"/>
+      <c r="BK21" s="142"/>
+      <c r="BL21" s="142"/>
+      <c r="BM21" s="142"/>
+      <c r="BN21" s="142"/>
+      <c r="BO21" s="142"/>
+      <c r="BP21" s="142"/>
+      <c r="BQ21" s="142"/>
+      <c r="BR21" s="142"/>
+      <c r="BS21" s="142"/>
+      <c r="BT21" s="142"/>
+      <c r="BU21" s="142"/>
+      <c r="BV21" s="142"/>
+      <c r="BW21" s="142"/>
+      <c r="BX21" s="142"/>
+      <c r="BY21" s="142"/>
+      <c r="BZ21" s="142"/>
+      <c r="CA21" s="142"/>
+      <c r="CB21" s="142"/>
+      <c r="CC21" s="142"/>
+      <c r="CD21" s="142"/>
+      <c r="CE21" s="142"/>
+      <c r="CF21" s="142"/>
+      <c r="CG21" s="142"/>
+      <c r="CH21" s="142"/>
+      <c r="CI21" s="142"/>
+      <c r="CJ21" s="142"/>
+      <c r="CK21" s="142"/>
+      <c r="CL21" s="142"/>
+      <c r="CM21" s="142"/>
+      <c r="CN21" s="142"/>
+      <c r="CO21" s="142"/>
+      <c r="CP21" s="142"/>
+      <c r="CQ21" s="142"/>
+      <c r="CR21" s="142"/>
+      <c r="CS21" s="142"/>
+      <c r="CT21" s="142"/>
+      <c r="CU21" s="142"/>
+      <c r="CV21" s="142"/>
+      <c r="CW21" s="142"/>
+      <c r="CX21" s="142"/>
+      <c r="CY21" s="142"/>
+      <c r="CZ21" s="142"/>
+      <c r="DA21" s="142"/>
+      <c r="DB21" s="142"/>
+      <c r="DC21" s="142"/>
+      <c r="DD21" s="142"/>
+      <c r="DE21" s="142"/>
+      <c r="DF21" s="142"/>
+      <c r="DG21" s="142"/>
+      <c r="DH21" s="142"/>
+      <c r="DI21" s="142"/>
+      <c r="DJ21" s="142"/>
+      <c r="DK21" s="142"/>
+      <c r="DL21" s="142"/>
+      <c r="DM21" s="142"/>
+      <c r="DN21" s="142"/>
+      <c r="DO21" s="142"/>
+      <c r="DP21" s="142"/>
+      <c r="DQ21" s="142"/>
+      <c r="DR21" s="142"/>
+      <c r="DS21" s="142"/>
+      <c r="DT21" s="142"/>
+      <c r="DU21" s="142"/>
+      <c r="DV21" s="142"/>
+      <c r="DW21" s="142"/>
+      <c r="DX21" s="142"/>
+      <c r="DY21" s="142"/>
+      <c r="DZ21" s="142"/>
+      <c r="EA21" s="142"/>
+      <c r="EB21" s="142"/>
+      <c r="EC21" s="142"/>
+      <c r="ED21" s="142"/>
+      <c r="EE21" s="142"/>
+      <c r="EF21" s="142"/>
+      <c r="EG21" s="142"/>
+      <c r="EH21" s="142"/>
+      <c r="EI21" s="142"/>
+      <c r="EJ21" s="142"/>
+      <c r="EK21" s="142"/>
+      <c r="EL21" s="142"/>
+      <c r="EM21" s="142"/>
+      <c r="EN21" s="142"/>
+      <c r="EO21" s="142"/>
+      <c r="EP21" s="142"/>
+      <c r="EQ21" s="142"/>
+      <c r="ER21" s="142"/>
+      <c r="ES21" s="142"/>
+      <c r="ET21" s="142"/>
+      <c r="EU21" s="142"/>
+      <c r="EV21" s="142"/>
+      <c r="EW21" s="142"/>
+      <c r="EX21" s="142"/>
+      <c r="EY21" s="142"/>
+      <c r="EZ21" s="142"/>
+      <c r="FA21" s="142"/>
+      <c r="FB21" s="142"/>
+      <c r="FC21" s="142"/>
+      <c r="FD21" s="142"/>
+      <c r="FE21" s="142"/>
+      <c r="FF21" s="142"/>
+      <c r="FG21" s="142"/>
+      <c r="FH21" s="142"/>
+      <c r="FI21" s="142"/>
+      <c r="FJ21" s="142"/>
+      <c r="FK21" s="142"/>
+      <c r="FL21" s="142"/>
+      <c r="FM21" s="142"/>
+      <c r="FN21" s="142"/>
+      <c r="FO21" s="142"/>
+      <c r="FP21" s="142"/>
+      <c r="FQ21" s="142"/>
+      <c r="FR21" s="142"/>
+      <c r="FS21" s="142"/>
+      <c r="FT21" s="142"/>
+      <c r="FU21" s="142"/>
+      <c r="FV21" s="142"/>
+      <c r="FW21" s="142"/>
+      <c r="FX21" s="142"/>
+      <c r="FY21" s="142"/>
+      <c r="FZ21" s="142"/>
+      <c r="GA21" s="142"/>
+      <c r="GB21" s="142"/>
+      <c r="GC21" s="142"/>
+      <c r="GD21" s="142"/>
+      <c r="GE21" s="142"/>
+      <c r="GF21" s="142"/>
+      <c r="GG21" s="142"/>
+      <c r="GH21" s="142"/>
+      <c r="GI21" s="142"/>
+      <c r="GJ21" s="142"/>
+      <c r="GK21" s="142"/>
+      <c r="GL21" s="142"/>
+      <c r="GM21" s="142"/>
+      <c r="GN21" s="142"/>
+      <c r="GO21" s="142"/>
+      <c r="GP21" s="142"/>
+      <c r="GQ21" s="142"/>
+      <c r="GR21" s="142"/>
+      <c r="GS21" s="142"/>
+      <c r="GT21" s="142"/>
+      <c r="GU21" s="142"/>
+      <c r="GV21" s="142"/>
+      <c r="GW21" s="142"/>
+      <c r="GX21" s="142"/>
+      <c r="GY21" s="142"/>
+      <c r="GZ21" s="142"/>
+      <c r="HA21" s="142"/>
+      <c r="HB21" s="142"/>
+      <c r="HC21" s="142"/>
+      <c r="HD21" s="142"/>
+      <c r="HE21" s="142"/>
+      <c r="HF21" s="142"/>
+      <c r="HG21" s="142"/>
+      <c r="HH21" s="142"/>
+      <c r="HI21" s="142"/>
+      <c r="HJ21" s="142"/>
+      <c r="HK21" s="142"/>
+      <c r="HL21" s="142"/>
+      <c r="HM21" s="142"/>
+      <c r="HN21" s="142"/>
+      <c r="HO21" s="142"/>
+      <c r="HP21" s="142"/>
+      <c r="HQ21" s="142"/>
+      <c r="HR21" s="142"/>
+      <c r="HS21" s="142"/>
+      <c r="HT21" s="142"/>
+      <c r="HU21" s="142"/>
+      <c r="HV21" s="142"/>
+      <c r="HW21" s="142"/>
+      <c r="HX21" s="142"/>
+      <c r="HY21" s="142"/>
+      <c r="HZ21" s="142"/>
+      <c r="IA21" s="142"/>
+      <c r="IB21" s="142"/>
+      <c r="IC21" s="142"/>
+      <c r="ID21" s="142"/>
+      <c r="IE21" s="142"/>
+      <c r="IF21" s="142"/>
+      <c r="IG21" s="142"/>
+      <c r="IH21" s="142"/>
+      <c r="II21" s="142"/>
+      <c r="IJ21" s="142"/>
+      <c r="IK21" s="142"/>
+      <c r="IL21" s="142"/>
+      <c r="IM21" s="142"/>
+      <c r="IN21" s="142"/>
+      <c r="IO21" s="142"/>
+      <c r="IP21" s="142"/>
+      <c r="IQ21" s="142"/>
+      <c r="IR21" s="142"/>
+      <c r="IS21" s="142"/>
+      <c r="IT21" s="142"/>
+      <c r="IU21" s="142"/>
+      <c r="IV21" s="142"/>
+      <c r="IW21" s="142"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="129"/>

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -232,6 +232,18 @@
     <t xml:space="preserve">Special Rate W Down Allowance</t>
   </si>
   <si>
+    <t xml:space="preserve">Single asset pool (P = private use or short-life asset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Asset Pool W Down Allowance main rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Asset Pool W Down Allowance special rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single Asset Pool Written Down Tax Value</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
   </si>
   <si>
@@ -272,6 +284,12 @@
   </si>
   <si>
     <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hatchback (30% private use, 2 years old)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - costing under £</t>
@@ -1695,7 +1713,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="5" width="11.32"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="26" min="25" style="7" width="9.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="1.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="28" style="1" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="8" width="5.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="7" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="8" width="5.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="31" style="7" width="10.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="34" style="1" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1709,30 +1731,30 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>101500</v>
+        <v>114000</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>14098</v>
+        <v>19098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
-        <v>34902</v>
+        <v>42402</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>17740</v>
+        <v>20865</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>31838</v>
+        <v>39963</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>56990</v>
+        <v>61365</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1741,7 +1763,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13" t="n">
         <f aca="false">O57+O110</f>
-        <v>33000</v>
+        <v>41000</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>4</v>
@@ -1752,11 +1774,11 @@
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>3360</v>
+        <v>4144</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>29100</v>
+        <v>36316</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1789,9 +1811,18 @@
         <v>540</v>
       </c>
       <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
+      <c r="AE1" s="13" t="n">
+        <f aca="false">AE57+AE110</f>
+        <v>784</v>
+      </c>
+      <c r="AF1" s="13" t="n">
+        <f aca="false">AF57+AF110</f>
+        <v>0</v>
+      </c>
+      <c r="AG1" s="13" t="n">
+        <f aca="false">AG57+AG110</f>
+        <v>7216</v>
+      </c>
       <c r="AH1" s="19"/>
       <c r="AI1" s="19"/>
       <c r="AJ1" s="19"/>
@@ -2084,6 +2115,18 @@
       </c>
       <c r="AC2" s="22" t="s">
         <v>23</v>
+      </c>
+      <c r="AD2" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE2" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF2" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG2" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2663,7 +2706,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43"/>
       <c r="B6" s="44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="45" t="n">
@@ -2697,7 +2740,7 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="43"/>
       <c r="B7" s="52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="53"/>
@@ -2881,7 +2924,7 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43"/>
       <c r="B11" s="60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -2956,6 +2999,18 @@
       <c r="AB11" s="25"/>
       <c r="AC11" s="62" t="n">
         <f aca="false">SUM(AC8:AC10)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="62" t="n">
+        <f aca="false">SUM(AE8:AE10)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="62" t="n">
+        <f aca="false">SUM(AF8:AF10)</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="62" t="n">
+        <f aca="false">SUM(AG8:AG10)</f>
         <v>0</v>
       </c>
     </row>
@@ -2991,7 +3046,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43"/>
       <c r="B13" s="52" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" s="52"/>
       <c r="D13" s="63"/>
@@ -3088,6 +3143,18 @@
         <f aca="false">IF(AND(O14&gt;0,AB14="S"),O14*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE14" s="48" t="str">
+        <f aca="false">IF(AND(AD14="P",AB14&lt;&gt;"S"),N(R14)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF14" s="48" t="str">
+        <f aca="false">IF(AND(AD14="P",AB14="S"),N(AC14)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG14" s="48" t="str">
+        <f aca="false">IF(AD14="P",N(S14)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="43"/>
@@ -3155,6 +3222,18 @@
         <f aca="false">IF(AND(O15&gt;0,AB15="S"),O15*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE15" s="48" t="str">
+        <f aca="false">IF(AND(AD15="P",AB15&lt;&gt;"S"),N(R15)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF15" s="48" t="str">
+        <f aca="false">IF(AND(AD15="P",AB15="S"),N(AC15)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG15" s="48" t="str">
+        <f aca="false">IF(AD15="P",N(S15)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="43"/>
@@ -3222,6 +3301,18 @@
         <f aca="false">IF(AND(O16&gt;0,AB16="S"),O16*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE16" s="48" t="str">
+        <f aca="false">IF(AND(AD16="P",AB16&lt;&gt;"S"),N(R16)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF16" s="48" t="str">
+        <f aca="false">IF(AND(AD16="P",AB16="S"),N(AC16)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG16" s="48" t="str">
+        <f aca="false">IF(AD16="P",N(S16)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="43"/>
@@ -3289,6 +3380,18 @@
         <f aca="false">IF(AND(O17&gt;0,AB17="S"),O17*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE17" s="48" t="str">
+        <f aca="false">IF(AND(AD17="P",AB17&lt;&gt;"S"),N(R17)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF17" s="48" t="str">
+        <f aca="false">IF(AND(AD17="P",AB17="S"),N(AC17)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG17" s="48" t="str">
+        <f aca="false">IF(AD17="P",N(S17)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="43"/>
@@ -3356,11 +3459,23 @@
         <f aca="false">IF(AND(O18&gt;0,AB18="S"),O18*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE18" s="48" t="str">
+        <f aca="false">IF(AND(AD18="P",AB18&lt;&gt;"S"),N(R18)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF18" s="48" t="str">
+        <f aca="false">IF(AND(AD18="P",AB18="S"),N(AC18)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG18" s="48" t="str">
+        <f aca="false">IF(AD18="P",N(S18)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="43"/>
       <c r="B19" s="60" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
@@ -3435,6 +3550,18 @@
       <c r="AB19" s="25"/>
       <c r="AC19" s="62" t="n">
         <f aca="false">SUM(AC14:AC18)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="62" t="n">
+        <f aca="false">SUM(AE14:AE18)</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="62" t="n">
+        <f aca="false">SUM(AF14:AF18)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="62" t="n">
+        <f aca="false">SUM(AG14:AG18)</f>
         <v>0</v>
       </c>
     </row>
@@ -3470,7 +3597,7 @@
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="43"/>
       <c r="B21" s="52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C21" s="52"/>
       <c r="D21" s="63"/>
@@ -3567,6 +3694,18 @@
         <f aca="false">IF(AND(O22&gt;0,AB22="S"),O22*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE22" s="48" t="str">
+        <f aca="false">IF(AND(AD22="P",AB22&lt;&gt;"S"),N(R22)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF22" s="48" t="str">
+        <f aca="false">IF(AND(AD22="P",AB22="S"),N(AC22)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG22" s="48" t="str">
+        <f aca="false">IF(AD22="P",N(S22)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="43"/>
@@ -3634,6 +3773,18 @@
         <f aca="false">IF(AND(O23&gt;0,AB23="S"),O23*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE23" s="48" t="str">
+        <f aca="false">IF(AND(AD23="P",AB23&lt;&gt;"S"),N(R23)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF23" s="48" t="str">
+        <f aca="false">IF(AND(AD23="P",AB23="S"),N(AC23)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG23" s="48" t="str">
+        <f aca="false">IF(AD23="P",N(S23)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43"/>
@@ -3701,6 +3852,18 @@
         <f aca="false">IF(AND(O24&gt;0,AB24="S"),O24*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE24" s="48" t="str">
+        <f aca="false">IF(AND(AD24="P",AB24&lt;&gt;"S"),N(R24)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF24" s="48" t="str">
+        <f aca="false">IF(AND(AD24="P",AB24="S"),N(AC24)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG24" s="48" t="str">
+        <f aca="false">IF(AD24="P",N(S24)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="43"/>
@@ -3768,6 +3931,18 @@
         <f aca="false">IF(AND(O25&gt;0,AB25="S"),O25*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE25" s="48" t="str">
+        <f aca="false">IF(AND(AD25="P",AB25&lt;&gt;"S"),N(R25)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF25" s="48" t="str">
+        <f aca="false">IF(AND(AD25="P",AB25="S"),N(AC25)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG25" s="48" t="str">
+        <f aca="false">IF(AD25="P",N(S25)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="43"/>
@@ -3835,11 +4010,23 @@
         <f aca="false">IF(AND(O26&gt;0,AB26="S"),O26*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE26" s="48" t="str">
+        <f aca="false">IF(AND(AD26="P",AB26&lt;&gt;"S"),N(R26)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF26" s="48" t="str">
+        <f aca="false">IF(AND(AD26="P",AB26="S"),N(AC26)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG26" s="48" t="str">
+        <f aca="false">IF(AD26="P",N(S26)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="43"/>
       <c r="B27" s="60" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -3914,6 +4101,18 @@
       <c r="AB27" s="25"/>
       <c r="AC27" s="62" t="n">
         <f aca="false">SUM(AC22:AC26)</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="62" t="n">
+        <f aca="false">SUM(AE22:AE26)</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="62" t="n">
+        <f aca="false">SUM(AF22:AF26)</f>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="62" t="n">
+        <f aca="false">SUM(AG22:AG26)</f>
         <v>0</v>
       </c>
     </row>
@@ -3949,7 +4148,7 @@
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="43"/>
       <c r="B29" s="52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="69"/>
@@ -3984,7 +4183,7 @@
       <c r="A30" s="43"/>
       <c r="B30" s="55"/>
       <c r="C30" s="56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D30" s="57"/>
       <c r="E30" s="58" t="n">
@@ -4050,6 +4249,18 @@
       <c r="AB30" s="55"/>
       <c r="AC30" s="48" t="str">
         <f aca="false">IF(AND(O30&gt;0,AB30="S"),O30*AC$4," ")</f>
+        <v> </v>
+      </c>
+      <c r="AE30" s="48" t="str">
+        <f aca="false">IF(AND(AD30="P",AB30&lt;&gt;"S"),N(R30)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF30" s="48" t="str">
+        <f aca="false">IF(AND(AD30="P",AB30="S"),N(AC30)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG30" s="48" t="str">
+        <f aca="false">IF(AD30="P",N(S30)," ")</f>
         <v> </v>
       </c>
     </row>
@@ -4119,6 +4330,18 @@
         <f aca="false">IF(AND(O31&gt;0,AB31="S"),O31*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE31" s="48" t="str">
+        <f aca="false">IF(AND(AD31="P",AB31&lt;&gt;"S"),N(R31)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF31" s="48" t="str">
+        <f aca="false">IF(AND(AD31="P",AB31="S"),N(AC31)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG31" s="48" t="str">
+        <f aca="false">IF(AD31="P",N(S31)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="43"/>
@@ -4186,6 +4409,18 @@
         <f aca="false">IF(AND(O32&gt;0,AB32="S"),O32*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE32" s="48" t="str">
+        <f aca="false">IF(AND(AD32="P",AB32&lt;&gt;"S"),N(R32)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF32" s="48" t="str">
+        <f aca="false">IF(AND(AD32="P",AB32="S"),N(AC32)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG32" s="48" t="str">
+        <f aca="false">IF(AD32="P",N(S32)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="43"/>
@@ -4253,6 +4488,18 @@
         <f aca="false">IF(AND(O33&gt;0,AB33="S"),O33*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE33" s="48" t="str">
+        <f aca="false">IF(AND(AD33="P",AB33&lt;&gt;"S"),N(R33)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF33" s="48" t="str">
+        <f aca="false">IF(AND(AD33="P",AB33="S"),N(AC33)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG33" s="48" t="str">
+        <f aca="false">IF(AD33="P",N(S33)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="43"/>
@@ -4320,11 +4567,23 @@
         <f aca="false">IF(AND(O34&gt;0,AB34="S"),O34*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE34" s="48" t="str">
+        <f aca="false">IF(AND(AD34="P",AB34&lt;&gt;"S"),N(R34)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF34" s="48" t="str">
+        <f aca="false">IF(AND(AD34="P",AB34="S"),N(AC34)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG34" s="48" t="str">
+        <f aca="false">IF(AD34="P",N(S34)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="43"/>
       <c r="B35" s="60" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -4399,6 +4658,18 @@
       <c r="AB35" s="25"/>
       <c r="AC35" s="62" t="n">
         <f aca="false">SUM(AC30:AC34)</f>
+        <v>0</v>
+      </c>
+      <c r="AE35" s="62" t="n">
+        <f aca="false">SUM(AE30:AE34)</f>
+        <v>0</v>
+      </c>
+      <c r="AF35" s="62" t="n">
+        <f aca="false">SUM(AF30:AF34)</f>
+        <v>0</v>
+      </c>
+      <c r="AG35" s="62" t="n">
+        <f aca="false">SUM(AG30:AG34)</f>
         <v>0</v>
       </c>
     </row>
@@ -4434,7 +4705,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="43"/>
       <c r="B37" s="70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C37" s="70"/>
       <c r="D37" s="71" t="n">
@@ -4472,7 +4743,7 @@
       <c r="A38" s="43"/>
       <c r="B38" s="55"/>
       <c r="C38" s="56" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D38" s="57"/>
       <c r="E38" s="58" t="n">
@@ -4548,12 +4819,24 @@
         <f aca="false">IF(AND(O38&gt;0,AB38="S"),O38*AC$4*(1-M38)," ")</f>
         <v> </v>
       </c>
+      <c r="AE38" s="48" t="str">
+        <f aca="false">IF(AND(AD38="P",AB38&lt;&gt;"S"),N(R38)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF38" s="48" t="str">
+        <f aca="false">IF(AND(AD38="P",AB38="S"),N(AC38)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG38" s="48" t="str">
+        <f aca="false">IF(AD38="P",N(S38)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="43"/>
       <c r="B39" s="55"/>
       <c r="C39" s="56" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D39" s="57"/>
       <c r="E39" s="58" t="n">
@@ -4621,55 +4904,75 @@
       </c>
       <c r="AA39" s="25"/>
       <c r="AB39" s="55" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AC39" s="48" t="n">
         <f aca="false">IF(AND(O39&gt;0,AB39="S"),O39*AC$4*(1-M39)," ")</f>
         <v>540</v>
+      </c>
+      <c r="AE39" s="48" t="str">
+        <f aca="false">IF(AND(AD39="P",AB39&lt;&gt;"S"),N(R39)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF39" s="48" t="str">
+        <f aca="false">IF(AND(AD39="P",AB39="S"),N(AC39)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG39" s="48" t="str">
+        <f aca="false">IF(AD39="P",N(S39)," ")</f>
+        <v> </v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="43"/>
       <c r="B40" s="55"/>
-      <c r="C40" s="56"/>
+      <c r="C40" s="56" t="s">
+        <v>42</v>
+      </c>
       <c r="D40" s="57"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="51" t="str">
+      <c r="E40" s="58" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F40" s="58" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G40" s="51" t="n">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
-        <v> </v>
+        <v>7500</v>
       </c>
       <c r="H40" s="59" t="n">
         <f aca="false">H$37</f>
         <v>0.25</v>
       </c>
-      <c r="I40" s="51" t="str">
+      <c r="I40" s="51" t="n">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J40" s="51" t="str">
+        <v>3125</v>
+      </c>
+      <c r="J40" s="51" t="n">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
-        <v> </v>
-      </c>
-      <c r="K40" s="51" t="str">
+        <v>8125</v>
+      </c>
+      <c r="K40" s="51" t="n">
         <f aca="false">IF(E40&gt;0,IF(V40&gt;0,0,E40-J40)," ")</f>
-        <v> </v>
+        <v>4375</v>
       </c>
       <c r="L40" s="51"/>
       <c r="M40" s="67" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="O40" s="68"/>
+      <c r="O40" s="68" t="n">
+        <v>8000</v>
+      </c>
       <c r="P40" s="49"/>
       <c r="Q40" s="48"/>
-      <c r="R40" s="48" t="str">
+      <c r="R40" s="48" t="n">
         <f aca="false">IF(AND(O40&gt;0,AB40&lt;&gt;"S"),O40*R$4*(1-M40)," ")</f>
-        <v> </v>
-      </c>
-      <c r="S40" s="48" t="str">
+        <v>784</v>
+      </c>
+      <c r="S40" s="48" t="n">
         <f aca="false">IF(O40&gt;0,O40-N(R40)-N(AC40)," ")</f>
-        <v> </v>
+        <v>7216</v>
       </c>
       <c r="T40" s="48"/>
       <c r="U40" s="55"/>
@@ -4695,6 +4998,21 @@
       <c r="AC40" s="48" t="str">
         <f aca="false">IF(AND(O40&gt;0,AB40="S"),O40*AC$4*(1-M40)," ")</f>
         <v> </v>
+      </c>
+      <c r="AD40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE40" s="48" t="n">
+        <f aca="false">IF(AND(AD40="P",AB40&lt;&gt;"S"),N(R40)," ")</f>
+        <v>784</v>
+      </c>
+      <c r="AF40" s="48" t="str">
+        <f aca="false">IF(AND(AD40="P",AB40="S"),N(AC40)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG40" s="48" t="n">
+        <f aca="false">IF(AD40="P",N(S40)," ")</f>
+        <v>7216</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4765,6 +5083,18 @@
         <f aca="false">IF(AND(O41&gt;0,AB41="S"),O41*AC$4*(1-M41)," ")</f>
         <v> </v>
       </c>
+      <c r="AE41" s="48" t="str">
+        <f aca="false">IF(AND(AD41="P",AB41&lt;&gt;"S"),N(R41)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF41" s="48" t="str">
+        <f aca="false">IF(AND(AD41="P",AB41="S"),N(AC41)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG41" s="48" t="str">
+        <f aca="false">IF(AD41="P",N(S41)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="43"/>
@@ -4834,11 +5164,23 @@
         <f aca="false">IF(AND(O42&gt;0,AB42="S"),O42*AC$4*(1-M42)," ")</f>
         <v> </v>
       </c>
+      <c r="AE42" s="48" t="str">
+        <f aca="false">IF(AND(AD42="P",AB42&lt;&gt;"S"),N(R42)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF42" s="48" t="str">
+        <f aca="false">IF(AND(AD42="P",AB42="S"),N(AC42)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG42" s="48" t="str">
+        <f aca="false">IF(AD42="P",N(S42)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="43"/>
       <c r="B43" s="70" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C43" s="70"/>
       <c r="D43" s="71" t="n">
@@ -4937,6 +5279,18 @@
         <f aca="false">IF(AND(O44&gt;0,AB44="S"),O44*AC$4*(1-M44)," ")</f>
         <v> </v>
       </c>
+      <c r="AE44" s="48" t="str">
+        <f aca="false">IF(AND(AD44="P",AB44&lt;&gt;"S"),N(R44)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF44" s="48" t="str">
+        <f aca="false">IF(AND(AD44="P",AB44="S"),N(AC44)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG44" s="48" t="str">
+        <f aca="false">IF(AD44="P",N(S44)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="43"/>
@@ -5006,6 +5360,18 @@
         <f aca="false">IF(AND(O45&gt;0,AB45="S"),O45*AC$4*(1-M45)," ")</f>
         <v> </v>
       </c>
+      <c r="AE45" s="48" t="str">
+        <f aca="false">IF(AND(AD45="P",AB45&lt;&gt;"S"),N(R45)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF45" s="48" t="str">
+        <f aca="false">IF(AND(AD45="P",AB45="S"),N(AC45)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG45" s="48" t="str">
+        <f aca="false">IF(AD45="P",N(S45)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="43"/>
@@ -5075,6 +5441,18 @@
         <f aca="false">IF(AND(O46&gt;0,AB46="S"),O46*AC$4*(1-M46)," ")</f>
         <v> </v>
       </c>
+      <c r="AE46" s="48" t="str">
+        <f aca="false">IF(AND(AD46="P",AB46&lt;&gt;"S"),N(R46)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF46" s="48" t="str">
+        <f aca="false">IF(AND(AD46="P",AB46="S"),N(AC46)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG46" s="48" t="str">
+        <f aca="false">IF(AD46="P",N(S46)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="43"/>
@@ -5144,6 +5522,18 @@
         <f aca="false">IF(AND(O47&gt;0,AB47="S"),O47*AC$4*(1-M47)," ")</f>
         <v> </v>
       </c>
+      <c r="AE47" s="48" t="str">
+        <f aca="false">IF(AND(AD47="P",AB47&lt;&gt;"S"),N(R47)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF47" s="48" t="str">
+        <f aca="false">IF(AND(AD47="P",AB47="S"),N(AC47)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG47" s="48" t="str">
+        <f aca="false">IF(AD47="P",N(S47)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="43"/>
@@ -5213,11 +5603,23 @@
         <f aca="false">IF(AND(O48&gt;0,AB48="S"),O48*AC$4*(1-M48)," ")</f>
         <v> </v>
       </c>
+      <c r="AE48" s="48" t="str">
+        <f aca="false">IF(AND(AD48="P",AB48&lt;&gt;"S"),N(R48)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF48" s="48" t="str">
+        <f aca="false">IF(AND(AD48="P",AB48="S"),N(AC48)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG48" s="48" t="str">
+        <f aca="false">IF(AD48="P",N(S48)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="43"/>
       <c r="B49" s="52" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C49" s="52"/>
       <c r="D49" s="63"/>
@@ -5313,6 +5715,18 @@
         <f aca="false">IF(AND(O50&gt;0,AB50="S"),O50*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE50" s="48" t="str">
+        <f aca="false">IF(AND(AD50="P",AB50&lt;&gt;"S"),N(R50)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF50" s="48" t="str">
+        <f aca="false">IF(AND(AD50="P",AB50="S"),N(AC50)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG50" s="48" t="str">
+        <f aca="false">IF(AD50="P",N(S50)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="43"/>
@@ -5382,6 +5796,18 @@
         <f aca="false">IF(AND(O51&gt;0,AB51="S"),O51*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE51" s="48" t="str">
+        <f aca="false">IF(AND(AD51="P",AB51&lt;&gt;"S"),N(R51)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF51" s="48" t="str">
+        <f aca="false">IF(AND(AD51="P",AB51="S"),N(AC51)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG51" s="48" t="str">
+        <f aca="false">IF(AD51="P",N(S51)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="43"/>
@@ -5451,6 +5877,18 @@
         <f aca="false">IF(AND(O52&gt;0,AB52="S"),O52*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE52" s="48" t="str">
+        <f aca="false">IF(AND(AD52="P",AB52&lt;&gt;"S"),N(R52)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF52" s="48" t="str">
+        <f aca="false">IF(AND(AD52="P",AB52="S"),N(AC52)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG52" s="48" t="str">
+        <f aca="false">IF(AD52="P",N(S52)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="43"/>
@@ -5520,6 +5958,18 @@
         <f aca="false">IF(AND(O53&gt;0,AB53="S"),O53*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE53" s="48" t="str">
+        <f aca="false">IF(AND(AD53="P",AB53&lt;&gt;"S"),N(R53)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF53" s="48" t="str">
+        <f aca="false">IF(AND(AD53="P",AB53="S"),N(AC53)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG53" s="48" t="str">
+        <f aca="false">IF(AD53="P",N(S53)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="43"/>
@@ -5589,45 +6039,57 @@
         <f aca="false">IF(AND(O54&gt;0,AB54="S"),O54*AC$4," ")</f>
         <v> </v>
       </c>
+      <c r="AE54" s="48" t="str">
+        <f aca="false">IF(AND(AD54="P",AB54&lt;&gt;"S"),N(R54)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF54" s="48" t="str">
+        <f aca="false">IF(AND(AD54="P",AB54="S"),N(AC54)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG54" s="48" t="str">
+        <f aca="false">IF(AD54="P",N(S54)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="43"/>
       <c r="B55" s="60" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C55" s="60"/>
       <c r="D55" s="60"/>
       <c r="E55" s="62" t="n">
         <f aca="false">SUM(E38:E54)</f>
-        <v>46000</v>
+        <v>58500</v>
       </c>
       <c r="F55" s="62" t="n">
         <f aca="false">SUM(F38:F54)</f>
-        <v>13828</v>
+        <v>18828</v>
       </c>
       <c r="G55" s="62" t="n">
         <f aca="false">SUM(G38:G54)</f>
-        <v>32172</v>
+        <v>39672</v>
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="62" t="n">
         <f aca="false">SUM(I38:I54)</f>
-        <v>11500</v>
+        <v>14625</v>
       </c>
       <c r="J55" s="62" t="n">
         <f aca="false">SUM(J38:J54)</f>
-        <v>25328</v>
+        <v>33453</v>
       </c>
       <c r="K55" s="62" t="n">
         <f aca="false">SUM(K38:K54)</f>
-        <v>8000</v>
+        <v>12375</v>
       </c>
       <c r="L55" s="51"/>
       <c r="M55" s="72"/>
       <c r="N55" s="51"/>
       <c r="O55" s="62" t="n">
         <f aca="false">SUM(O38:O54)</f>
-        <v>33000</v>
+        <v>41000</v>
       </c>
       <c r="P55" s="63"/>
       <c r="Q55" s="62" t="n">
@@ -5636,11 +6098,11 @@
       </c>
       <c r="R55" s="62" t="n">
         <f aca="false">SUM(R38:R54)</f>
-        <v>3360</v>
+        <v>4144</v>
       </c>
       <c r="S55" s="62" t="n">
         <f aca="false">SUM(S38:S54)</f>
-        <v>29100</v>
+        <v>36316</v>
       </c>
       <c r="T55" s="51"/>
       <c r="U55" s="50"/>
@@ -5669,6 +6131,18 @@
       <c r="AC55" s="62" t="n">
         <f aca="false">SUM(AC38:AC54)</f>
         <v>540</v>
+      </c>
+      <c r="AE55" s="62" t="n">
+        <f aca="false">SUM(AE38:AE54)</f>
+        <v>784</v>
+      </c>
+      <c r="AF55" s="62" t="n">
+        <f aca="false">SUM(AF38:AF54)</f>
+        <v>0</v>
+      </c>
+      <c r="AG55" s="62" t="n">
+        <f aca="false">SUM(AG38:AG54)</f>
+        <v>7216</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5713,35 +6187,35 @@
       </c>
       <c r="E57" s="75" t="n">
         <f aca="false">E11+E19+E27+E35+E55</f>
-        <v>49000</v>
+        <v>61500</v>
       </c>
       <c r="F57" s="75" t="n">
         <f aca="false">F11+F19+F27+F35+F55</f>
-        <v>14098</v>
+        <v>19098</v>
       </c>
       <c r="G57" s="75" t="n">
         <f aca="false">G11+G19+G27+G35+G55</f>
-        <v>34902</v>
+        <v>42402</v>
       </c>
       <c r="H57" s="59"/>
       <c r="I57" s="75" t="n">
         <f aca="false">I11+I19+I27+I35+I55</f>
-        <v>12490</v>
+        <v>15615</v>
       </c>
       <c r="J57" s="75" t="n">
         <f aca="false">J11+J19+J27+J35+J55</f>
-        <v>26588</v>
+        <v>34713</v>
       </c>
       <c r="K57" s="75" t="n">
         <f aca="false">K11+K19+K27+K35+K55</f>
-        <v>9740</v>
+        <v>14115</v>
       </c>
       <c r="L57" s="51"/>
       <c r="M57" s="59"/>
       <c r="N57" s="51"/>
       <c r="O57" s="75" t="n">
         <f aca="false">O11+O19+O27+O35+O55</f>
-        <v>33000</v>
+        <v>41000</v>
       </c>
       <c r="P57" s="63"/>
       <c r="Q57" s="75" t="n">
@@ -5750,11 +6224,11 @@
       </c>
       <c r="R57" s="75" t="n">
         <f aca="false">R11+R19+R27+R35+R55</f>
-        <v>3360</v>
+        <v>4144</v>
       </c>
       <c r="S57" s="75" t="n">
         <f aca="false">S11+S19+S27+S35+S55</f>
-        <v>29100</v>
+        <v>36316</v>
       </c>
       <c r="T57" s="48"/>
       <c r="U57" s="50"/>
@@ -5783,6 +6257,18 @@
       <c r="AC57" s="75" t="n">
         <f aca="false">AC11+AC19+AC27+AC35+AC55</f>
         <v>540</v>
+      </c>
+      <c r="AE57" s="75" t="n">
+        <f aca="false">AE11+AE19+AE27+AE35+AE55</f>
+        <v>784</v>
+      </c>
+      <c r="AF57" s="75" t="n">
+        <f aca="false">AF11+AF19+AF27+AF35+AF55</f>
+        <v>0</v>
+      </c>
+      <c r="AG57" s="75" t="n">
+        <f aca="false">AG11+AG19+AG27+AG35+AG55</f>
+        <v>7216</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5817,7 +6303,7 @@
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="43"/>
       <c r="B59" s="44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C59" s="44"/>
       <c r="D59" s="45" t="n">
@@ -5851,7 +6337,7 @@
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="43"/>
       <c r="B60" s="52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C60" s="52"/>
       <c r="D60" s="53"/>
@@ -6026,7 +6512,7 @@
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="43"/>
       <c r="B64" s="60" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C64" s="60"/>
       <c r="D64" s="60"/>
@@ -6101,6 +6587,18 @@
       <c r="AB64" s="25"/>
       <c r="AC64" s="62" t="n">
         <f aca="false">SUM(AC61:AC63)</f>
+        <v>0</v>
+      </c>
+      <c r="AE64" s="62" t="n">
+        <f aca="false">SUM(AE61:AE63)</f>
+        <v>0</v>
+      </c>
+      <c r="AF64" s="62" t="n">
+        <f aca="false">SUM(AF61:AF63)</f>
+        <v>0</v>
+      </c>
+      <c r="AG64" s="62" t="n">
+        <f aca="false">SUM(AG61:AG63)</f>
         <v>0</v>
       </c>
     </row>
@@ -6136,7 +6634,7 @@
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="43"/>
       <c r="B66" s="52" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C66" s="52"/>
       <c r="D66" s="63"/>
@@ -6173,7 +6671,7 @@
         <v>46157</v>
       </c>
       <c r="C67" s="56" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D67" s="57"/>
       <c r="E67" s="58" t="n">
@@ -6241,7 +6739,7 @@
         <v>46174</v>
       </c>
       <c r="C68" s="56" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D68" s="57"/>
       <c r="E68" s="58" t="n">
@@ -6309,7 +6807,7 @@
         <v>46218</v>
       </c>
       <c r="C69" s="56" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D69" s="57"/>
       <c r="E69" s="58" t="n">
@@ -6377,7 +6875,7 @@
         <v>46266</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D70" s="57"/>
       <c r="E70" s="58" t="n">
@@ -6445,7 +6943,7 @@
         <v>46320</v>
       </c>
       <c r="C71" s="56" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D71" s="57"/>
       <c r="E71" s="58" t="n">
@@ -6510,7 +7008,7 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="43"/>
       <c r="B72" s="60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C72" s="60"/>
       <c r="D72" s="60"/>
@@ -6585,6 +7083,18 @@
       <c r="AB72" s="25"/>
       <c r="AC72" s="62" t="n">
         <f aca="false">SUM(AC67:AC71)</f>
+        <v>0</v>
+      </c>
+      <c r="AE72" s="62" t="n">
+        <f aca="false">SUM(AE67:AE71)</f>
+        <v>0</v>
+      </c>
+      <c r="AF72" s="62" t="n">
+        <f aca="false">SUM(AF67:AF71)</f>
+        <v>0</v>
+      </c>
+      <c r="AG72" s="62" t="n">
+        <f aca="false">SUM(AG67:AG71)</f>
         <v>0</v>
       </c>
     </row>
@@ -6620,7 +7130,7 @@
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="43"/>
       <c r="B74" s="52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C74" s="52"/>
       <c r="D74" s="63"/>
@@ -6964,7 +7474,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="43"/>
       <c r="B80" s="60" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
@@ -7039,6 +7549,18 @@
       <c r="AB80" s="25"/>
       <c r="AC80" s="62" t="n">
         <f aca="false">SUM(AC75:AC79)</f>
+        <v>0</v>
+      </c>
+      <c r="AE80" s="62" t="n">
+        <f aca="false">SUM(AE75:AE79)</f>
+        <v>0</v>
+      </c>
+      <c r="AF80" s="62" t="n">
+        <f aca="false">SUM(AF75:AF79)</f>
+        <v>0</v>
+      </c>
+      <c r="AG80" s="62" t="n">
+        <f aca="false">SUM(AG75:AG79)</f>
         <v>0</v>
       </c>
     </row>
@@ -7074,7 +7596,7 @@
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="43"/>
       <c r="B82" s="52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C82" s="52"/>
       <c r="D82" s="69"/>
@@ -7418,7 +7940,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="43"/>
       <c r="B88" s="60" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C88" s="60"/>
       <c r="D88" s="60"/>
@@ -7493,6 +8015,18 @@
       <c r="AB88" s="25"/>
       <c r="AC88" s="62" t="n">
         <f aca="false">SUM(AC83:AC87)</f>
+        <v>0</v>
+      </c>
+      <c r="AE88" s="62" t="n">
+        <f aca="false">SUM(AE83:AE87)</f>
+        <v>0</v>
+      </c>
+      <c r="AF88" s="62" t="n">
+        <f aca="false">SUM(AF83:AF87)</f>
+        <v>0</v>
+      </c>
+      <c r="AG88" s="62" t="n">
+        <f aca="false">SUM(AG83:AG87)</f>
         <v>0</v>
       </c>
     </row>
@@ -7628,6 +8162,18 @@
         <f aca="false">IF(AND(E91&gt;0,AB91="S"),E91*AC$4*(1-M91)," ")</f>
         <v> </v>
       </c>
+      <c r="AE91" s="48" t="str">
+        <f aca="false">IF(AND(AD91="P",AB91&lt;&gt;"S"),N(R91)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF91" s="48" t="str">
+        <f aca="false">IF(AND(AD91="P",AB91="S"),N(AC91)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG91" s="48" t="str">
+        <f aca="false">IF(AD91="P",N(S91)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="43"/>
@@ -7694,6 +8240,18 @@
         <f aca="false">IF(AND(E92&gt;0,AB92="S"),E92*AC$4*(1-M92)," ")</f>
         <v> </v>
       </c>
+      <c r="AE92" s="48" t="str">
+        <f aca="false">IF(AND(AD92="P",AB92&lt;&gt;"S"),N(R92)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF92" s="48" t="str">
+        <f aca="false">IF(AND(AD92="P",AB92="S"),N(AC92)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG92" s="48" t="str">
+        <f aca="false">IF(AD92="P",N(S92)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="43"/>
@@ -7760,6 +8318,18 @@
         <f aca="false">IF(AND(E93&gt;0,AB93="S"),E93*AC$4*(1-M93)," ")</f>
         <v> </v>
       </c>
+      <c r="AE93" s="48" t="str">
+        <f aca="false">IF(AND(AD93="P",AB93&lt;&gt;"S"),N(R93)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF93" s="48" t="str">
+        <f aca="false">IF(AND(AD93="P",AB93="S"),N(AC93)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG93" s="48" t="str">
+        <f aca="false">IF(AD93="P",N(S93)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="43"/>
@@ -7826,6 +8396,18 @@
         <f aca="false">IF(AND(E94&gt;0,AB94="S"),E94*AC$4*(1-M94)," ")</f>
         <v> </v>
       </c>
+      <c r="AE94" s="48" t="str">
+        <f aca="false">IF(AND(AD94="P",AB94&lt;&gt;"S"),N(R94)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF94" s="48" t="str">
+        <f aca="false">IF(AND(AD94="P",AB94="S"),N(AC94)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG94" s="48" t="str">
+        <f aca="false">IF(AD94="P",N(S94)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="43"/>
@@ -7890,6 +8472,18 @@
       <c r="AB95" s="55"/>
       <c r="AC95" s="48" t="str">
         <f aca="false">IF(AND(E95&gt;0,AB95="S"),E95*AC$4*(1-M95)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AE95" s="48" t="str">
+        <f aca="false">IF(AND(AD95="P",AB95&lt;&gt;"S"),N(R95)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF95" s="48" t="str">
+        <f aca="false">IF(AND(AD95="P",AB95="S"),N(AC95)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG95" s="48" t="str">
+        <f aca="false">IF(AD95="P",N(S95)," ")</f>
         <v> </v>
       </c>
     </row>
@@ -7993,6 +8587,18 @@
         <f aca="false">IF(AND(E97&gt;0,AB97="S"),E97*AC$4*(1-M97)," ")</f>
         <v> </v>
       </c>
+      <c r="AE97" s="48" t="str">
+        <f aca="false">IF(AND(AD97="P",AB97&lt;&gt;"S"),N(R97)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF97" s="48" t="str">
+        <f aca="false">IF(AND(AD97="P",AB97="S"),N(AC97)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG97" s="48" t="str">
+        <f aca="false">IF(AD97="P",N(S97)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="43"/>
@@ -8059,6 +8665,18 @@
         <f aca="false">IF(AND(E98&gt;0,AB98="S"),E98*AC$4*(1-M98)," ")</f>
         <v> </v>
       </c>
+      <c r="AE98" s="48" t="str">
+        <f aca="false">IF(AND(AD98="P",AB98&lt;&gt;"S"),N(R98)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF98" s="48" t="str">
+        <f aca="false">IF(AND(AD98="P",AB98="S"),N(AC98)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG98" s="48" t="str">
+        <f aca="false">IF(AD98="P",N(S98)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="43"/>
@@ -8125,6 +8743,18 @@
         <f aca="false">IF(AND(E99&gt;0,AB99="S"),E99*AC$4*(1-M99)," ")</f>
         <v> </v>
       </c>
+      <c r="AE99" s="48" t="str">
+        <f aca="false">IF(AND(AD99="P",AB99&lt;&gt;"S"),N(R99)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF99" s="48" t="str">
+        <f aca="false">IF(AND(AD99="P",AB99="S"),N(AC99)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG99" s="48" t="str">
+        <f aca="false">IF(AD99="P",N(S99)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="43"/>
@@ -8191,6 +8821,18 @@
         <f aca="false">IF(AND(E100&gt;0,AB100="S"),E100*AC$4*(1-M100)," ")</f>
         <v> </v>
       </c>
+      <c r="AE100" s="48" t="str">
+        <f aca="false">IF(AND(AD100="P",AB100&lt;&gt;"S"),N(R100)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF100" s="48" t="str">
+        <f aca="false">IF(AND(AD100="P",AB100="S"),N(AC100)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG100" s="48" t="str">
+        <f aca="false">IF(AD100="P",N(S100)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="43"/>
@@ -8257,11 +8899,23 @@
         <f aca="false">IF(AND(E101&gt;0,AB101="S"),E101*AC$4*(1-M101)," ")</f>
         <v> </v>
       </c>
+      <c r="AE101" s="48" t="str">
+        <f aca="false">IF(AND(AD101="P",AB101&lt;&gt;"S"),N(R101)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AF101" s="48" t="str">
+        <f aca="false">IF(AND(AD101="P",AB101="S"),N(AC101)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AG101" s="48" t="str">
+        <f aca="false">IF(AD101="P",N(S101)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="43"/>
       <c r="B102" s="52" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C102" s="52"/>
       <c r="D102" s="69"/>
@@ -8612,7 +9266,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="43"/>
       <c r="B108" s="60" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C108" s="60"/>
       <c r="D108" s="60"/>
@@ -8687,6 +9341,18 @@
       <c r="AB108" s="25"/>
       <c r="AC108" s="62" t="n">
         <f aca="false">SUM(AC91:AC107)</f>
+        <v>0</v>
+      </c>
+      <c r="AE108" s="62" t="n">
+        <f aca="false">SUM(AE91:AE107)</f>
+        <v>0</v>
+      </c>
+      <c r="AF108" s="62" t="n">
+        <f aca="false">SUM(AF91:AF107)</f>
+        <v>0</v>
+      </c>
+      <c r="AG108" s="62" t="n">
+        <f aca="false">SUM(AG91:AG107)</f>
         <v>0</v>
       </c>
     </row>
@@ -8801,6 +9467,18 @@
       <c r="AB110" s="25"/>
       <c r="AC110" s="75" t="n">
         <f aca="false">AC64+AC72+AC80+AC88+AC108</f>
+        <v>0</v>
+      </c>
+      <c r="AE110" s="75" t="n">
+        <f aca="false">AE64+AE72+AE80+AE88+AE108</f>
+        <v>0</v>
+      </c>
+      <c r="AF110" s="75" t="n">
+        <f aca="false">AF64+AF72+AF80+AF88+AF108</f>
+        <v>0</v>
+      </c>
+      <c r="AG110" s="75" t="n">
+        <f aca="false">AG64+AG72+AG80+AG88+AG108</f>
         <v>0</v>
       </c>
     </row>
@@ -9197,7 +9875,7 @@
       <c r="C2" s="100"/>
       <c r="D2" s="101"/>
       <c r="E2" s="102" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F2" s="102"/>
       <c r="G2" s="102"/>
@@ -9714,7 +10392,7 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="98"/>
       <c r="B4" s="108" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C4" s="100"/>
       <c r="D4" s="101"/>
@@ -9723,17 +10401,17 @@
       </c>
       <c r="F4" s="103"/>
       <c r="G4" s="110" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H4" s="110"/>
       <c r="I4" s="110"/>
       <c r="J4" s="103"/>
       <c r="K4" s="109" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="103"/>
       <c r="M4" s="111" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N4" s="111"/>
       <c r="O4" s="105"/>
@@ -9983,14 +10661,14 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="98"/>
       <c r="B5" s="99" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C5" s="100"/>
       <c r="D5" s="101"/>
       <c r="E5" s="103"/>
       <c r="F5" s="103"/>
       <c r="G5" s="99" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H5" s="100"/>
       <c r="I5" s="101"/>
@@ -10246,7 +10924,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="98"/>
       <c r="B6" s="112" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C6" s="112"/>
       <c r="D6" s="112"/>
@@ -10256,7 +10934,7 @@
       </c>
       <c r="F6" s="103"/>
       <c r="G6" s="112" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="112"/>
@@ -10515,7 +11193,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98"/>
       <c r="B7" s="112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C7" s="112"/>
       <c r="D7" s="112"/>
@@ -10525,7 +11203,7 @@
       </c>
       <c r="F7" s="103"/>
       <c r="G7" s="112" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H7" s="112"/>
       <c r="I7" s="112"/>
@@ -10784,7 +11462,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="98"/>
       <c r="B8" s="112" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" s="112"/>
       <c r="D8" s="112"/>
@@ -10794,7 +11472,7 @@
       </c>
       <c r="F8" s="103"/>
       <c r="G8" s="112" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H8" s="112"/>
       <c r="I8" s="112"/>
@@ -11053,7 +11731,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="98"/>
       <c r="B9" s="112" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C9" s="112"/>
       <c r="D9" s="112"/>
@@ -11063,7 +11741,7 @@
       </c>
       <c r="F9" s="103"/>
       <c r="G9" s="112" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H9" s="112"/>
       <c r="I9" s="112"/>
@@ -11322,7 +12000,7 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="98"/>
       <c r="B10" s="112" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C10" s="112"/>
       <c r="D10" s="112"/>
@@ -11332,7 +12010,7 @@
       </c>
       <c r="F10" s="103"/>
       <c r="G10" s="112" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H10" s="112"/>
       <c r="I10" s="112"/>
@@ -11591,7 +12269,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="98"/>
       <c r="B11" s="114" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C11" s="114"/>
       <c r="D11" s="114"/>
@@ -11601,7 +12279,7 @@
       </c>
       <c r="F11" s="103"/>
       <c r="G11" s="116" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -12119,7 +12797,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98"/>
       <c r="B13" s="114" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C13" s="114"/>
       <c r="D13" s="114"/>
@@ -12129,7 +12807,7 @@
       </c>
       <c r="F13" s="103"/>
       <c r="G13" s="116" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
@@ -13246,7 +13924,7 @@
       <c r="A2" s="129"/>
       <c r="B2" s="132"/>
       <c r="C2" s="133" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
@@ -13255,7 +13933,7 @@
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H2" s="136"/>
       <c r="I2" s="136"/>
@@ -13267,7 +13945,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="129"/>
       <c r="B3" s="137" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="63"/>
       <c r="D3" s="138"/>
@@ -13299,33 +13977,33 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E5" s="141" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F5" s="141" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I5" s="141" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J5" s="141"/>
       <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M5" s="140"/>
       <c r="N5" s="142"/>
@@ -13583,13 +14261,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="141" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J6" s="141" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K6" s="141" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
@@ -13859,10 +14537,10 @@
         <v>46174</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E8" s="134" t="n">
         <v>13000</v>
@@ -13889,7 +14567,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M8" s="129"/>
     </row>
@@ -13914,10 +14592,10 @@
         <v>46266</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E10" s="134" t="n">
         <v>7000</v>
@@ -13944,7 +14622,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M10" s="129"/>
     </row>
@@ -14059,7 +14737,7 @@
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="129"/>
       <c r="B17" s="137" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="138"/>
@@ -14067,7 +14745,7 @@
       <c r="F17" s="132"/>
       <c r="G17" s="132"/>
       <c r="H17" s="63" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I17" s="132"/>
       <c r="J17" s="132"/>
@@ -14093,33 +14771,33 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E19" s="141" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F19" s="141" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J19" s="141"/>
       <c r="K19" s="141"/>
       <c r="L19" s="21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M19" s="140"/>
       <c r="N19" s="142"/>
@@ -14377,13 +15055,13 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="141" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K20" s="141" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L20" s="21"/>
       <c r="M20" s="140"/>

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t xml:space="preserve">Single Asset Pool Written Down Tax Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written Down Tax Value main pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written Down Tax Value special rate pool</t>
   </si>
   <si>
     <t xml:space="preserve">EXISTING FIXED ASSETS at </t>
@@ -1716,8 +1722,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="8" width="5.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="7" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="8" width="5.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="31" style="7" width="10.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="34" style="1" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="31" style="7" width="10.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="36" style="1" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1823,8 +1829,14 @@
         <f aca="false">AG57+AG110</f>
         <v>7216</v>
       </c>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
+      <c r="AH1" s="13" t="n">
+        <f aca="false">AH57+AH110</f>
+        <v>20640</v>
+      </c>
+      <c r="AI1" s="13" t="n">
+        <f aca="false">AI57+AI110</f>
+        <v>8460</v>
+      </c>
       <c r="AJ1" s="19"/>
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
@@ -2127,6 +2139,12 @@
       </c>
       <c r="AG2" s="22" t="s">
         <v>27</v>
+      </c>
+      <c r="AH2" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI2" s="22" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2706,7 +2724,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43"/>
       <c r="B6" s="44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="45" t="n">
@@ -2740,7 +2758,7 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="43"/>
       <c r="B7" s="52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="53"/>
@@ -2924,7 +2942,7 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43"/>
       <c r="B11" s="60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -3011,6 +3029,14 @@
       </c>
       <c r="AG11" s="62" t="n">
         <f aca="false">SUM(AG8:AG10)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="62" t="n">
+        <f aca="false">SUM(AH8:AH10)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="62" t="n">
+        <f aca="false">SUM(AI8:AI10)</f>
         <v>0</v>
       </c>
     </row>
@@ -3046,7 +3072,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43"/>
       <c r="B13" s="52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="52"/>
       <c r="D13" s="63"/>
@@ -3155,6 +3181,14 @@
         <f aca="false">IF(AD14="P",N(S14)," ")</f>
         <v> </v>
       </c>
+      <c r="AH14" s="48" t="n">
+        <f aca="false">IF(AND(AD14&lt;&gt;"P",AB14&lt;&gt;"S"),N(S14)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="48" t="str">
+        <f aca="false">IF(AND(AD14&lt;&gt;"P",AB14="S"),N(S14)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="43"/>
@@ -3234,6 +3268,14 @@
         <f aca="false">IF(AD15="P",N(S15)," ")</f>
         <v> </v>
       </c>
+      <c r="AH15" s="48" t="n">
+        <f aca="false">IF(AND(AD15&lt;&gt;"P",AB15&lt;&gt;"S"),N(S15)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="48" t="str">
+        <f aca="false">IF(AND(AD15&lt;&gt;"P",AB15="S"),N(S15)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="43"/>
@@ -3313,6 +3355,14 @@
         <f aca="false">IF(AD16="P",N(S16)," ")</f>
         <v> </v>
       </c>
+      <c r="AH16" s="48" t="n">
+        <f aca="false">IF(AND(AD16&lt;&gt;"P",AB16&lt;&gt;"S"),N(S16)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="48" t="str">
+        <f aca="false">IF(AND(AD16&lt;&gt;"P",AB16="S"),N(S16)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="43"/>
@@ -3392,6 +3442,14 @@
         <f aca="false">IF(AD17="P",N(S17)," ")</f>
         <v> </v>
       </c>
+      <c r="AH17" s="48" t="n">
+        <f aca="false">IF(AND(AD17&lt;&gt;"P",AB17&lt;&gt;"S"),N(S17)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="48" t="str">
+        <f aca="false">IF(AND(AD17&lt;&gt;"P",AB17="S"),N(S17)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="43"/>
@@ -3471,11 +3529,19 @@
         <f aca="false">IF(AD18="P",N(S18)," ")</f>
         <v> </v>
       </c>
+      <c r="AH18" s="48" t="n">
+        <f aca="false">IF(AND(AD18&lt;&gt;"P",AB18&lt;&gt;"S"),N(S18)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="48" t="str">
+        <f aca="false">IF(AND(AD18&lt;&gt;"P",AB18="S"),N(S18)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="43"/>
       <c r="B19" s="60" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
@@ -3562,6 +3628,14 @@
       </c>
       <c r="AG19" s="62" t="n">
         <f aca="false">SUM(AG14:AG18)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="62" t="n">
+        <f aca="false">SUM(AH14:AH18)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="62" t="n">
+        <f aca="false">SUM(AI14:AI18)</f>
         <v>0</v>
       </c>
     </row>
@@ -3597,7 +3671,7 @@
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="43"/>
       <c r="B21" s="52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="52"/>
       <c r="D21" s="63"/>
@@ -3706,6 +3780,14 @@
         <f aca="false">IF(AD22="P",N(S22)," ")</f>
         <v> </v>
       </c>
+      <c r="AH22" s="48" t="n">
+        <f aca="false">IF(AND(AD22&lt;&gt;"P",AB22&lt;&gt;"S"),N(S22)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="48" t="str">
+        <f aca="false">IF(AND(AD22&lt;&gt;"P",AB22="S"),N(S22)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="43"/>
@@ -3785,6 +3867,14 @@
         <f aca="false">IF(AD23="P",N(S23)," ")</f>
         <v> </v>
       </c>
+      <c r="AH23" s="48" t="n">
+        <f aca="false">IF(AND(AD23&lt;&gt;"P",AB23&lt;&gt;"S"),N(S23)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="48" t="str">
+        <f aca="false">IF(AND(AD23&lt;&gt;"P",AB23="S"),N(S23)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43"/>
@@ -3864,6 +3954,14 @@
         <f aca="false">IF(AD24="P",N(S24)," ")</f>
         <v> </v>
       </c>
+      <c r="AH24" s="48" t="n">
+        <f aca="false">IF(AND(AD24&lt;&gt;"P",AB24&lt;&gt;"S"),N(S24)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="48" t="str">
+        <f aca="false">IF(AND(AD24&lt;&gt;"P",AB24="S"),N(S24)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="43"/>
@@ -3943,6 +4041,14 @@
         <f aca="false">IF(AD25="P",N(S25)," ")</f>
         <v> </v>
       </c>
+      <c r="AH25" s="48" t="n">
+        <f aca="false">IF(AND(AD25&lt;&gt;"P",AB25&lt;&gt;"S"),N(S25)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="48" t="str">
+        <f aca="false">IF(AND(AD25&lt;&gt;"P",AB25="S"),N(S25)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="43"/>
@@ -4022,11 +4128,19 @@
         <f aca="false">IF(AD26="P",N(S26)," ")</f>
         <v> </v>
       </c>
+      <c r="AH26" s="48" t="n">
+        <f aca="false">IF(AND(AD26&lt;&gt;"P",AB26&lt;&gt;"S"),N(S26)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI26" s="48" t="str">
+        <f aca="false">IF(AND(AD26&lt;&gt;"P",AB26="S"),N(S26)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="43"/>
       <c r="B27" s="60" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -4113,6 +4227,14 @@
       </c>
       <c r="AG27" s="62" t="n">
         <f aca="false">SUM(AG22:AG26)</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="62" t="n">
+        <f aca="false">SUM(AH22:AH26)</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="62" t="n">
+        <f aca="false">SUM(AI22:AI26)</f>
         <v>0</v>
       </c>
     </row>
@@ -4148,7 +4270,7 @@
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="43"/>
       <c r="B29" s="52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="69"/>
@@ -4183,7 +4305,7 @@
       <c r="A30" s="43"/>
       <c r="B30" s="55"/>
       <c r="C30" s="56" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" s="57"/>
       <c r="E30" s="58" t="n">
@@ -4261,6 +4383,14 @@
       </c>
       <c r="AG30" s="48" t="str">
         <f aca="false">IF(AD30="P",N(S30)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AH30" s="48" t="n">
+        <f aca="false">IF(AND(AD30&lt;&gt;"P",AB30&lt;&gt;"S"),N(S30)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="48" t="str">
+        <f aca="false">IF(AND(AD30&lt;&gt;"P",AB30="S"),N(S30)," ")</f>
         <v> </v>
       </c>
     </row>
@@ -4342,6 +4472,14 @@
         <f aca="false">IF(AD31="P",N(S31)," ")</f>
         <v> </v>
       </c>
+      <c r="AH31" s="48" t="n">
+        <f aca="false">IF(AND(AD31&lt;&gt;"P",AB31&lt;&gt;"S"),N(S31)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="48" t="str">
+        <f aca="false">IF(AND(AD31&lt;&gt;"P",AB31="S"),N(S31)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="43"/>
@@ -4421,6 +4559,14 @@
         <f aca="false">IF(AD32="P",N(S32)," ")</f>
         <v> </v>
       </c>
+      <c r="AH32" s="48" t="n">
+        <f aca="false">IF(AND(AD32&lt;&gt;"P",AB32&lt;&gt;"S"),N(S32)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI32" s="48" t="str">
+        <f aca="false">IF(AND(AD32&lt;&gt;"P",AB32="S"),N(S32)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="43"/>
@@ -4500,6 +4646,14 @@
         <f aca="false">IF(AD33="P",N(S33)," ")</f>
         <v> </v>
       </c>
+      <c r="AH33" s="48" t="n">
+        <f aca="false">IF(AND(AD33&lt;&gt;"P",AB33&lt;&gt;"S"),N(S33)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI33" s="48" t="str">
+        <f aca="false">IF(AND(AD33&lt;&gt;"P",AB33="S"),N(S33)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="43"/>
@@ -4579,11 +4733,19 @@
         <f aca="false">IF(AD34="P",N(S34)," ")</f>
         <v> </v>
       </c>
+      <c r="AH34" s="48" t="n">
+        <f aca="false">IF(AND(AD34&lt;&gt;"P",AB34&lt;&gt;"S"),N(S34)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI34" s="48" t="str">
+        <f aca="false">IF(AND(AD34&lt;&gt;"P",AB34="S"),N(S34)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="43"/>
       <c r="B35" s="60" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -4670,6 +4832,14 @@
       </c>
       <c r="AG35" s="62" t="n">
         <f aca="false">SUM(AG30:AG34)</f>
+        <v>0</v>
+      </c>
+      <c r="AH35" s="62" t="n">
+        <f aca="false">SUM(AH30:AH34)</f>
+        <v>0</v>
+      </c>
+      <c r="AI35" s="62" t="n">
+        <f aca="false">SUM(AI30:AI34)</f>
         <v>0</v>
       </c>
     </row>
@@ -4705,7 +4875,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="43"/>
       <c r="B37" s="70" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C37" s="70"/>
       <c r="D37" s="71" t="n">
@@ -4743,7 +4913,7 @@
       <c r="A38" s="43"/>
       <c r="B38" s="55"/>
       <c r="C38" s="56" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D38" s="57"/>
       <c r="E38" s="58" t="n">
@@ -4831,12 +5001,20 @@
         <f aca="false">IF(AD38="P",N(S38)," ")</f>
         <v> </v>
       </c>
+      <c r="AH38" s="48" t="n">
+        <f aca="false">IF(AND(AD38&lt;&gt;"P",AB38&lt;&gt;"S"),N(S38)," ")</f>
+        <v>20640</v>
+      </c>
+      <c r="AI38" s="48" t="str">
+        <f aca="false">IF(AND(AD38&lt;&gt;"P",AB38="S"),N(S38)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="43"/>
       <c r="B39" s="55"/>
       <c r="C39" s="56" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D39" s="57"/>
       <c r="E39" s="58" t="n">
@@ -4904,7 +5082,7 @@
       </c>
       <c r="AA39" s="25"/>
       <c r="AB39" s="55" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AC39" s="48" t="n">
         <f aca="false">IF(AND(O39&gt;0,AB39="S"),O39*AC$4*(1-M39)," ")</f>
@@ -4921,13 +5099,21 @@
       <c r="AG39" s="48" t="str">
         <f aca="false">IF(AD39="P",N(S39)," ")</f>
         <v> </v>
+      </c>
+      <c r="AH39" s="48" t="str">
+        <f aca="false">IF(AND(AD39&lt;&gt;"P",AB39&lt;&gt;"S"),N(S39)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AI39" s="48" t="n">
+        <f aca="false">IF(AND(AD39&lt;&gt;"P",AB39="S"),N(S39)," ")</f>
+        <v>8460</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="43"/>
       <c r="B40" s="55"/>
       <c r="C40" s="56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D40" s="57"/>
       <c r="E40" s="58" t="n">
@@ -5000,7 +5186,7 @@
         <v> </v>
       </c>
       <c r="AD40" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AE40" s="48" t="n">
         <f aca="false">IF(AND(AD40="P",AB40&lt;&gt;"S"),N(R40)," ")</f>
@@ -5013,6 +5199,14 @@
       <c r="AG40" s="48" t="n">
         <f aca="false">IF(AD40="P",N(S40)," ")</f>
         <v>7216</v>
+      </c>
+      <c r="AH40" s="48" t="str">
+        <f aca="false">IF(AND(AD40&lt;&gt;"P",AB40&lt;&gt;"S"),N(S40)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AI40" s="48" t="str">
+        <f aca="false">IF(AND(AD40&lt;&gt;"P",AB40="S"),N(S40)," ")</f>
+        <v> </v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,6 +5289,14 @@
         <f aca="false">IF(AD41="P",N(S41)," ")</f>
         <v> </v>
       </c>
+      <c r="AH41" s="48" t="n">
+        <f aca="false">IF(AND(AD41&lt;&gt;"P",AB41&lt;&gt;"S"),N(S41)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI41" s="48" t="str">
+        <f aca="false">IF(AND(AD41&lt;&gt;"P",AB41="S"),N(S41)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="43"/>
@@ -5176,11 +5378,19 @@
         <f aca="false">IF(AD42="P",N(S42)," ")</f>
         <v> </v>
       </c>
+      <c r="AH42" s="48" t="n">
+        <f aca="false">IF(AND(AD42&lt;&gt;"P",AB42&lt;&gt;"S"),N(S42)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI42" s="48" t="str">
+        <f aca="false">IF(AND(AD42&lt;&gt;"P",AB42="S"),N(S42)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="43"/>
       <c r="B43" s="70" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C43" s="70"/>
       <c r="D43" s="71" t="n">
@@ -5291,6 +5501,14 @@
         <f aca="false">IF(AD44="P",N(S44)," ")</f>
         <v> </v>
       </c>
+      <c r="AH44" s="48" t="n">
+        <f aca="false">IF(AND(AD44&lt;&gt;"P",AB44&lt;&gt;"S"),N(S44)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI44" s="48" t="str">
+        <f aca="false">IF(AND(AD44&lt;&gt;"P",AB44="S"),N(S44)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="43"/>
@@ -5372,6 +5590,14 @@
         <f aca="false">IF(AD45="P",N(S45)," ")</f>
         <v> </v>
       </c>
+      <c r="AH45" s="48" t="n">
+        <f aca="false">IF(AND(AD45&lt;&gt;"P",AB45&lt;&gt;"S"),N(S45)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI45" s="48" t="str">
+        <f aca="false">IF(AND(AD45&lt;&gt;"P",AB45="S"),N(S45)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="43"/>
@@ -5453,6 +5679,14 @@
         <f aca="false">IF(AD46="P",N(S46)," ")</f>
         <v> </v>
       </c>
+      <c r="AH46" s="48" t="n">
+        <f aca="false">IF(AND(AD46&lt;&gt;"P",AB46&lt;&gt;"S"),N(S46)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI46" s="48" t="str">
+        <f aca="false">IF(AND(AD46&lt;&gt;"P",AB46="S"),N(S46)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="43"/>
@@ -5534,6 +5768,14 @@
         <f aca="false">IF(AD47="P",N(S47)," ")</f>
         <v> </v>
       </c>
+      <c r="AH47" s="48" t="n">
+        <f aca="false">IF(AND(AD47&lt;&gt;"P",AB47&lt;&gt;"S"),N(S47)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI47" s="48" t="str">
+        <f aca="false">IF(AND(AD47&lt;&gt;"P",AB47="S"),N(S47)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="43"/>
@@ -5615,11 +5857,19 @@
         <f aca="false">IF(AD48="P",N(S48)," ")</f>
         <v> </v>
       </c>
+      <c r="AH48" s="48" t="n">
+        <f aca="false">IF(AND(AD48&lt;&gt;"P",AB48&lt;&gt;"S"),N(S48)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI48" s="48" t="str">
+        <f aca="false">IF(AND(AD48&lt;&gt;"P",AB48="S"),N(S48)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="43"/>
       <c r="B49" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C49" s="52"/>
       <c r="D49" s="63"/>
@@ -5727,6 +5977,14 @@
         <f aca="false">IF(AD50="P",N(S50)," ")</f>
         <v> </v>
       </c>
+      <c r="AH50" s="48" t="n">
+        <f aca="false">IF(AND(AD50&lt;&gt;"P",AB50&lt;&gt;"S"),N(S50)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI50" s="48" t="str">
+        <f aca="false">IF(AND(AD50&lt;&gt;"P",AB50="S"),N(S50)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="43"/>
@@ -5808,6 +6066,14 @@
         <f aca="false">IF(AD51="P",N(S51)," ")</f>
         <v> </v>
       </c>
+      <c r="AH51" s="48" t="n">
+        <f aca="false">IF(AND(AD51&lt;&gt;"P",AB51&lt;&gt;"S"),N(S51)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI51" s="48" t="str">
+        <f aca="false">IF(AND(AD51&lt;&gt;"P",AB51="S"),N(S51)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="43"/>
@@ -5889,6 +6155,14 @@
         <f aca="false">IF(AD52="P",N(S52)," ")</f>
         <v> </v>
       </c>
+      <c r="AH52" s="48" t="n">
+        <f aca="false">IF(AND(AD52&lt;&gt;"P",AB52&lt;&gt;"S"),N(S52)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI52" s="48" t="str">
+        <f aca="false">IF(AND(AD52&lt;&gt;"P",AB52="S"),N(S52)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="43"/>
@@ -5970,6 +6244,14 @@
         <f aca="false">IF(AD53="P",N(S53)," ")</f>
         <v> </v>
       </c>
+      <c r="AH53" s="48" t="n">
+        <f aca="false">IF(AND(AD53&lt;&gt;"P",AB53&lt;&gt;"S"),N(S53)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI53" s="48" t="str">
+        <f aca="false">IF(AND(AD53&lt;&gt;"P",AB53="S"),N(S53)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="43"/>
@@ -6051,11 +6333,19 @@
         <f aca="false">IF(AD54="P",N(S54)," ")</f>
         <v> </v>
       </c>
+      <c r="AH54" s="48" t="n">
+        <f aca="false">IF(AND(AD54&lt;&gt;"P",AB54&lt;&gt;"S"),N(S54)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI54" s="48" t="str">
+        <f aca="false">IF(AND(AD54&lt;&gt;"P",AB54="S"),N(S54)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="43"/>
       <c r="B55" s="60" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C55" s="60"/>
       <c r="D55" s="60"/>
@@ -6143,6 +6433,14 @@
       <c r="AG55" s="62" t="n">
         <f aca="false">SUM(AG38:AG54)</f>
         <v>7216</v>
+      </c>
+      <c r="AH55" s="62" t="n">
+        <f aca="false">SUM(AH38:AH54)</f>
+        <v>20640</v>
+      </c>
+      <c r="AI55" s="62" t="n">
+        <f aca="false">SUM(AI38:AI54)</f>
+        <v>8460</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6270,6 +6568,14 @@
         <f aca="false">AG11+AG19+AG27+AG35+AG55</f>
         <v>7216</v>
       </c>
+      <c r="AH57" s="75" t="n">
+        <f aca="false">AH11+AH19+AH27+AH35+AH55</f>
+        <v>20640</v>
+      </c>
+      <c r="AI57" s="75" t="n">
+        <f aca="false">AI11+AI19+AI27+AI35+AI55</f>
+        <v>8460</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="43"/>
@@ -6303,7 +6609,7 @@
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="43"/>
       <c r="B59" s="44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C59" s="44"/>
       <c r="D59" s="45" t="n">
@@ -6337,7 +6643,7 @@
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="43"/>
       <c r="B60" s="52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C60" s="52"/>
       <c r="D60" s="53"/>
@@ -6512,7 +6818,7 @@
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="43"/>
       <c r="B64" s="60" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C64" s="60"/>
       <c r="D64" s="60"/>
@@ -6599,6 +6905,14 @@
       </c>
       <c r="AG64" s="62" t="n">
         <f aca="false">SUM(AG61:AG63)</f>
+        <v>0</v>
+      </c>
+      <c r="AH64" s="62" t="n">
+        <f aca="false">SUM(AH61:AH63)</f>
+        <v>0</v>
+      </c>
+      <c r="AI64" s="62" t="n">
+        <f aca="false">SUM(AI61:AI63)</f>
         <v>0</v>
       </c>
     </row>
@@ -6634,7 +6948,7 @@
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="43"/>
       <c r="B66" s="52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C66" s="52"/>
       <c r="D66" s="63"/>
@@ -6671,7 +6985,7 @@
         <v>46157</v>
       </c>
       <c r="C67" s="56" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D67" s="57"/>
       <c r="E67" s="58" t="n">
@@ -6739,7 +7053,7 @@
         <v>46174</v>
       </c>
       <c r="C68" s="56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D68" s="57"/>
       <c r="E68" s="58" t="n">
@@ -6807,7 +7121,7 @@
         <v>46218</v>
       </c>
       <c r="C69" s="56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D69" s="57"/>
       <c r="E69" s="58" t="n">
@@ -6875,7 +7189,7 @@
         <v>46266</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D70" s="57"/>
       <c r="E70" s="58" t="n">
@@ -6943,7 +7257,7 @@
         <v>46320</v>
       </c>
       <c r="C71" s="56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D71" s="57"/>
       <c r="E71" s="58" t="n">
@@ -7008,7 +7322,7 @@
     <row r="72" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="43"/>
       <c r="B72" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C72" s="60"/>
       <c r="D72" s="60"/>
@@ -7095,6 +7409,14 @@
       </c>
       <c r="AG72" s="62" t="n">
         <f aca="false">SUM(AG67:AG71)</f>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="62" t="n">
+        <f aca="false">SUM(AH67:AH71)</f>
+        <v>0</v>
+      </c>
+      <c r="AI72" s="62" t="n">
+        <f aca="false">SUM(AI67:AI71)</f>
         <v>0</v>
       </c>
     </row>
@@ -7130,7 +7452,7 @@
     <row r="74" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="43"/>
       <c r="B74" s="52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C74" s="52"/>
       <c r="D74" s="63"/>
@@ -7474,7 +7796,7 @@
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="43"/>
       <c r="B80" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
@@ -7561,6 +7883,14 @@
       </c>
       <c r="AG80" s="62" t="n">
         <f aca="false">SUM(AG75:AG79)</f>
+        <v>0</v>
+      </c>
+      <c r="AH80" s="62" t="n">
+        <f aca="false">SUM(AH75:AH79)</f>
+        <v>0</v>
+      </c>
+      <c r="AI80" s="62" t="n">
+        <f aca="false">SUM(AI75:AI79)</f>
         <v>0</v>
       </c>
     </row>
@@ -7596,7 +7926,7 @@
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="43"/>
       <c r="B82" s="52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C82" s="52"/>
       <c r="D82" s="69"/>
@@ -7940,7 +8270,7 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="43"/>
       <c r="B88" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C88" s="60"/>
       <c r="D88" s="60"/>
@@ -8027,6 +8357,14 @@
       </c>
       <c r="AG88" s="62" t="n">
         <f aca="false">SUM(AG83:AG87)</f>
+        <v>0</v>
+      </c>
+      <c r="AH88" s="62" t="n">
+        <f aca="false">SUM(AH83:AH87)</f>
+        <v>0</v>
+      </c>
+      <c r="AI88" s="62" t="n">
+        <f aca="false">SUM(AI83:AI87)</f>
         <v>0</v>
       </c>
     </row>
@@ -8174,6 +8512,14 @@
         <f aca="false">IF(AD91="P",N(S91)," ")</f>
         <v> </v>
       </c>
+      <c r="AH91" s="48" t="n">
+        <f aca="false">IF(AND(AD91&lt;&gt;"P",AB91&lt;&gt;"S"),N(S91)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI91" s="48" t="str">
+        <f aca="false">IF(AND(AD91&lt;&gt;"P",AB91="S"),N(S91)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="43"/>
@@ -8252,6 +8598,14 @@
         <f aca="false">IF(AD92="P",N(S92)," ")</f>
         <v> </v>
       </c>
+      <c r="AH92" s="48" t="n">
+        <f aca="false">IF(AND(AD92&lt;&gt;"P",AB92&lt;&gt;"S"),N(S92)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI92" s="48" t="str">
+        <f aca="false">IF(AND(AD92&lt;&gt;"P",AB92="S"),N(S92)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="43"/>
@@ -8330,6 +8684,14 @@
         <f aca="false">IF(AD93="P",N(S93)," ")</f>
         <v> </v>
       </c>
+      <c r="AH93" s="48" t="n">
+        <f aca="false">IF(AND(AD93&lt;&gt;"P",AB93&lt;&gt;"S"),N(S93)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI93" s="48" t="str">
+        <f aca="false">IF(AND(AD93&lt;&gt;"P",AB93="S"),N(S93)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="43"/>
@@ -8408,6 +8770,14 @@
         <f aca="false">IF(AD94="P",N(S94)," ")</f>
         <v> </v>
       </c>
+      <c r="AH94" s="48" t="n">
+        <f aca="false">IF(AND(AD94&lt;&gt;"P",AB94&lt;&gt;"S"),N(S94)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI94" s="48" t="str">
+        <f aca="false">IF(AND(AD94&lt;&gt;"P",AB94="S"),N(S94)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="43"/>
@@ -8484,6 +8854,14 @@
       </c>
       <c r="AG95" s="48" t="str">
         <f aca="false">IF(AD95="P",N(S95)," ")</f>
+        <v> </v>
+      </c>
+      <c r="AH95" s="48" t="n">
+        <f aca="false">IF(AND(AD95&lt;&gt;"P",AB95&lt;&gt;"S"),N(S95)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI95" s="48" t="str">
+        <f aca="false">IF(AND(AD95&lt;&gt;"P",AB95="S"),N(S95)," ")</f>
         <v> </v>
       </c>
     </row>
@@ -8599,6 +8977,14 @@
         <f aca="false">IF(AD97="P",N(S97)," ")</f>
         <v> </v>
       </c>
+      <c r="AH97" s="48" t="n">
+        <f aca="false">IF(AND(AD97&lt;&gt;"P",AB97&lt;&gt;"S"),N(S97)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI97" s="48" t="str">
+        <f aca="false">IF(AND(AD97&lt;&gt;"P",AB97="S"),N(S97)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="43"/>
@@ -8677,6 +9063,14 @@
         <f aca="false">IF(AD98="P",N(S98)," ")</f>
         <v> </v>
       </c>
+      <c r="AH98" s="48" t="n">
+        <f aca="false">IF(AND(AD98&lt;&gt;"P",AB98&lt;&gt;"S"),N(S98)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI98" s="48" t="str">
+        <f aca="false">IF(AND(AD98&lt;&gt;"P",AB98="S"),N(S98)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="43"/>
@@ -8755,6 +9149,14 @@
         <f aca="false">IF(AD99="P",N(S99)," ")</f>
         <v> </v>
       </c>
+      <c r="AH99" s="48" t="n">
+        <f aca="false">IF(AND(AD99&lt;&gt;"P",AB99&lt;&gt;"S"),N(S99)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI99" s="48" t="str">
+        <f aca="false">IF(AND(AD99&lt;&gt;"P",AB99="S"),N(S99)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="43"/>
@@ -8833,6 +9235,14 @@
         <f aca="false">IF(AD100="P",N(S100)," ")</f>
         <v> </v>
       </c>
+      <c r="AH100" s="48" t="n">
+        <f aca="false">IF(AND(AD100&lt;&gt;"P",AB100&lt;&gt;"S"),N(S100)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI100" s="48" t="str">
+        <f aca="false">IF(AND(AD100&lt;&gt;"P",AB100="S"),N(S100)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="43"/>
@@ -8911,11 +9321,19 @@
         <f aca="false">IF(AD101="P",N(S101)," ")</f>
         <v> </v>
       </c>
+      <c r="AH101" s="48" t="n">
+        <f aca="false">IF(AND(AD101&lt;&gt;"P",AB101&lt;&gt;"S"),N(S101)," ")</f>
+        <v>0</v>
+      </c>
+      <c r="AI101" s="48" t="str">
+        <f aca="false">IF(AND(AD101&lt;&gt;"P",AB101="S"),N(S101)," ")</f>
+        <v> </v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="43"/>
       <c r="B102" s="52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C102" s="52"/>
       <c r="D102" s="69"/>
@@ -9266,7 +9684,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="43"/>
       <c r="B108" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C108" s="60"/>
       <c r="D108" s="60"/>
@@ -9353,6 +9771,14 @@
       </c>
       <c r="AG108" s="62" t="n">
         <f aca="false">SUM(AG91:AG107)</f>
+        <v>0</v>
+      </c>
+      <c r="AH108" s="62" t="n">
+        <f aca="false">SUM(AH91:AH107)</f>
+        <v>0</v>
+      </c>
+      <c r="AI108" s="62" t="n">
+        <f aca="false">SUM(AI91:AI107)</f>
         <v>0</v>
       </c>
     </row>
@@ -9479,6 +9905,14 @@
       </c>
       <c r="AG110" s="75" t="n">
         <f aca="false">AG64+AG72+AG80+AG88+AG108</f>
+        <v>0</v>
+      </c>
+      <c r="AH110" s="75" t="n">
+        <f aca="false">AH64+AH72+AH80+AH88+AH108</f>
+        <v>0</v>
+      </c>
+      <c r="AI110" s="75" t="n">
+        <f aca="false">AI64+AI72+AI80+AI88+AI108</f>
         <v>0</v>
       </c>
     </row>
@@ -9875,7 +10309,7 @@
       <c r="C2" s="100"/>
       <c r="D2" s="101"/>
       <c r="E2" s="102" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="102"/>
       <c r="G2" s="102"/>
@@ -10392,7 +10826,7 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="98"/>
       <c r="B4" s="108" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" s="100"/>
       <c r="D4" s="101"/>
@@ -10401,17 +10835,17 @@
       </c>
       <c r="F4" s="103"/>
       <c r="G4" s="110" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H4" s="110"/>
       <c r="I4" s="110"/>
       <c r="J4" s="103"/>
       <c r="K4" s="109" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L4" s="103"/>
       <c r="M4" s="111" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N4" s="111"/>
       <c r="O4" s="105"/>
@@ -10661,14 +11095,14 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="98"/>
       <c r="B5" s="99" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="100"/>
       <c r="D5" s="101"/>
       <c r="E5" s="103"/>
       <c r="F5" s="103"/>
       <c r="G5" s="99" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="100"/>
       <c r="I5" s="101"/>
@@ -10924,7 +11358,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="98"/>
       <c r="B6" s="112" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="112"/>
       <c r="D6" s="112"/>
@@ -10934,7 +11368,7 @@
       </c>
       <c r="F6" s="103"/>
       <c r="G6" s="112" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="112"/>
@@ -11193,7 +11627,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="98"/>
       <c r="B7" s="112" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="112"/>
       <c r="D7" s="112"/>
@@ -11203,7 +11637,7 @@
       </c>
       <c r="F7" s="103"/>
       <c r="G7" s="112" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H7" s="112"/>
       <c r="I7" s="112"/>
@@ -11462,7 +11896,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="98"/>
       <c r="B8" s="112" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="112"/>
       <c r="D8" s="112"/>
@@ -11472,7 +11906,7 @@
       </c>
       <c r="F8" s="103"/>
       <c r="G8" s="112" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" s="112"/>
       <c r="I8" s="112"/>
@@ -11731,7 +12165,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="98"/>
       <c r="B9" s="112" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="112"/>
       <c r="D9" s="112"/>
@@ -11741,7 +12175,7 @@
       </c>
       <c r="F9" s="103"/>
       <c r="G9" s="112" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H9" s="112"/>
       <c r="I9" s="112"/>
@@ -12000,7 +12434,7 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="98"/>
       <c r="B10" s="112" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="112"/>
       <c r="D10" s="112"/>
@@ -12010,7 +12444,7 @@
       </c>
       <c r="F10" s="103"/>
       <c r="G10" s="112" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H10" s="112"/>
       <c r="I10" s="112"/>
@@ -12269,7 +12703,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="98"/>
       <c r="B11" s="114" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="114"/>
       <c r="D11" s="114"/>
@@ -12279,7 +12713,7 @@
       </c>
       <c r="F11" s="103"/>
       <c r="G11" s="116" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -12797,7 +13231,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98"/>
       <c r="B13" s="114" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C13" s="114"/>
       <c r="D13" s="114"/>
@@ -12807,7 +13241,7 @@
       </c>
       <c r="F13" s="103"/>
       <c r="G13" s="116" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
@@ -13924,7 +14358,7 @@
       <c r="A2" s="129"/>
       <c r="B2" s="132"/>
       <c r="C2" s="133" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
@@ -13933,7 +14367,7 @@
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H2" s="136"/>
       <c r="I2" s="136"/>
@@ -13945,7 +14379,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="129"/>
       <c r="B3" s="137" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="63"/>
       <c r="D3" s="138"/>
@@ -13977,33 +14411,33 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5" s="141" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" s="141" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I5" s="141" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J5" s="141"/>
       <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M5" s="140"/>
       <c r="N5" s="142"/>
@@ -14261,13 +14695,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="141" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J6" s="141" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K6" s="141" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
@@ -14537,10 +14971,10 @@
         <v>46174</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" s="134" t="n">
         <v>13000</v>
@@ -14567,7 +15001,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M8" s="129"/>
     </row>
@@ -14592,10 +15026,10 @@
         <v>46266</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" s="134" t="n">
         <v>7000</v>
@@ -14622,7 +15056,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M10" s="129"/>
     </row>
@@ -14737,7 +15171,7 @@
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="129"/>
       <c r="B17" s="137" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="138"/>
@@ -14745,7 +15179,7 @@
       <c r="F17" s="132"/>
       <c r="G17" s="132"/>
       <c r="H17" s="63" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I17" s="132"/>
       <c r="J17" s="132"/>
@@ -14771,33 +15205,33 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E19" s="141" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F19" s="141" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J19" s="141"/>
       <c r="K19" s="141"/>
       <c r="L19" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M19" s="140"/>
       <c r="N19" s="142"/>
@@ -15055,13 +15489,13 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="141" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K20" s="141" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L20" s="21"/>
       <c r="M20" s="140"/>

--- a/examples/se-latest/Fixedassets.xlsx
+++ b/examples/se-latest/Fixedassets.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="112">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -335,6 +335,60 @@
   </si>
   <si>
     <t xml:space="preserve">New Motor Vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRUCTURES AND BUILDINGS ALLOWANCE (SA103F boxes 53 and 53.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date first in qualifying use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualifying expenditure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax site (F = Freeport or Investment Zone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date qualifying use ceased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days claimed this year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowance this year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit 4 Trafford Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M17 1AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L24 9AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structures and Buildings Allowance (box 53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freeport and Investment Zone SBA (box 53.1)</t>
   </si>
   <si>
     <t xml:space="preserve">FIXED ASSET RECONCILIATION</t>
@@ -1454,6 +1508,16 @@
             <v>0.06</v>
           </cell>
         </row>
+        <row r="9">
+          <cell r="G9">
+            <v>0.03</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="G10">
+            <v>0.1</v>
+          </cell>
+        </row>
         <row r="13">
           <cell r="G13">
             <v>0</v>
@@ -1691,7 +1755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IW111"/>
+  <dimension ref="A1:IW121"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.66"/>
@@ -9944,6 +10008,184 @@
       <c r="Y111" s="92"/>
       <c r="Z111" s="92"/>
       <c r="AA111" s="94"/>
+    </row>
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B113" s="44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B114" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C114" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D114" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E114" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G114" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H114" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="I114" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J114" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="K114" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="27" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C115" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D115" s="55"/>
+      <c r="E115" s="58" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F115" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="G115" s="55"/>
+      <c r="H115" s="29" t="n">
+        <f aca="false">IF(E115&gt;0,IF(G115="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v>0.03</v>
+      </c>
+      <c r="I115" s="27"/>
+      <c r="J115" s="48" t="n">
+        <f aca="false">IF(E115&gt;0,MAX(0,MIN($S$4,IF(N(I115)&gt;0,I115,$S$4),EDATE(B115,IF(G115="F",120,400))-1)-MAX($D$6,B115)+1)," ")</f>
+        <v>365</v>
+      </c>
+      <c r="K115" s="48" t="n">
+        <f aca="false">IF(E115&gt;0,E115*H115*J115/($S$4-$D$6+1)," ")</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="E116" s="58" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F116" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G116" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="H116" s="29" t="n">
+        <f aca="false">IF(E116&gt;0,IF(G116="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v>0.1</v>
+      </c>
+      <c r="I116" s="27"/>
+      <c r="J116" s="48" t="n">
+        <f aca="false">IF(E116&gt;0,MAX(0,MIN($S$4,IF(N(I116)&gt;0,I116,$S$4),EDATE(B116,IF(G116="F",120,400))-1)-MAX($D$6,B116)+1)," ")</f>
+        <v>187</v>
+      </c>
+      <c r="K116" s="48" t="n">
+        <f aca="false">IF(E116&gt;0,E116*H116*J116/($S$4-$D$6+1)," ")</f>
+        <v>1024.65753424658</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="27"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="58"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="29" t="str">
+        <f aca="false">IF(E117&gt;0,IF(G117="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v> </v>
+      </c>
+      <c r="I117" s="27"/>
+      <c r="J117" s="48" t="str">
+        <f aca="false">IF(E117&gt;0,MAX(0,MIN($S$4,IF(N(I117)&gt;0,I117,$S$4),EDATE(B117,IF(G117="F",120,400))-1)-MAX($D$6,B117)+1)," ")</f>
+        <v> </v>
+      </c>
+      <c r="K117" s="48" t="str">
+        <f aca="false">IF(E117&gt;0,E117*H117*J117/($S$4-$D$6+1)," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="27"/>
+      <c r="C118" s="55"/>
+      <c r="D118" s="55"/>
+      <c r="E118" s="58"/>
+      <c r="F118" s="55"/>
+      <c r="G118" s="55"/>
+      <c r="H118" s="29" t="str">
+        <f aca="false">IF(E118&gt;0,IF(G118="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v> </v>
+      </c>
+      <c r="I118" s="27"/>
+      <c r="J118" s="48" t="str">
+        <f aca="false">IF(E118&gt;0,MAX(0,MIN($S$4,IF(N(I118)&gt;0,I118,$S$4),EDATE(B118,IF(G118="F",120,400))-1)-MAX($D$6,B118)+1)," ")</f>
+        <v> </v>
+      </c>
+      <c r="K118" s="48" t="str">
+        <f aca="false">IF(E118&gt;0,E118*H118*J118/($S$4-$D$6+1)," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="27"/>
+      <c r="C119" s="55"/>
+      <c r="D119" s="55"/>
+      <c r="E119" s="58"/>
+      <c r="F119" s="55"/>
+      <c r="G119" s="55"/>
+      <c r="H119" s="29" t="str">
+        <f aca="false">IF(E119&gt;0,IF(G119="F",[1]Admin!$G$10,[1]Admin!$G$9)," ")</f>
+        <v> </v>
+      </c>
+      <c r="I119" s="27"/>
+      <c r="J119" s="48" t="str">
+        <f aca="false">IF(E119&gt;0,MAX(0,MIN($S$4,IF(N(I119)&gt;0,I119,$S$4),EDATE(B119,IF(G119="F",120,400))-1)-MAX($D$6,B119)+1)," ")</f>
+        <v> </v>
+      </c>
+      <c r="K119" s="48" t="str">
+        <f aca="false">IF(E119&gt;0,E119*H119*J119/($S$4-$D$6+1)," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="262.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="K120" s="62" t="n">
+        <f aca="false">SUMIF(G115:G119,"&lt;&gt;F",K115:K119)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="294" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="K121" s="62" t="n">
+        <f aca="false">SUMIF(G115:G119,"F",K115:K119)</f>
+        <v>1024.65753424658</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -10309,7 +10551,7 @@
       <c r="C2" s="100"/>
       <c r="D2" s="101"/>
       <c r="E2" s="102" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F2" s="102"/>
       <c r="G2" s="102"/>
@@ -10826,7 +11068,7 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="98"/>
       <c r="B4" s="108" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C4" s="100"/>
       <c r="D4" s="101"/>
@@ -10835,17 +11077,17 @@
       </c>
       <c r="F4" s="103"/>
       <c r="G4" s="110" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H4" s="110"/>
       <c r="I4" s="110"/>
       <c r="J4" s="103"/>
       <c r="K4" s="109" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="L4" s="103"/>
       <c r="M4" s="111" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="N4" s="111"/>
       <c r="O4" s="105"/>
@@ -11095,14 +11337,14 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="98"/>
       <c r="B5" s="99" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C5" s="100"/>
       <c r="D5" s="101"/>
       <c r="E5" s="103"/>
       <c r="F5" s="103"/>
       <c r="G5" s="99" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H5" s="100"/>
       <c r="I5" s="101"/>
@@ -11368,7 +11610,7 @@
       </c>
       <c r="F6" s="103"/>
       <c r="G6" s="112" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H6" s="112"/>
       <c r="I6" s="112"/>
@@ -11637,7 +11879,7 @@
       </c>
       <c r="F7" s="103"/>
       <c r="G7" s="112" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H7" s="112"/>
       <c r="I7" s="112"/>
@@ -11906,7 +12148,7 @@
       </c>
       <c r="F8" s="103"/>
       <c r="G8" s="112" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="H8" s="112"/>
       <c r="I8" s="112"/>
@@ -12175,7 +12417,7 @@
       </c>
       <c r="F9" s="103"/>
       <c r="G9" s="112" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H9" s="112"/>
       <c r="I9" s="112"/>
@@ -12444,7 +12686,7 @@
       </c>
       <c r="F10" s="103"/>
       <c r="G10" s="112" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H10" s="112"/>
       <c r="I10" s="112"/>
@@ -12703,7 +12945,7 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="98"/>
       <c r="B11" s="114" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C11" s="114"/>
       <c r="D11" s="114"/>
@@ -12713,7 +12955,7 @@
       </c>
       <c r="F11" s="103"/>
       <c r="G11" s="116" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H11" s="116"/>
       <c r="I11" s="116"/>
@@ -13231,7 +13473,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="98"/>
       <c r="B13" s="114" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C13" s="114"/>
       <c r="D13" s="114"/>
@@ -13241,7 +13483,7 @@
       </c>
       <c r="F13" s="103"/>
       <c r="G13" s="116" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
@@ -14358,7 +14600,7 @@
       <c r="A2" s="129"/>
       <c r="B2" s="132"/>
       <c r="C2" s="133" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
@@ -14367,7 +14609,7 @@
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H2" s="136"/>
       <c r="I2" s="136"/>
@@ -14379,7 +14621,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="129"/>
       <c r="B3" s="137" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C3" s="63"/>
       <c r="D3" s="138"/>
@@ -14411,33 +14653,33 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E5" s="141" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="F5" s="141" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="I5" s="141" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="J5" s="141"/>
       <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="M5" s="140"/>
       <c r="N5" s="142"/>
@@ -14695,13 +14937,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="141" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="J6" s="141" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="K6" s="141" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
@@ -14971,10 +15213,10 @@
         <v>46174</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E8" s="134" t="n">
         <v>13000</v>
@@ -15026,10 +15268,10 @@
         <v>46266</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E10" s="134" t="n">
         <v>7000</v>
@@ -15171,7 +15413,7 @@
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="129"/>
       <c r="B17" s="137" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="138"/>
@@ -15179,7 +15421,7 @@
       <c r="F17" s="132"/>
       <c r="G17" s="132"/>
       <c r="H17" s="63" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I17" s="132"/>
       <c r="J17" s="132"/>
@@ -15205,33 +15447,33 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="140"/>
       <c r="B19" s="10" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E19" s="141" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="F19" s="141" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G19" s="141" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="I19" s="141" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="J19" s="141"/>
       <c r="K19" s="141"/>
       <c r="L19" s="21" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="M19" s="140"/>
       <c r="N19" s="142"/>
@@ -15489,13 +15731,13 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="141" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="J20" s="141" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="K20" s="141" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="L20" s="21"/>
       <c r="M20" s="140"/>
